--- a/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
+++ b/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-20" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,13 +35,13 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <color rgb="000CA30C"/>
+    </font>
+    <font>
       <color rgb="00D03B3B"/>
     </font>
     <font>
       <color rgb="00898781"/>
-    </font>
-    <font>
-      <color rgb="000CA30C"/>
     </font>
   </fonts>
   <fills count="3">
@@ -69,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -83,7 +83,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -542,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.425</v>
+        <v>0.705</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.023</v>
+        <v>0.0217</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>2548800</v>
+        <v>14476900</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="H2" t="n">
-        <v>34.26</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.472</v>
+        <v>0.626</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.481</v>
+        <v>0.537</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -587,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.445</v>
+        <v>0.33</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0</v>
+        <v>-0.0294</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>2167600</v>
+        <v>13559400</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="H3" t="n">
-        <v>78.7</v>
+        <v>63.6</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.39</v>
+        <v>0.307</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.285</v>
+        <v>0.259</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -632,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.6899999999999999</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0</v>
+        <v>0.055</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0.1</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>2058600</v>
+        <v>13545800</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="H4" t="n">
-        <v>78.11</v>
+        <v>24.48</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.625</v>
+        <v>0.116</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.537</v>
+        <v>0.309</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -677,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.265</v>
+        <v>0.47</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>-0.0364</v>
+        <v>0.0562</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1168900</v>
+        <v>12244900</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H5" t="n">
-        <v>38.24</v>
+        <v>81.92</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.295</v>
+        <v>0.393</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.28</v>
+        <v>0.286</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -722,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-0.0227</v>
+        <v>0.88</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1150000</v>
+        <v>9018600</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>1.53</v>
+        <v>0.13</v>
       </c>
       <c r="H6" t="n">
-        <v>42.03</v>
+        <v>62.03</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.223</v>
+        <v>0.832</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.232</v>
+        <v>0.741</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -767,45 +768,2234 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E7" s="8" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="E7" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>732900</v>
+        <v>8060800</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.05</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>49.91</v>
+        <v>33.85</v>
       </c>
       <c r="I7" s="9" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.775</v>
+        <v>0.396</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.776</v>
+        <v>0.406</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>7917800</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n"/>
+      <c r="K8" s="2" t="n"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>7071</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>OCR</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>7400200</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>29.14</v>
+      </c>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E10" s="8" t="n">
+        <v>-0.0278</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>6289000</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="H10" t="n">
+        <v>18.46</v>
+      </c>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>6807</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PUNCAK</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>0.0513</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>4757900</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>12.49</v>
+      </c>
+      <c r="H11" t="n">
+        <v>84.3</v>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E12" s="8" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>4519700</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H12" t="n">
+        <v>35.32</v>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0471</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PIONEER</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0.0548</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>4308700</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="H13" t="n">
+        <v>68.34</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="K13" s="2" t="n"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0104</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>GENETEC</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E14" s="8" t="n">
+        <v>-0.0345</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>3085400</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H14" t="n">
+        <v>33.77</v>
+      </c>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E15" s="8" t="n">
+        <v>-0.0098</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>2982700</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>1.942</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>1.754</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>-0.0251</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>2852400</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H16" t="n">
+        <v>41.14</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1.042</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.964</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HEXTAR</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>2642900</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H17" t="n">
+        <v>49.91</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>-0.0364</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>2526700</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H18" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>-0.0364</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>2481400</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H19" t="n">
+        <v>43.63</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="E20" s="8" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>2279200</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>2174500</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H21" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>3.668</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>3.055</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>-0.0154</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>1908500</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>45.65</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>2.635</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>2.556</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>-0.0186</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>1815200</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H23" t="n">
+        <v>31.05</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>1.708</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>1.763</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>-0.0116</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>1733900</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H24" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0.0247</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>1584900</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H25" t="n">
+        <v>57.67</v>
+      </c>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>0.394</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>-0.0553</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>1474800</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H26" t="n">
+        <v>60.56</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5843</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>KPS</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>0.007800000000000001</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>1469300</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="H27" t="n">
+        <v>78.69</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>-0.0621</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>1463600</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H28" t="n">
+        <v>40.06</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>0.6860000000000001</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5932</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>BPURI</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="E29" s="8" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>1383900</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="H29" t="n">
+        <v>42.03</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E30" s="8" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>1362200</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H30" t="n">
+        <v>49.92</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E31" s="8" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>1352300</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n"/>
+      <c r="K31" s="2" t="n"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>-0.0536</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>1329500</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H32" t="n">
+        <v>31.76</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E33" s="3" t="n">
+        <v>0.0137</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>1324200</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="H33" t="n">
+        <v>84.81999999999999</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>2.865</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>2.455</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>1263000</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H34" t="n">
+        <v>55.61</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>0.8110000000000001</v>
+      </c>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>1243000</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H35" t="n">
+        <v>59.52</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>1239300</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H36" t="n">
+        <v>55.75</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>1209200</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H37" t="n">
+        <v>45.37</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>-0.0345</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>1186000</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H38" t="n">
+        <v>49.76</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>0.416</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>5243</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>VELESTO</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>-0.0238</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>1131400</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H39" t="n">
+        <v>40.25</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0251</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>SFPTECH</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>-0.0385</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>1108900</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H40" t="n">
+        <v>38.79</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>1086900</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="H41" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0397</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5ER</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0.04650000000000001</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1059400</v>
+      </c>
+      <c r="G42" s="5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="H42" t="n">
+        <v>75.44</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>0.209</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>-0.011</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1015400</v>
+      </c>
+      <c r="G43" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H43" t="n">
+        <v>27.06</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>-0.0183</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>972000</v>
+      </c>
+      <c r="G44" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H44" t="n">
+        <v>46.52</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>0.5580000000000001</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E45" s="8" t="n">
+        <v>-0.023</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>881600</v>
+      </c>
+      <c r="G45" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H45" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>804000</v>
+      </c>
+      <c r="G46" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H46" t="n">
+        <v>50.9</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>802600</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H47" t="n">
+        <v>68.05</v>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>-0.013</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>785400</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H48" t="n">
+        <v>47</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>-0.0336</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>718600</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H49" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>690000</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H50" t="n">
+        <v>47.87</v>
+      </c>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>-0.0452</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>616100</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H51" t="n">
+        <v>56.63</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>0.731</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="7" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>-0.0242</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>614700</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H52" t="n">
+        <v>48.06</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>0.824</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E53" s="8" t="n">
+        <v>-0.0226</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>560800</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H53" t="n">
+        <v>33.49</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>0.744</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5338</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>PARADIGM</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>0.795</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>536200</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H54" t="n">
+        <v>23.74</v>
+      </c>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>0.8179999999999999</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="7" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>536000</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H55" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>519000</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H56" t="n">
+        <v>51.58</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M7"/>
+  <autoFilter ref="A1:M56"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
+++ b/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-20" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,10 +35,10 @@
       <color rgb="00FFFFFF"/>
     </font>
     <font>
-      <color rgb="000CA30C"/>
+      <color rgb="00D03B3B"/>
     </font>
     <font>
-      <color rgb="00D03B3B"/>
+      <color rgb="000CA30C"/>
     </font>
     <font>
       <color rgb="00898781"/>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -543,39 +543,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.705</v>
+        <v>0.33</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>0.0217</v>
+        <v>-0.0294</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>14476900</v>
+        <v>32343800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.57</v>
+        <v>0.4</v>
       </c>
       <c r="H2" t="n">
-        <v>80.01000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.626</v>
+        <v>0.307</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0.537</v>
+        <v>0.259</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" s="7" t="inlineStr"/>
@@ -588,39 +588,39 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.33</v>
+        <v>0.47</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>-0.0294</v>
+        <v>0.0562</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>13559400</v>
+        <v>25781300</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.17</v>
+        <v>0.74</v>
       </c>
       <c r="H3" t="n">
-        <v>63.6</v>
+        <v>81.92</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.307</v>
+        <v>0.393</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0.259</v>
+        <v>0.286</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" s="7" t="inlineStr"/>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.0145</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>13545800</v>
+        <v>15769200</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.04</v>
+        <v>0.62</v>
       </c>
       <c r="H4" t="n">
-        <v>24.48</v>
+        <v>79.42</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.116</v>
+        <v>0.626</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.309</v>
+        <v>0.537</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0.0562</v>
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>12244900</v>
+        <v>15236600</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.35</v>
+        <v>0.04</v>
       </c>
       <c r="H5" t="n">
-        <v>81.92</v>
+        <v>22.63</v>
       </c>
       <c r="I5" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.393</v>
+        <v>0.116</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.286</v>
+        <v>0.309</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -732,27 +732,27 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>-0.0112</v>
+        <v>0.885</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>9018600</v>
+        <v>13303500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H6" t="n">
-        <v>62.03</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
+        <v>63.08</v>
+      </c>
+      <c r="I6" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.832</v>
+        <v>0.833</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.741</v>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0</v>
+        <v>0.375</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>8060800</v>
+        <v>9382900</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="H7" t="n">
-        <v>33.85</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
+        <v>22.97</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.396</v>
+        <v>0.508</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.406</v>
+        <v>0.606</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -822,18 +822,18 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>7917800</v>
+        <v>9154600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
+        <v>0.39</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
@@ -851,39 +851,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>OCR</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>7400200</v>
+        <v>9091300</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>3</v>
+        <v>0.91</v>
       </c>
       <c r="H9" t="n">
-        <v>29.14</v>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
+        <v>28.49</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.049</v>
+        <v>0.396</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.05</v>
+        <v>0.406</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -896,39 +896,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E10" s="8" t="n">
-        <v>-0.0278</v>
+        <v>0.475</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-0.06860000000000001</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>6289000</v>
+        <v>7826800</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>18.46</v>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
+        <v>43.95</v>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.505</v>
+        <v>0.515</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.606</v>
+        <v>0.463</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -941,39 +941,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PUNCAK</t>
+          <t>OCR</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0.0513</v>
+        <v>0.045</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>4757900</v>
+        <v>7400200</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>12.49</v>
+        <v>3</v>
       </c>
       <c r="H11" t="n">
-        <v>84.3</v>
+        <v>29.14</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.177</v>
+        <v>0.049</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.171</v>
+        <v>0.05</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -986,39 +986,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>-0.0115</v>
+        <v>0.265</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-0.0364</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>4519700</v>
+        <v>6843000</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.12</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="n">
-        <v>35.32</v>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
+        <v>38.24</v>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.473</v>
+        <v>0.295</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.481</v>
+        <v>0.28</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1031,38 +1031,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.385</v>
+        <v>1.54</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>0.0548</v>
+        <v>-0.0435</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>4308700</v>
+        <v>6840200</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.82</v>
+        <v>1.37</v>
       </c>
       <c r="H13" t="n">
-        <v>68.34</v>
+        <v>28.24</v>
       </c>
       <c r="I13" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="K13" s="2" t="n"/>
+        <v>1.704</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1.762</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1074,40 +1076,38 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>-0.0345</v>
+        <v>0.0411</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>3085400</v>
+        <v>6773100</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.49</v>
+        <v>1.29</v>
       </c>
       <c r="H14" t="n">
-        <v>33.77</v>
+        <v>67.44</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0.334</v>
-      </c>
+        <v>0.325</v>
+      </c>
+      <c r="K14" s="2" t="n"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
     </row>
@@ -1119,39 +1119,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>PUNCAK</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>2.03</v>
+        <v>0.205</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>-0.0098</v>
+        <v>0.0513</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2982700</v>
+        <v>5555100</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1</v>
+        <v>14.58</v>
       </c>
       <c r="H15" t="n">
-        <v>59.32</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
+        <v>84.3</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.942</v>
+        <v>0.177</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>1.754</v>
+        <v>0.171</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1164,39 +1164,39 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>-0.0251</v>
+        <v>0.43</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>2852400</v>
+        <v>5229700</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.35</v>
+        <v>0.14</v>
       </c>
       <c r="H16" t="n">
-        <v>41.14</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
+        <v>35.32</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.042</v>
+        <v>0.473</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>0.964</v>
+        <v>0.481</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1209,39 +1209,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
+        <v>2.01</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.0195</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>2642900</v>
+        <v>4902000</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.17</v>
       </c>
       <c r="H17" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I17" s="6" t="inlineStr">
+        <v>57.86</v>
+      </c>
+      <c r="I17" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>0.775</v>
+        <v>1.94</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0.776</v>
+        <v>1.753</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1254,39 +1254,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E18" s="8" t="n">
-        <v>-0.0364</v>
+        <v>0.535</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>2526700</v>
+        <v>4792600</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.26</v>
+        <v>0.23</v>
       </c>
       <c r="H18" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
+        <v>44.44</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.295</v>
+        <v>0.57</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.28</v>
+        <v>0.543</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1299,39 +1299,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E19" s="8" t="n">
-        <v>-0.0364</v>
+        <v>0.775</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>2481400</v>
+        <v>4512900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.12</v>
+        <v>0.29</v>
       </c>
       <c r="H19" t="n">
-        <v>43.63</v>
+        <v>49.91</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.569</v>
+        <v>0.775</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.542</v>
+        <v>0.776</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1344,39 +1344,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E20" s="8" t="n">
-        <v>-0.0294</v>
+        <v>0.29</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>2279200</v>
+        <v>4010700</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="H20" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
+        <v>36.95</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.517</v>
+        <v>0.313</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.464</v>
+        <v>0.334</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1389,39 +1389,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>-0.0052</v>
+        <v>0.97</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0251</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>2174500</v>
+        <v>3575200</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="H21" t="n">
-        <v>58.09</v>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
+        <v>41.14</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.668</v>
+        <v>1.042</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>3.055</v>
+        <v>0.964</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1434,40 +1434,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>-0.0154</v>
+        <v>0.705</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.06619999999999999</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>1908500</v>
+        <v>3257100</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H22" t="n">
-        <v>45.65</v>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n">
-        <v>2.635</v>
-      </c>
-      <c r="K22" s="2" t="n">
-        <v>2.556</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n"/>
+      <c r="K22" s="2" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
     </row>
@@ -1479,39 +1472,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>-0.0186</v>
+        <v>0.345</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>1815200</v>
+        <v>3179400</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
       <c r="H23" t="n">
-        <v>31.05</v>
-      </c>
-      <c r="I23" s="9" t="inlineStr">
+        <v>48.17</v>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.708</v>
+        <v>0.353</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1.763</v>
+        <v>0.328</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1524,39 +1517,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>-0.0116</v>
+        <v>3.84</v>
+      </c>
+      <c r="E24" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>1733900</v>
+        <v>2940500</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.08</v>
+        <v>0.34</v>
       </c>
       <c r="H24" t="n">
-        <v>53.34</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
+        <v>58.77</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.423</v>
+        <v>3.67</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.37</v>
+        <v>3.056</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1569,39 +1562,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.415</v>
+        <v>0.82</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>0.0247</v>
+        <v>-0.0061</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>1584900</v>
+        <v>2827300</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H25" t="n">
-        <v>57.67</v>
+        <v>55.61</v>
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.394</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.379</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1614,39 +1607,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>-0.0553</v>
+        <v>0.68</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-0.0621</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1474800</v>
+        <v>2799100</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.36</v>
+        <v>0.54</v>
       </c>
       <c r="H26" t="n">
-        <v>60.56</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
+        <v>40.06</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.85</v>
+        <v>0.753</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.586</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1659,39 +1652,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.645</v>
+        <v>2.56</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.007800000000000001</v>
+        <v>-0.0116</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1469300</v>
+        <v>2629300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>8.19</v>
+        <v>0.14</v>
       </c>
       <c r="H27" t="n">
-        <v>78.69</v>
+        <v>46.2</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>2.636</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.546</v>
+        <v>2.556</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1704,39 +1697,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.68</v>
+        <v>0.41</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>-0.0621</v>
+        <v>0.0123</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1463600</v>
+        <v>2607400</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.28</v>
+        <v>0.21</v>
       </c>
       <c r="H28" t="n">
-        <v>40.06</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
+        <v>56.41</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.753</v>
+        <v>0.393</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.379</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1749,39 +1742,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E29" s="8" t="n">
-        <v>-0.0227</v>
+        <v>0.545</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.0268</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>1383900</v>
+        <v>2499600</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>1.84</v>
+        <v>0.27</v>
       </c>
       <c r="H29" t="n">
-        <v>42.03</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
+        <v>33.38</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.223</v>
+        <v>0.637</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.232</v>
+        <v>0.619</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1794,39 +1787,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E30" s="8" t="n">
-        <v>-0.0133</v>
+        <v>0.63</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>1362200</v>
+        <v>2424700</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="H30" t="n">
-        <v>49.92</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
+        <v>59.52</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.371</v>
+        <v>0.619</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.369</v>
+        <v>0.616</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1839,33 +1832,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.745</v>
+        <v>4.75</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>-0.0132</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>1352300</v>
+        <v>2381000</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I31" s="6" t="inlineStr">
+        <v>0.12</v>
+      </c>
+      <c r="H31" t="n">
+        <v>50.15</v>
+      </c>
+      <c r="I31" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
+      <c r="J31" s="2" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>4.84</v>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
     </row>
@@ -1877,39 +1877,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>-0.0536</v>
+        <v>0.0133</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>1329500</v>
+        <v>2318000</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.14</v>
+        <v>0.31</v>
       </c>
       <c r="H32" t="n">
-        <v>31.76</v>
+        <v>60.65</v>
       </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.635</v>
+        <v>0.372</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.619</v>
+        <v>0.369</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1922,39 +1922,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>3.19</v>
+        <v>0.335</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.0137</v>
+        <v>-0.0147</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1324200</v>
+        <v>2279000</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.42</v>
+        <v>0.23</v>
       </c>
       <c r="H33" t="n">
-        <v>84.81999999999999</v>
+        <v>47.18</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>2.865</v>
+        <v>0.345</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2.455</v>
+        <v>0.335</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1967,39 +1967,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>-0.0061</v>
+        <v>0.465</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-0.0312</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1263000</v>
+        <v>2220400</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="H34" t="n">
-        <v>55.61</v>
+        <v>35.11</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.503</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.523</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2012,39 +2012,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.63</v>
+        <v>0.43</v>
       </c>
       <c r="E35" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>1243000</v>
+        <v>2007700</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="H35" t="n">
-        <v>59.52</v>
+        <v>54.75</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.619</v>
+        <v>0.423</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.616</v>
+        <v>0.371</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2057,39 +2057,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>-0.033</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1239300</v>
+        <v>2000500</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>1.33</v>
+        <v>0.09</v>
       </c>
       <c r="H36" t="n">
-        <v>55.75</v>
+        <v>25.77</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.276</v>
+        <v>0.501</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.268</v>
+        <v>0.665</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2102,39 +2102,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>-0.0294</v>
+        <v>0.205</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1209200</v>
+        <v>1934200</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
       <c r="H37" t="n">
-        <v>45.37</v>
-      </c>
-      <c r="I37" s="9" t="inlineStr">
+        <v>40.25</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.345</v>
+        <v>0.217</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.334</v>
+        <v>0.234</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2147,39 +2147,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>-0.0345</v>
+        <v>0.9350000000000001</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>-0.0603</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1186000</v>
+        <v>1877000</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.17</v>
+        <v>0.46</v>
       </c>
       <c r="H38" t="n">
-        <v>49.76</v>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
+        <v>60.18</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.424</v>
+        <v>0.85</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.416</v>
+        <v>0.586</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2192,39 +2192,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.205</v>
+        <v>0.23</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>-0.0238</v>
+        <v>0.0698</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1131400</v>
+        <v>1819200</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.05</v>
+        <v>1.79</v>
       </c>
       <c r="H39" t="n">
-        <v>40.25</v>
+        <v>78.56</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.217</v>
+        <v>0.21</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.234</v>
+        <v>0.21</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2237,39 +2237,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.25</v>
+        <v>3.2</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>-0.0385</v>
+        <v>0.0168</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1108900</v>
+        <v>1781500</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.16</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>38.79</v>
+        <v>85.06</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.271</v>
+        <v>2.866</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.292</v>
+        <v>2.455</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2282,39 +2282,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>0.0238</v>
+        <v>0.65</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1086900</v>
+        <v>1616700</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.51</v>
+        <v>9.02</v>
       </c>
       <c r="H41" t="n">
-        <v>56.24</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
+        <v>79.31</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.418</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.433</v>
+        <v>0.546</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2327,39 +2327,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.31</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1059400</v>
+        <v>1597000</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>1.04</v>
+        <v>0.08</v>
       </c>
       <c r="H42" t="n">
-        <v>75.44</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
+        <v>54.55</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.209</v>
+        <v>0.309</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.21</v>
+        <v>0.301</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2372,39 +2372,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>-0.011</v>
+        <v>0.425</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1015400</v>
+        <v>1418300</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="H43" t="n">
-        <v>27.06</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
+        <v>51</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.502</v>
+        <v>0.425</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.665</v>
+        <v>0.416</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2417,39 +2417,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>-0.0183</v>
+        <v>0.215</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>972000</v>
+        <v>1383900</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.18</v>
+        <v>1.84</v>
       </c>
       <c r="H44" t="n">
-        <v>46.52</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
+        <v>42.03</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.223</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.518</v>
+        <v>0.232</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2462,39 +2462,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="E45" s="8" t="n">
-        <v>-0.023</v>
+        <v>0.25</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>881600</v>
+        <v>1362500</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="H45" t="n">
-        <v>40.99</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
+        <v>38.79</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.92</v>
+        <v>0.271</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.85</v>
+        <v>0.292</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2507,39 +2507,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0</v>
+        <v>1.41</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>804000</v>
+        <v>1359500</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.36</v>
+        <v>0.12</v>
       </c>
       <c r="H46" t="n">
-        <v>50.9</v>
+        <v>20.99</v>
       </c>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>0.637</v>
+        <v>1.666</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0.624</v>
+        <v>1.931</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2552,39 +2552,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.975</v>
+        <v>0.215</v>
       </c>
       <c r="E47" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>802600</v>
+        <v>1328800</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="H47" t="n">
-        <v>68.05</v>
+        <v>31.92</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.93</v>
+        <v>0.233</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.88</v>
+        <v>0.282</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2597,39 +2597,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>-0.013</v>
+        <v>0.865</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>785400</v>
+        <v>1327400</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>47</v>
+        <v>46.09</v>
       </c>
       <c r="I48" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.77</v>
+        <v>0.868</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.771</v>
+        <v>0.869</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2642,39 +2642,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>-0.0336</v>
+        <v>0.54</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.0092</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>718600</v>
+        <v>1311800</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H49" t="n">
-        <v>64.59999999999999</v>
+        <v>47.65</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
-          <t>多头</t>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.516</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.471</v>
+        <v>0.518</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2687,39 +2687,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.585</v>
+        <v>1.29</v>
       </c>
       <c r="E50" s="8" t="n">
-        <v>-0.0168</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>690000</v>
+        <v>1282100</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H50" t="n">
-        <v>47.87</v>
+        <v>63.52</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.597</v>
+        <v>1.207</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.586</v>
+        <v>1.192</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2732,39 +2732,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>-0.0452</v>
+        <v>0.86</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>616100</v>
+        <v>1274700</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.27</v>
+        <v>0.17</v>
       </c>
       <c r="H51" t="n">
-        <v>56.63</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
+        <v>42.14</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.731</v>
+        <v>0.921</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.652</v>
+        <v>0.85</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2777,39 +2777,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>-0.0242</v>
+        <v>0.28</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>614700</v>
+        <v>1239300</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.18</v>
+        <v>1.33</v>
       </c>
       <c r="H52" t="n">
-        <v>48.06</v>
+        <v>55.75</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.824</v>
+        <v>0.276</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.784</v>
+        <v>0.268</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2822,39 +2822,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.65</v>
+        <v>7.19</v>
       </c>
       <c r="E53" s="8" t="n">
-        <v>-0.0226</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>560800</v>
+        <v>1192500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>33.49</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
+        <v>35.12</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.717</v>
+        <v>7.475</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.744</v>
+        <v>7.672</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2867,39 +2867,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PARADIGM</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.795</v>
+        <v>0.43</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>-0.0124</v>
+        <v>0.0238</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>536200</v>
+        <v>1157900</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>1.4</v>
+        <v>0.55</v>
       </c>
       <c r="H54" t="n">
-        <v>23.74</v>
+        <v>56.24</v>
       </c>
       <c r="I54" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.418</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.848</v>
+        <v>0.433</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2912,39 +2912,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>-0.016</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>536000</v>
+        <v>1052400</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="H55" t="n">
-        <v>38.68</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
-          <t>空头</t>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.292</v>
+        <v>0.795</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1.314</v>
+        <v>0.773</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2957,45 +2957,1665 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>0.0167</v>
+        <v>0.77</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>519000</v>
+        <v>1050400</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H56" t="n">
-        <v>51.58</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
+        <v>49.5</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.238</v>
+        <v>0.771</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.077</v>
+        <v>0.772</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>5148</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>UEMS</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>1046600</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H57" t="n">
+        <v>27.78</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="7" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0345</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SUNLOGY</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>1030300</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H58" t="n">
+        <v>41.34</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>0.434</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>-0.0168</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>1017600</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H59" t="n">
+        <v>67.13</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5102</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>GCB</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-0.016</v>
+      </c>
+      <c r="F60" s="4" t="n">
+        <v>970100</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H60" t="n">
+        <v>38.68</v>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>1.292</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>1.314</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="7" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F61" s="4" t="n">
+        <v>962300</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H61" t="n">
+        <v>48.87</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="7" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>-0.008399999999999999</v>
+      </c>
+      <c r="F62" s="4" t="n">
+        <v>933900</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H62" t="n">
+        <v>49.02</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>-0.0155</v>
+      </c>
+      <c r="F63" s="4" t="n">
+        <v>897600</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>40.83</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>0.674</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>0.6889999999999999</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F64" s="4" t="n">
+        <v>888200</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H64" t="n">
+        <v>53.44</v>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="7" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="E65" s="8" t="n">
+        <v>0.0123</v>
+      </c>
+      <c r="F65" s="4" t="n">
+        <v>875600</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H65" t="n">
+        <v>54.36</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>2.448</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>2.392</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="7" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="4" t="n">
+        <v>846900</v>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H66" t="n">
+        <v>68.05</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="7" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0359</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HKB</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>-0.0258</v>
+      </c>
+      <c r="F67" s="4" t="n">
+        <v>841700</v>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H67" t="n">
+        <v>60.75</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>0.732</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="7" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="F68" s="4" t="n">
+        <v>827100</v>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H68" t="n">
+        <v>22.97</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>1.375</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>1.551</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="7" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-0.0157</v>
+      </c>
+      <c r="F69" s="4" t="n">
+        <v>824000</v>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H69" t="n">
+        <v>44.42</v>
+      </c>
+      <c r="I69" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="K69" s="2" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F70" s="4" t="n">
+        <v>811100</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H70" t="n">
+        <v>29.66</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>2.769</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>2.879</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="4" t="n">
+        <v>806700</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H71" t="n">
+        <v>49.45</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>1.236</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>1.077</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.0301</v>
+      </c>
+      <c r="F72" s="4" t="n">
+        <v>794100</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H72" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="F73" s="4" t="n">
+        <v>792100</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H73" t="n">
+        <v>51.56</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>1.625</v>
+      </c>
+      <c r="K73" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F74" s="4" t="n">
+        <v>730900</v>
+      </c>
+      <c r="G74" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H74" t="n">
+        <v>33.15</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="K74" s="2" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="F75" s="4" t="n">
+        <v>726100</v>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H75" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>2.802</v>
+      </c>
+      <c r="K75" s="2" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>7179</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>LAGENDA</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F76" s="4" t="n">
+        <v>711900</v>
+      </c>
+      <c r="G76" s="5" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H76" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>1.497</v>
+      </c>
+      <c r="K76" s="2" t="n">
+        <v>1.504</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="F77" s="4" t="n">
+        <v>707500</v>
+      </c>
+      <c r="G77" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H77" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>3.955</v>
+      </c>
+      <c r="K77" s="2" t="n">
+        <v>3.572</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>6.73</v>
+      </c>
+      <c r="E78" s="8" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="F78" s="4" t="n">
+        <v>695700</v>
+      </c>
+      <c r="G78" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H78" t="n">
+        <v>31.09</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>7.163</v>
+      </c>
+      <c r="K78" s="2" t="n">
+        <v>7.581</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F79" s="4" t="n">
+        <v>634600</v>
+      </c>
+      <c r="G79" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H79" t="n">
+        <v>32.46</v>
+      </c>
+      <c r="I79" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>2.134</v>
+      </c>
+      <c r="K79" s="2" t="n">
+        <v>2.235</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5338</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>PARADIGM</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F80" s="4" t="n">
+        <v>598200</v>
+      </c>
+      <c r="G80" s="5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="H80" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K80" s="2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F81" s="4" t="n">
+        <v>595300</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H81" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="K81" s="2" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>-0.0315</v>
+      </c>
+      <c r="F82" s="4" t="n">
+        <v>585000</v>
+      </c>
+      <c r="G82" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H82" t="n">
+        <v>46.57</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="K82" s="2" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F83" s="4" t="n">
+        <v>581500</v>
+      </c>
+      <c r="G83" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H83" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="K83" s="2" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>0.775</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F84" s="4" t="n">
+        <v>576900</v>
+      </c>
+      <c r="G84" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H84" t="n">
+        <v>57.68</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K84" s="2" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F85" s="4" t="n">
+        <v>568900</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H85" t="n">
+        <v>46.11</v>
+      </c>
+      <c r="I85" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>4.893</v>
+      </c>
+      <c r="K85" s="2" t="n">
+        <v>4.736</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>-0.009000000000000001</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>556500</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H86" t="n">
+        <v>43.24</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K86" s="2" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0.008500000000000001</v>
+      </c>
+      <c r="F87" s="4" t="n">
+        <v>552100</v>
+      </c>
+      <c r="G87" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H87" t="n">
+        <v>38.44</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="K87" s="2" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>6.51</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F88" s="4" t="n">
+        <v>538000</v>
+      </c>
+      <c r="G88" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H88" t="n">
+        <v>56.99</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>6.209</v>
+      </c>
+      <c r="K88" s="2" t="n">
+        <v>5.931</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F89" s="4" t="n">
+        <v>511400</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H89" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="I89" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K89" s="2" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F90" s="4" t="n">
+        <v>508100</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H90" t="n">
+        <v>43.57</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>2.601</v>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="F91" s="4" t="n">
+        <v>502900</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H91" t="n">
+        <v>60.34</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>2.233</v>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F92" s="4" t="n">
+        <v>501300</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H92" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>1.364</v>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M56"/>
+  <autoFilter ref="A1:M92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
+++ b/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-20" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$120</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M92"/>
+  <dimension ref="A1:M120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.0294</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>32343800</v>
+        <v>39038200</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.4</v>
+        <v>0.48</v>
       </c>
       <c r="H2" t="n">
         <v>63.6</v>
@@ -603,10 +603,10 @@
         <v>0.0562</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>25781300</v>
+        <v>30125400</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.74</v>
+        <v>0.87</v>
       </c>
       <c r="H3" t="n">
         <v>81.92</v>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.7</v>
+        <v>0.055</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>0.0145</v>
+        <v>0.1</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>15769200</v>
+        <v>19957600</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.62</v>
+        <v>0.05</v>
       </c>
       <c r="H4" t="n">
-        <v>79.42</v>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.48</v>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.626</v>
+        <v>0.116</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.537</v>
+        <v>0.309</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E5" s="8" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>15236600</v>
+        <v>17158800</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.04</v>
+        <v>0.68</v>
       </c>
       <c r="H5" t="n">
-        <v>22.63</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.01000000000001</v>
+      </c>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.116</v>
+        <v>0.626</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.309</v>
+        <v>0.537</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.885</v>
+        <v>0.88</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.005600000000000001</v>
+        <v>-0.0112</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>13303500</v>
+        <v>14946200</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H6" t="n">
-        <v>63.08</v>
+        <v>62.03</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.833</v>
+        <v>0.832</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>0.741</v>
@@ -777,19 +777,19 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.375</v>
+        <v>0.395</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.09720000000000001</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>9382900</v>
+        <v>13559500</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.02</v>
+        <v>1.47</v>
       </c>
       <c r="H7" t="n">
-        <v>22.97</v>
+        <v>27.6</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.508</v>
+        <v>0.51</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.606</v>
+        <v>0.607</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,33 +813,40 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.245</v>
+        <v>0.47</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.0784</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>9154600</v>
+        <v>11814600</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.39</v>
+        <v>1.06</v>
+      </c>
+      <c r="H8" t="n">
+        <v>43.16</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
+      <c r="J8" s="2" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>0.463</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
     </row>
@@ -851,28 +858,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.385</v>
+        <v>0.265</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.0128</v>
+        <v>-0.0364</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>9091300</v>
+        <v>10549100</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.91</v>
+        <v>1.07</v>
       </c>
       <c r="H9" t="n">
-        <v>28.49</v>
+        <v>38.24</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -880,10 +887,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.396</v>
+        <v>0.295</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.406</v>
+        <v>0.28</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -896,28 +903,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.475</v>
+        <v>0.385</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-0.06860000000000001</v>
+        <v>-0.0128</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>7826800</v>
+        <v>9505300</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.7</v>
+        <v>0.95</v>
       </c>
       <c r="H10" t="n">
-        <v>43.95</v>
+        <v>28.49</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -925,10 +932,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.515</v>
+        <v>0.396</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.463</v>
+        <v>0.406</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -941,40 +948,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>OCR</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0</v>
+        <v>0.245</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.02</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>7400200</v>
+        <v>9170000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H11" t="n">
-        <v>29.14</v>
+        <v>0.39</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -986,28 +986,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.265</v>
+        <v>1.53</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.0364</v>
+        <v>-0.04969999999999999</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>6843000</v>
+        <v>8606600</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.7</v>
+        <v>1.72</v>
       </c>
       <c r="H12" t="n">
-        <v>38.24</v>
+        <v>27.62</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.295</v>
+        <v>1.703</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.28</v>
+        <v>1.762</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1031,40 +1031,38 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>-0.0435</v>
+        <v>0.38</v>
+      </c>
+      <c r="E13" s="8" t="n">
+        <v>0.0411</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6840200</v>
+        <v>7839400</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.37</v>
+        <v>1.49</v>
       </c>
       <c r="H13" t="n">
-        <v>28.24</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.44</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.704</v>
-      </c>
-      <c r="K13" s="2" t="n">
-        <v>1.762</v>
-      </c>
+        <v>0.325</v>
+      </c>
+      <c r="K13" s="2" t="n"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1076,38 +1074,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>0.0411</v>
+        <v>0.43</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6773100</v>
+        <v>7795300</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>1.29</v>
+        <v>0.21</v>
       </c>
       <c r="H14" t="n">
-        <v>67.44</v>
-      </c>
-      <c r="I14" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.32</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="K14" s="2" t="n"/>
+        <v>0.473</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.481</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
     </row>
@@ -1119,39 +1119,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>PUNCAK</t>
+          <t>OCR</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>0.0513</v>
+        <v>0.045</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>5555100</v>
+        <v>7400200</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>14.58</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>84.3</v>
-      </c>
-      <c r="I15" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.14</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.177</v>
+        <v>0.049</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.171</v>
+        <v>0.05</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1164,40 +1164,33 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.43</v>
+        <v>0.735</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.0115</v>
+        <v>-0.0265</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>5229700</v>
+        <v>6694300</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H16" t="n">
-        <v>35.32</v>
+        <v>0.11</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>0.481</v>
-      </c>
+      <c r="J16" s="2" t="n"/>
+      <c r="K16" s="2" t="n"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
     </row>
@@ -1209,28 +1202,28 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>PUNCAK</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-0.0195</v>
+        <v>0.2</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>4902000</v>
+        <v>6258400</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.17</v>
+        <v>16.43</v>
       </c>
       <c r="H17" t="n">
-        <v>57.86</v>
+        <v>82.42</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -1238,10 +1231,10 @@
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.94</v>
+        <v>0.177</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>1.753</v>
+        <v>0.171</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
@@ -1254,39 +1247,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.535</v>
+        <v>2.03</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-0.0273</v>
+        <v>-0.0098</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>4792600</v>
+        <v>5956500</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="H18" t="n">
-        <v>44.44</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.32</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.57</v>
+        <v>1.942</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.543</v>
+        <v>1.754</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1299,39 +1292,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.775</v>
+        <v>0.29</v>
       </c>
       <c r="E19" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>4512900</v>
+        <v>5876400</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.29</v>
+        <v>0.93</v>
       </c>
       <c r="H19" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.95</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.775</v>
+        <v>0.313</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.776</v>
+        <v>0.334</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1344,28 +1337,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>4010700</v>
+        <v>5675400</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.63</v>
+        <v>0.27</v>
       </c>
       <c r="H20" t="n">
-        <v>36.95</v>
+        <v>45.28</v>
       </c>
       <c r="I20" s="6" t="inlineStr">
         <is>
@@ -1373,10 +1366,10 @@
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.313</v>
+        <v>0.57</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.334</v>
+        <v>0.543</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1389,39 +1382,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="E21" s="3" t="n">
-        <v>-0.0251</v>
+        <v>0.775</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3575200</v>
+        <v>5620500</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="H21" t="n">
-        <v>41.14</v>
-      </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.91</v>
+      </c>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>1.042</v>
+        <v>0.775</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.964</v>
+        <v>0.776</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1434,33 +1427,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.06619999999999999</v>
+        <v>0.31</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3257100</v>
+        <v>5263000</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="n"/>
-      <c r="K22" s="2" t="n"/>
+        <v>0.27</v>
+      </c>
+      <c r="H22" t="n">
+        <v>54.55</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>0.301</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
     </row>
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.345</v>
+        <v>0.205</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-0.0143</v>
+        <v>-0.0238</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>3179400</v>
+        <v>4851100</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.41</v>
+        <v>0.22</v>
       </c>
       <c r="H23" t="n">
-        <v>48.17</v>
+        <v>40.25</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.353</v>
+        <v>0.217</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.328</v>
+        <v>0.234</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1517,28 +1517,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>3.84</v>
+        <v>0.175</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>2940500</v>
+        <v>4750000</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.34</v>
+        <v>0.21</v>
       </c>
       <c r="H24" t="n">
-        <v>58.77</v>
+        <v>40.18</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>3.67</v>
+        <v>0.188</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>3.056</v>
+        <v>0.185</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1562,39 +1562,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-0.0061</v>
+        <v>0.175</v>
+      </c>
+      <c r="E25" s="8" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>2827300</v>
+        <v>4677400</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.18</v>
+        <v>0.9</v>
       </c>
       <c r="H25" t="n">
-        <v>55.61</v>
-      </c>
-      <c r="I25" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.66</v>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.174</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.181</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1607,28 +1607,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.68</v>
+        <v>0.97</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.0621</v>
+        <v>-0.0251</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2799100</v>
+        <v>4501500</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H26" t="n">
-        <v>40.06</v>
+        <v>41.14</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1636,10 +1636,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.753</v>
+        <v>1.042</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.964</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1652,39 +1652,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>2.56</v>
+        <v>0.82</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.0116</v>
+        <v>-0.0061</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>2629300</v>
+        <v>4487600</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="H27" t="n">
-        <v>46.2</v>
-      </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.61</v>
+      </c>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>2.636</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>2.556</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1706,19 +1706,19 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.41</v>
+        <v>0.415</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0.0123</v>
+        <v>0.0247</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>2607400</v>
+        <v>4162200</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.21</v>
+        <v>0.34</v>
       </c>
       <c r="H28" t="n">
-        <v>56.41</v>
+        <v>57.67</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1726,7 +1726,7 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.393</v>
+        <v>0.394</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0.379</v>
@@ -1742,39 +1742,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-0.0268</v>
+        <v>0.63</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2499600</v>
+        <v>4139800</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="H29" t="n">
-        <v>33.38</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.52</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.637</v>
+        <v>0.619</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.619</v>
+        <v>0.616</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1787,39 +1787,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0</v>
+        <v>2.57</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>2424700</v>
+        <v>3726600</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="H30" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="I30" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.76</v>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.619</v>
+        <v>2.637</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.616</v>
+        <v>2.556</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1832,39 +1832,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>4.75</v>
+        <v>0.125</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0417</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>2381000</v>
+        <v>3489700</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="H31" t="n">
-        <v>50.15</v>
-      </c>
-      <c r="I31" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.06</v>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>4.73</v>
+        <v>0.126</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>4.84</v>
+        <v>0.102</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1877,39 +1877,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E32" s="8" t="n">
-        <v>0.0133</v>
+        <v>0.135</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>2318000</v>
+        <v>3422100</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.31</v>
+        <v>0.05</v>
       </c>
       <c r="H32" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.16</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.372</v>
+        <v>0.157</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.369</v>
+        <v>0.141</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1922,28 +1922,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.335</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>-0.0147</v>
+        <v>-0.0552</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>2279000</v>
+        <v>3384200</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.23</v>
+        <v>0.66</v>
       </c>
       <c r="H33" t="n">
-        <v>47.18</v>
+        <v>40.68</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.345</v>
+        <v>0.753</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.335</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1967,28 +1967,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.465</v>
+        <v>0.545</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-0.0312</v>
+        <v>-0.0268</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>2220400</v>
+        <v>3372900</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.26</v>
+        <v>0.37</v>
       </c>
       <c r="H34" t="n">
-        <v>35.11</v>
+        <v>33.38</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.503</v>
+        <v>0.637</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.523</v>
+        <v>0.619</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2012,28 +2012,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.175</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.0541</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2007700</v>
+        <v>3316100</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.1</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>54.75</v>
+        <v>24.82</v>
       </c>
       <c r="I35" s="6" t="inlineStr">
         <is>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.423</v>
+        <v>0.197</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.371</v>
+        <v>0.207</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2057,39 +2057,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E36" s="3" t="n">
-        <v>-0.033</v>
+        <v>4.74</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0.0064</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>2000500</v>
+        <v>3238700</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.09</v>
+        <v>0.16</v>
       </c>
       <c r="H36" t="n">
-        <v>25.77</v>
-      </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.36</v>
+      </c>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.501</v>
+        <v>4.729</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.665</v>
+        <v>4.84</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2102,28 +2102,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.205</v>
+        <v>3.81</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.0238</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>1934200</v>
+        <v>3219100</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="H37" t="n">
-        <v>40.25</v>
+        <v>57.75</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2131,10 +2131,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.217</v>
+        <v>3.667</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.234</v>
+        <v>3.055</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2147,28 +2147,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.345</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>-0.0603</v>
+        <v>-0.0143</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1877000</v>
+        <v>3179400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="H38" t="n">
-        <v>60.18</v>
+        <v>48.17</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.85</v>
+        <v>0.353</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.586</v>
+        <v>0.328</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2192,28 +2192,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="E39" s="8" t="n">
-        <v>0.0698</v>
+        <v>0.0133</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>1819200</v>
+        <v>2784200</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>1.79</v>
+        <v>0.38</v>
       </c>
       <c r="H39" t="n">
-        <v>78.56</v>
+        <v>60.65</v>
       </c>
       <c r="I39" s="9" t="inlineStr">
         <is>
@@ -2221,10 +2221,10 @@
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.21</v>
+        <v>0.372</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.21</v>
+        <v>0.369</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2237,28 +2237,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0.0168</v>
+        <v>0.865</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1781500</v>
+        <v>2751400</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.14</v>
       </c>
       <c r="H40" t="n">
-        <v>85.06</v>
+        <v>46.09</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>2.866</v>
+        <v>0.868</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>2.455</v>
+        <v>0.869</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2282,39 +2282,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.0156</v>
+        <v>0.335</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>1616700</v>
+        <v>2648300</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>9.02</v>
+        <v>0.27</v>
       </c>
       <c r="H41" t="n">
-        <v>79.31</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.18</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.345</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.546</v>
+        <v>0.335</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2327,28 +2327,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0</v>
+        <v>3.23</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.0264</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1597000</v>
+        <v>2529600</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.08</v>
+        <v>0.79</v>
       </c>
       <c r="H42" t="n">
-        <v>54.55</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.309</v>
+        <v>2.869</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.301</v>
+        <v>2.456</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2372,28 +2372,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.425</v>
+        <v>0.445</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-0.023</v>
+        <v>-0.022</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>1418300</v>
+        <v>2501500</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.2</v>
+        <v>0.11</v>
       </c>
       <c r="H43" t="n">
-        <v>51</v>
+        <v>26.4</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.425</v>
+        <v>0.501</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.416</v>
+        <v>0.665</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2417,28 +2417,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.215</v>
+        <v>0.425</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>-0.0227</v>
+        <v>-0.0116</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>1383900</v>
+        <v>2488900</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>1.84</v>
+        <v>0.12</v>
       </c>
       <c r="H44" t="n">
-        <v>42.03</v>
+        <v>53.34</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2446,10 +2446,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.223</v>
+        <v>0.423</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.232</v>
+        <v>0.37</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2462,28 +2462,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.25</v>
+        <v>0.465</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>-0.0385</v>
+        <v>-0.0312</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>1362500</v>
+        <v>2278700</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="H45" t="n">
-        <v>38.79</v>
+        <v>35.11</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2491,10 +2491,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.271</v>
+        <v>0.503</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.292</v>
+        <v>0.523</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2507,39 +2507,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="E46" s="3" t="n">
-        <v>-0.0208</v>
+        <v>1.28</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1359500</v>
+        <v>2262400</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="H46" t="n">
-        <v>20.99</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.51</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.666</v>
+        <v>1.206</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.931</v>
+        <v>1.192</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2552,28 +2552,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>1328800</v>
+        <v>2146700</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.09</v>
+        <v>0.26</v>
       </c>
       <c r="H47" t="n">
-        <v>31.92</v>
+        <v>33.4</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.233</v>
+        <v>0.275</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.282</v>
+        <v>0.3</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2597,39 +2597,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.865</v>
+        <v>0.93</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0653</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1327400</v>
+        <v>2020600</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.49</v>
       </c>
       <c r="H48" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.8</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.868</v>
+        <v>0.849</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.869</v>
+        <v>0.586</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2642,28 +2642,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>-0.0092</v>
+        <v>7.18</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0.0042</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1311800</v>
+        <v>1998900</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.25</v>
+        <v>0.12</v>
       </c>
       <c r="H49" t="n">
-        <v>47.65</v>
+        <v>34.58</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.5580000000000001</v>
+        <v>7.474</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.518</v>
+        <v>7.672</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2687,28 +2687,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.41</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>1282100</v>
+        <v>1839600</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="H50" t="n">
-        <v>63.52</v>
+        <v>55.66</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -2716,10 +2716,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.207</v>
+        <v>0.393</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1.192</v>
+        <v>0.362</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2732,28 +2732,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.86</v>
+        <v>0.21</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>-0.0115</v>
+        <v>-0.0233</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1274700</v>
+        <v>1820800</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.17</v>
+        <v>0.12</v>
       </c>
       <c r="H51" t="n">
-        <v>42.14</v>
+        <v>30.1</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.921</v>
+        <v>0.232</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.85</v>
+        <v>0.282</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2777,28 +2777,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0</v>
+        <v>0.225</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.04650000000000001</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1239300</v>
+        <v>1819400</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="H52" t="n">
-        <v>55.75</v>
+        <v>75.44</v>
       </c>
       <c r="I52" s="9" t="inlineStr">
         <is>
@@ -2806,10 +2806,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.276</v>
+        <v>0.209</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.268</v>
+        <v>0.21</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2822,39 +2822,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>7.19</v>
-      </c>
-      <c r="E53" s="8" t="n">
-        <v>0.005600000000000001</v>
+        <v>0.64</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1192500</v>
+        <v>1815600</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="H53" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.03</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7.475</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>7.672</v>
+        <v>0.546</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2867,39 +2867,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.43</v>
+        <v>2.04</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>0.0238</v>
+        <v>0.009899999999999999</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1157900</v>
+        <v>1793000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.55</v>
+        <v>0.15</v>
       </c>
       <c r="H54" t="n">
-        <v>56.24</v>
-      </c>
-      <c r="I54" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.15</v>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.418</v>
+        <v>2.137</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.433</v>
+        <v>2.236</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2912,28 +2912,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>1.62</v>
+      </c>
+      <c r="E55" s="8" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1052400</v>
+        <v>1763100</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H55" t="n">
-        <v>64.98999999999999</v>
+        <v>47.87</v>
       </c>
       <c r="I55" s="9" t="inlineStr">
         <is>
@@ -2941,10 +2941,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.795</v>
+        <v>1.623</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.773</v>
+        <v>1.689</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2957,39 +2957,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0</v>
+        <v>7.25</v>
+      </c>
+      <c r="E56" s="8" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1050400</v>
+        <v>1642100</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H56" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.59</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.771</v>
+        <v>7.435</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.772</v>
+        <v>7.919</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3002,28 +3002,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>0.855</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-0.0172</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1046600</v>
+        <v>1633300</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="H57" t="n">
-        <v>27.78</v>
+        <v>41.56</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.493</v>
+        <v>0.921</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.552</v>
+        <v>0.85</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3047,39 +3047,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.405</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1030300</v>
+        <v>1621800</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.11</v>
+        <v>0.29</v>
       </c>
       <c r="H58" t="n">
-        <v>41.34</v>
-      </c>
-      <c r="I58" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I58" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.434</v>
+        <v>0.795</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.435</v>
+        <v>0.773</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3092,39 +3092,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.585</v>
+        <v>1.43</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>-0.0168</v>
+        <v>-0.0069</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1017600</v>
+        <v>1618700</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="H59" t="n">
-        <v>67.13</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.73</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.517</v>
+        <v>1.668</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.472</v>
+        <v>1.931</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3137,28 +3137,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.23</v>
+        <v>0.43</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>-0.016</v>
+        <v>-0.0115</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>970100</v>
+        <v>1541300</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="H60" t="n">
-        <v>38.68</v>
+        <v>52.29</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.292</v>
+        <v>0.425</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1.314</v>
+        <v>0.417</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3182,28 +3182,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.535</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0183</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>962300</v>
+        <v>1463000</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>0.27</v>
       </c>
       <c r="H61" t="n">
-        <v>48.87</v>
+        <v>46.52</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3211,10 +3211,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.825</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.784</v>
+        <v>0.518</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3227,39 +3227,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>-0.008399999999999999</v>
+        <v>1.17</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>933900</v>
+        <v>1421400</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="H62" t="n">
-        <v>49.02</v>
-      </c>
-      <c r="I62" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.42</v>
+      </c>
+      <c r="I62" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.597</v>
+        <v>1.227</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.586</v>
+        <v>1.316</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3272,28 +3272,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.635</v>
+        <v>0.25</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>-0.0155</v>
+        <v>-0.0385</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>897600</v>
+        <v>1416100</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="H63" t="n">
-        <v>40.83</v>
+        <v>38.79</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3301,10 +3301,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.674</v>
+        <v>0.271</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.292</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3317,28 +3317,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.57</v>
+        <v>0.215</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.05</v>
+        <v>-0.0227</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>888200</v>
+        <v>1383900</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.15</v>
+        <v>1.84</v>
       </c>
       <c r="H64" t="n">
-        <v>53.44</v>
+        <v>42.03</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3346,10 +3346,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.57</v>
+        <v>0.223</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.473</v>
+        <v>0.232</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3362,28 +3362,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="E65" s="8" t="n">
-        <v>0.0123</v>
+        <v>1.23</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>875600</v>
+        <v>1366600</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="H65" t="n">
-        <v>54.36</v>
+        <v>38.68</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3391,10 +3391,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.448</v>
+        <v>1.292</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>2.392</v>
+        <v>1.314</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3407,39 +3407,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E66" s="8" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>846900</v>
+        <v>1273100</v>
       </c>
       <c r="G66" s="5" t="n">
         <v>0.14</v>
       </c>
       <c r="H66" t="n">
-        <v>68.05</v>
-      </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.34</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.93</v>
+        <v>0.435</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.88</v>
+        <v>0.436</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3452,39 +3452,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E67" s="3" t="n">
-        <v>-0.0258</v>
+        <v>0.28</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>841700</v>
+        <v>1239300</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.37</v>
+        <v>1.33</v>
       </c>
       <c r="H67" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.75</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.732</v>
+        <v>0.276</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.652</v>
+        <v>0.268</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3497,28 +3497,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>-0.008199999999999999</v>
+        <v>5.35</v>
+      </c>
+      <c r="E68" s="8" t="n">
+        <v>0.0171</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>827100</v>
+        <v>1232800</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="H68" t="n">
-        <v>22.97</v>
+        <v>44.39</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.375</v>
+        <v>5.493</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1.551</v>
+        <v>5.471</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3542,39 +3542,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>-0.0157</v>
+        <v>0.45</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>824000</v>
+        <v>1207600</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.37</v>
+        <v>0.16</v>
       </c>
       <c r="H69" t="n">
-        <v>44.42</v>
-      </c>
-      <c r="I69" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.78</v>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.636</v>
+        <v>0.493</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.624</v>
+        <v>0.552</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3587,39 +3587,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>-0.04</v>
+        <v>0.435</v>
+      </c>
+      <c r="E70" s="8" t="n">
+        <v>0.0357</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>811100</v>
+        <v>1205600</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
       <c r="H70" t="n">
-        <v>29.66</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.96</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>2.769</v>
+        <v>0.419</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2.879</v>
+        <v>0.433</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3632,28 +3632,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0</v>
+        <v>0.63</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>-0.0233</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>806700</v>
+        <v>1198400</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.24</v>
+        <v>0.13</v>
       </c>
       <c r="H71" t="n">
-        <v>49.45</v>
+        <v>40</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.236</v>
+        <v>0.674</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1.077</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3677,28 +3677,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.645</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.0301</v>
+        <v>0.595</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>794100</v>
+        <v>1172100</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H72" t="n">
-        <v>32.82</v>
+        <v>50.22</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3706,10 +3706,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.717</v>
+        <v>0.598</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.743</v>
+        <v>0.586</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3722,39 +3722,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>0.0248</v>
+        <v>0.51</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>792100</v>
+        <v>1165100</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="H73" t="n">
-        <v>51.56</v>
-      </c>
-      <c r="I73" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.58</v>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>1.625</v>
+        <v>0.54</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>1.69</v>
+        <v>0.569</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3767,28 +3767,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>730900</v>
+        <v>1154600</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.27</v>
+        <v>0.6</v>
       </c>
       <c r="H74" t="n">
-        <v>33.15</v>
+        <v>40.67</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.54</v>
+        <v>0.728</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.569</v>
+        <v>0.744</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3812,28 +3812,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>2.85</v>
+        <v>0.57</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>-0.0035</v>
+        <v>-0.05</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>726100</v>
+        <v>1154500</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H75" t="n">
-        <v>55.12</v>
+        <v>53.44</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>2.802</v>
+        <v>0.57</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>2.672</v>
+        <v>0.473</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3857,28 +3857,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>-0.0069</v>
+        <v>0.77</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>711900</v>
+        <v>1132500</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="H76" t="n">
-        <v>35.04</v>
+        <v>49.5</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3886,10 +3886,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.497</v>
+        <v>0.771</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1.504</v>
+        <v>0.772</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3902,39 +3902,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>3.9</v>
+        <v>0.385</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>-0.0152</v>
+        <v>-0.0128</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>707500</v>
+        <v>1110100</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.45</v>
       </c>
       <c r="H77" t="n">
-        <v>50.43</v>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.59</v>
+      </c>
+      <c r="I77" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>3.955</v>
+        <v>0.388</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>3.572</v>
+        <v>0.39</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3947,39 +3947,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>6.73</v>
-      </c>
-      <c r="E78" s="8" t="n">
-        <v>0.0075</v>
+        <v>0.585</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.0168</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>695700</v>
+        <v>1106600</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="H78" t="n">
-        <v>31.09</v>
-      </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.13</v>
+      </c>
+      <c r="I78" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>7.163</v>
+        <v>0.517</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>7.581</v>
+        <v>0.472</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3992,28 +3992,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>2.01</v>
+        <v>0.825</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>-0.005</v>
+        <v>-0.0237</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>634600</v>
+        <v>1095900</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.05</v>
+        <v>0.36</v>
       </c>
       <c r="H79" t="n">
-        <v>32.46</v>
+        <v>14.93</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4021,10 +4021,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.134</v>
+        <v>0.907</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2.235</v>
+        <v>0.969</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4037,28 +4037,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>PARADIGM</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.8</v>
+        <v>0.915</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>-0.0062</v>
+        <v>-0.0161</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>598200</v>
+        <v>1092800</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>1.56</v>
+        <v>0.27</v>
       </c>
       <c r="H80" t="n">
-        <v>25.89</v>
+        <v>23.81</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4066,10 +4066,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.819</v>
+        <v>0.965</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.848</v>
+        <v>1.049</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4082,28 +4082,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>3</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>-0.0066</v>
+        <v>-0.0121</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>595300</v>
+        <v>1085800</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.2</v>
+        <v>0.31</v>
       </c>
       <c r="H81" t="n">
-        <v>50.71</v>
+        <v>49.71</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4111,10 +4111,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>3.025</v>
+        <v>0.825</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>2.859</v>
+        <v>0.785</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4127,28 +4127,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E82" s="3" t="n">
-        <v>-0.0315</v>
+        <v>2.46</v>
+      </c>
+      <c r="E82" s="8" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>585000</v>
+        <v>1059300</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.19</v>
+        <v>0.09</v>
       </c>
       <c r="H82" t="n">
-        <v>46.57</v>
+        <v>53.17</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4156,10 +4156,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.282</v>
+        <v>2.447</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>1.228</v>
+        <v>2.392</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4172,39 +4172,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E83" s="3" t="n">
-        <v>-0.0227</v>
+        <v>2.1</v>
+      </c>
+      <c r="E83" s="8" t="n">
+        <v>0.009599999999999999</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>581500</v>
+        <v>1056000</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.24</v>
+        <v>0.06</v>
       </c>
       <c r="H83" t="n">
-        <v>54.96</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.3</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>1.264</v>
+        <v>2.106</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>1.176</v>
+        <v>2.103</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4217,39 +4217,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0261</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.4</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-0.0361</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>576900</v>
+        <v>1026700</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.23</v>
+        <v>2.16</v>
       </c>
       <c r="H84" t="n">
-        <v>57.68</v>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.07</v>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.74</v>
+        <v>0.384</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.705</v>
+        <v>0.365</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4262,28 +4262,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>4.8</v>
+        <v>1.07</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>-0.0103</v>
+        <v>-0.0183</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>568900</v>
+        <v>986100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.02</v>
+        <v>0.11</v>
       </c>
       <c r="H85" t="n">
-        <v>46.11</v>
+        <v>49.53</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4291,10 +4291,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>4.893</v>
+        <v>1.077</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>4.736</v>
+        <v>1.047</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4307,28 +4307,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1.1</v>
+        <v>0.865</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.009000000000000001</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>556500</v>
+        <v>978000</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.14</v>
+        <v>0.32</v>
       </c>
       <c r="H86" t="n">
-        <v>43.24</v>
+        <v>51.48</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4336,10 +4336,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.15</v>
+        <v>0.865</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1.103</v>
+        <v>0.86</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4352,39 +4352,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E87" s="8" t="n">
-        <v>0.008500000000000001</v>
+        <v>1.42</v>
+      </c>
+      <c r="E87" s="3" t="n">
+        <v>-0.0207</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>552100</v>
+        <v>970700</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="H87" t="n">
-        <v>38.44</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.08</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.228</v>
+        <v>1.495</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1.316</v>
+        <v>1.503</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4397,39 +4397,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>6.51</v>
+        <v>1.21</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>-0.0061</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>538000</v>
+        <v>967200</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.09</v>
+        <v>0.22</v>
       </c>
       <c r="H88" t="n">
-        <v>56.99</v>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.97</v>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>6.209</v>
+        <v>1.375</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>5.931</v>
+        <v>1.551</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4442,28 +4442,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1.17</v>
+        <v>2.42</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.032</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>511400</v>
+        <v>963400</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H89" t="n">
-        <v>50.89</v>
+        <v>30.24</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>1.17</v>
+        <v>2.771</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1.139</v>
+        <v>2.88</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4487,28 +4487,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="E90" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>3.96</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>508100</v>
+        <v>906700</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H90" t="n">
-        <v>43.57</v>
+        <v>52.54</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4516,10 +4516,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.601</v>
+        <v>3.96</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>2.61</v>
+        <v>3.573</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4532,39 +4532,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.2</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>502900</v>
+        <v>890800</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H91" t="n">
-        <v>60.34</v>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.45</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>2.233</v>
+        <v>1.236</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>2.175</v>
+        <v>1.077</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4577,28 +4577,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0</v>
+        <v>0.76</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>-0.0194</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>501300</v>
+        <v>886700</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="H92" t="n">
-        <v>40.19</v>
+        <v>62.26</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4606,16 +4606,1276 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.364</v>
+        <v>0.733</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1.342</v>
+        <v>0.652</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
     </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0167</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>MCLEAN</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>-0.03759999999999999</v>
+      </c>
+      <c r="F93" s="4" t="n">
+        <v>881400</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H93" t="n">
+        <v>32.17</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>0.716</v>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0.743</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>0.975</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>867600</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H94" t="n">
+        <v>68.05</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="F95" s="4" t="n">
+        <v>849100</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H95" t="n">
+        <v>55.12</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>2.802</v>
+      </c>
+      <c r="K95" s="2" t="n">
+        <v>2.672</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0112</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>MIKROMB</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F96" s="4" t="n">
+        <v>841600</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H96" t="n">
+        <v>47.44</v>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K96" s="2" t="n">
+        <v>0.624</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>5271</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>PECCA</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="4" t="n">
+        <v>796900</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H97" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>1.364</v>
+      </c>
+      <c r="K97" s="2" t="n">
+        <v>1.342</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>3336</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>IJM</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="E98" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="4" t="n">
+        <v>794600</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H98" t="n">
+        <v>44.85</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>2.755</v>
+      </c>
+      <c r="K98" s="2" t="n">
+        <v>2.741</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>6.74</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F99" s="4" t="n">
+        <v>787500</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H99" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>7.164</v>
+      </c>
+      <c r="K99" s="2" t="n">
+        <v>7.582</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>6.53</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="F100" s="4" t="n">
+        <v>763900</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H100" t="n">
+        <v>57.37</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>6.211</v>
+      </c>
+      <c r="K100" s="2" t="n">
+        <v>5.932</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="4" t="n">
+        <v>735100</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H101" t="n">
+        <v>58.81</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="K101" s="2" t="n">
+        <v>0.923</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>4.81</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>-0.008199999999999999</v>
+      </c>
+      <c r="F102" s="4" t="n">
+        <v>729500</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H102" t="n">
+        <v>46.62</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>4.894</v>
+      </c>
+      <c r="K102" s="2" t="n">
+        <v>4.736</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E103" s="8" t="n">
+        <v>0.0051</v>
+      </c>
+      <c r="F103" s="4" t="n">
+        <v>710800</v>
+      </c>
+      <c r="G103" s="5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H103" t="n">
+        <v>44.98</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>9.996</v>
+      </c>
+      <c r="K103" s="2" t="n">
+        <v>10.137</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.0049</v>
+      </c>
+      <c r="F104" s="4" t="n">
+        <v>706400</v>
+      </c>
+      <c r="G104" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H104" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>2.042</v>
+      </c>
+      <c r="K104" s="2" t="n">
+        <v>2.069</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.0236</v>
+      </c>
+      <c r="F105" s="4" t="n">
+        <v>704300</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H105" t="n">
+        <v>47.31</v>
+      </c>
+      <c r="I105" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="K105" s="2" t="n">
+        <v>1.228</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F106" s="4" t="n">
+        <v>678300</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H106" t="n">
+        <v>54.96</v>
+      </c>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="K106" s="2" t="n">
+        <v>1.176</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="F107" s="4" t="n">
+        <v>655900</v>
+      </c>
+      <c r="G107" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H107" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="K107" s="2" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F108" s="4" t="n">
+        <v>650000</v>
+      </c>
+      <c r="G108" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H108" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="K108" s="2" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F109" s="4" t="n">
+        <v>640600</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H109" t="n">
+        <v>27.95</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>5.872</v>
+      </c>
+      <c r="K109" s="2" t="n">
+        <v>6.163</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E110" s="8" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F110" s="4" t="n">
+        <v>627100</v>
+      </c>
+      <c r="G110" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H110" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>1.152</v>
+      </c>
+      <c r="K110" s="2" t="n">
+        <v>1.103</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="F111" s="4" t="n">
+        <v>608000</v>
+      </c>
+      <c r="G111" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H111" t="n">
+        <v>59.64</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>2.232</v>
+      </c>
+      <c r="K111" s="2" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F112" s="4" t="n">
+        <v>607200</v>
+      </c>
+      <c r="G112" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H112" t="n">
+        <v>48.34</v>
+      </c>
+      <c r="I112" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>3.844</v>
+      </c>
+      <c r="K112" s="2" t="n">
+        <v>3.699</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5338</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>PARADIGM</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F113" s="4" t="n">
+        <v>603200</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="H113" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K113" s="2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="E114" s="8" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F114" s="4" t="n">
+        <v>581000</v>
+      </c>
+      <c r="G114" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H114" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>4.363</v>
+      </c>
+      <c r="K114" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F115" s="4" t="n">
+        <v>572600</v>
+      </c>
+      <c r="G115" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H115" t="n">
+        <v>55.77</v>
+      </c>
+      <c r="I115" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>0.647</v>
+      </c>
+      <c r="K115" s="2" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F116" s="4" t="n">
+        <v>571300</v>
+      </c>
+      <c r="G116" s="5" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H116" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="K116" s="2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F117" s="4" t="n">
+        <v>559200</v>
+      </c>
+      <c r="G117" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H117" t="n">
+        <v>50.89</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="K117" s="2" t="n">
+        <v>1.139</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F118" s="4" t="n">
+        <v>510900</v>
+      </c>
+      <c r="G118" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H118" t="n">
+        <v>44.34</v>
+      </c>
+      <c r="I118" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>2.602</v>
+      </c>
+      <c r="K118" s="2" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="F119" s="4" t="n">
+        <v>503400</v>
+      </c>
+      <c r="G119" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H119" t="n">
+        <v>51.15</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="K119" s="2" t="n">
+        <v>0.679</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="F120" s="4" t="n">
+        <v>500800</v>
+      </c>
+      <c r="G120" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H120" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="I120" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="K120" s="2" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M92"/>
+  <autoFilter ref="A1:M120"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
+++ b/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-20" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$120</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.0294</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>39038200</v>
+        <v>39822800</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="H2" t="n">
         <v>63.6</v>
@@ -603,7 +603,7 @@
         <v>0.0562</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>30125400</v>
+        <v>30297300</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>0.87</v>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="E4" s="8" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>19957600</v>
+        <v>25283500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>24.48</v>
+        <v>22.63</v>
       </c>
       <c r="I4" s="6" t="inlineStr">
         <is>
@@ -678,28 +678,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0.0217</v>
+        <v>0.88</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>-0.0112</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>17158800</v>
+        <v>20940600</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.68</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="n">
-        <v>80.01000000000001</v>
+        <v>62.03</v>
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
@@ -707,10 +707,10 @@
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.626</v>
+        <v>0.832</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.537</v>
+        <v>0.741</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -723,28 +723,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>-0.0112</v>
+        <v>0.705</v>
+      </c>
+      <c r="E6" s="8" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>14946200</v>
+        <v>17362300</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.21</v>
+        <v>0.68</v>
       </c>
       <c r="H6" t="n">
-        <v>62.03</v>
+        <v>80.01000000000001</v>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
@@ -752,10 +752,10 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.832</v>
+        <v>0.626</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.741</v>
+        <v>0.537</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,28 +768,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="E7" s="8" t="n">
-        <v>0.09720000000000001</v>
+        <v>1.47</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>-0.08699999999999999</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>13559500</v>
+        <v>17152100</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.47</v>
+        <v>3.42</v>
       </c>
       <c r="H7" t="n">
-        <v>27.6</v>
+        <v>24.38</v>
       </c>
       <c r="I7" s="6" t="inlineStr">
         <is>
@@ -797,10 +797,10 @@
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.51</v>
+        <v>1.698</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.607</v>
+        <v>1.76</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,28 +813,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>-0.0784</v>
+        <v>0.395</v>
+      </c>
+      <c r="E8" s="8" t="n">
+        <v>0.09720000000000001</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>11814600</v>
+        <v>14822900</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.06</v>
+        <v>1.61</v>
       </c>
       <c r="H8" t="n">
-        <v>43.16</v>
+        <v>27.6</v>
       </c>
       <c r="I8" s="6" t="inlineStr">
         <is>
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.515</v>
+        <v>0.51</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.463</v>
+        <v>0.607</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -858,28 +858,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.265</v>
+        <v>0.455</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.0364</v>
+        <v>-0.1078</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10549100</v>
+        <v>14668500</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.07</v>
+        <v>1.31</v>
       </c>
       <c r="H9" t="n">
-        <v>38.24</v>
+        <v>40.96</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.295</v>
+        <v>0.513</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.28</v>
+        <v>0.463</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,28 +903,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.385</v>
+        <v>0.265</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>-0.0128</v>
+        <v>-0.0364</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>9505300</v>
+        <v>11779200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.95</v>
+        <v>1.2</v>
       </c>
       <c r="H10" t="n">
-        <v>28.49</v>
+        <v>38.24</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.396</v>
+        <v>0.295</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.406</v>
+        <v>0.28</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,33 +948,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.245</v>
+        <v>0.385</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.02</v>
+        <v>-0.0128</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>9170000</v>
+        <v>10471200</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.39</v>
+        <v>1.05</v>
+      </c>
+      <c r="H11" t="n">
+        <v>28.49</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+      <c r="J11" s="2" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.406</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -986,40 +993,33 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>-0.04969999999999999</v>
+        <v>0.25</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>8606600</v>
+        <v>9375000</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="H12" t="n">
-        <v>27.62</v>
+        <v>0.4</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>1.703</v>
-      </c>
-      <c r="K12" s="2" t="n">
-        <v>1.762</v>
-      </c>
+      <c r="J12" s="2" t="n"/>
+      <c r="K12" s="2" t="n"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1040,19 +1040,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.38</v>
+        <v>0.385</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.0411</v>
+        <v>0.0548</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>7839400</v>
+        <v>8467100</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="H13" t="n">
-        <v>67.44</v>
+        <v>68.34</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1060,7 +1060,7 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.325</v>
+        <v>0.326</v>
       </c>
       <c r="K13" s="2" t="n"/>
       <c r="L13" t="inlineStr"/>
@@ -1083,19 +1083,19 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-0.0115</v>
+        <v>0.435</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>7795300</v>
+        <v>8271800</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H14" t="n">
-        <v>35.32</v>
+        <v>36.45</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1164,33 +1164,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.735</v>
+        <v>2.02</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>-0.0265</v>
+        <v>-0.0146</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6694300</v>
+        <v>7255500</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+        <v>0.25</v>
+      </c>
+      <c r="H16" t="n">
+        <v>58.58</v>
+      </c>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1.941</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1.754</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
     </row>
@@ -1202,40 +1209,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>PUNCAK</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>0.0256</v>
+        <v>0.745</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>6258400</v>
+        <v>7234600</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>16.43</v>
-      </c>
-      <c r="H17" t="n">
-        <v>82.42</v>
-      </c>
-      <c r="I17" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>0.177</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>0.171</v>
-      </c>
+        <v>0.12</v>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1247,39 +1247,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2.03</v>
+        <v>0.205</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-0.0098</v>
+        <v>-0.0238</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>5956500</v>
+        <v>7018500</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.21</v>
+        <v>0.31</v>
       </c>
       <c r="H18" t="n">
-        <v>59.32</v>
-      </c>
-      <c r="I18" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.25</v>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>1.942</v>
+        <v>0.217</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>1.754</v>
+        <v>0.234</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1292,39 +1292,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0</v>
+        <v>0.305</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5876400</v>
+        <v>6527600</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.93</v>
+        <v>0.34</v>
       </c>
       <c r="H19" t="n">
-        <v>36.95</v>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.44</v>
+      </c>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.313</v>
+        <v>0.308</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.334</v>
+        <v>0.301</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1337,39 +1337,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.54</v>
+        <v>0.82</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0061</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>5675400</v>
+        <v>6412400</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="H20" t="n">
-        <v>45.28</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.61</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.57</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0.543</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
@@ -1382,28 +1382,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>PUNCAK</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0</v>
+        <v>0.2</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>5620500</v>
+        <v>6339400</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.37</v>
+        <v>16.64</v>
       </c>
       <c r="H21" t="n">
-        <v>49.91</v>
+        <v>82.42</v>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
@@ -1411,10 +1411,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.775</v>
+        <v>0.177</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.776</v>
+        <v>0.171</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1427,39 +1427,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>2.54</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.0193</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>5263000</v>
+        <v>6235000</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="H22" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="I22" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.11</v>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.309</v>
+        <v>2.634</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.301</v>
+        <v>2.556</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1472,28 +1472,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.205</v>
+        <v>0.285</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>-0.0238</v>
+        <v>-0.0172</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>4851100</v>
+        <v>6123600</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.22</v>
+        <v>0.97</v>
       </c>
       <c r="H23" t="n">
-        <v>40.25</v>
+        <v>35.29</v>
       </c>
       <c r="I23" s="6" t="inlineStr">
         <is>
@@ -1501,10 +1501,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.217</v>
+        <v>0.312</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.234</v>
+        <v>0.334</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1517,39 +1517,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.175</v>
+        <v>0.775</v>
       </c>
       <c r="E24" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>4750000</v>
+        <v>6117000</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.21</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="n">
-        <v>40.18</v>
-      </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.91</v>
+      </c>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.188</v>
+        <v>0.775</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.185</v>
+        <v>0.776</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1562,28 +1562,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E25" s="8" t="n">
-        <v>0.0294</v>
+        <v>0.53</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>-0.0364</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>4677400</v>
+        <v>5967300</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.9</v>
+        <v>0.29</v>
       </c>
       <c r="H25" t="n">
-        <v>48.66</v>
+        <v>43.63</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.174</v>
+        <v>0.569</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.181</v>
+        <v>0.542</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1622,10 +1622,10 @@
         <v>-0.0251</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>4501500</v>
+        <v>5349700</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H26" t="n">
         <v>41.14</v>
@@ -1652,28 +1652,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.82</v>
+        <v>0.865</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.0061</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>4487600</v>
+        <v>5345600</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="H27" t="n">
-        <v>55.61</v>
+        <v>46.09</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -1681,10 +1681,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.868</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.869</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1697,28 +1697,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E28" s="8" t="n">
-        <v>0.0247</v>
+        <v>0.435</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>-0.044</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>4162200</v>
+        <v>5242100</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="H28" t="n">
-        <v>57.67</v>
+        <v>25.17</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.394</v>
+        <v>0.5</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.379</v>
+        <v>0.665</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>4139800</v>
+        <v>5230900</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="H29" t="n">
         <v>59.52</v>
@@ -1787,40 +1787,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2.57</v>
+        <v>0.11</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-0.0077</v>
+        <v>-0.0833</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3726600</v>
+        <v>5143200</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H30" t="n">
-        <v>46.76</v>
+        <v>0.13</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n">
-        <v>2.637</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>2.556</v>
-      </c>
+      <c r="J30" s="2" t="n"/>
+      <c r="K30" s="2" t="n"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
     </row>
@@ -1832,28 +1825,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.125</v>
+        <v>0.175</v>
       </c>
       <c r="E31" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0294</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3489700</v>
+        <v>5092000</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.36</v>
+        <v>0.98</v>
       </c>
       <c r="H31" t="n">
-        <v>53.06</v>
+        <v>48.66</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1861,10 +1854,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.126</v>
+        <v>0.174</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.102</v>
+        <v>0.181</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1877,28 +1870,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E32" s="3" t="n">
-        <v>-0.0357</v>
+        <v>0.415</v>
+      </c>
+      <c r="E32" s="8" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>3422100</v>
+        <v>4931700</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.05</v>
+        <v>0.4</v>
       </c>
       <c r="H32" t="n">
-        <v>40.16</v>
+        <v>57.67</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1906,10 +1899,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.157</v>
+        <v>0.394</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.141</v>
+        <v>0.379</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1922,28 +1915,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="E33" s="3" t="n">
-        <v>-0.0552</v>
+        <v>0.175</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>3384200</v>
+        <v>4875000</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.66</v>
+        <v>0.22</v>
       </c>
       <c r="H33" t="n">
-        <v>40.68</v>
+        <v>40.18</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1951,10 +1944,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.753</v>
+        <v>0.188</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.185</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1967,28 +1960,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.545</v>
+        <v>0.655</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>-0.0268</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>3372900</v>
+        <v>4586500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.37</v>
+        <v>0.89</v>
       </c>
       <c r="H34" t="n">
-        <v>33.38</v>
+        <v>37.19</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1996,10 +1989,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.637</v>
+        <v>0.75</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.619</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2012,39 +2005,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-0.0541</v>
+        <v>0.38</v>
+      </c>
+      <c r="E35" s="8" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>3316100</v>
+        <v>4448200</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="H35" t="n">
-        <v>24.82</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.65</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.197</v>
+        <v>0.372</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.207</v>
+        <v>0.369</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2057,39 +2050,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>4.74</v>
+        <v>0.125</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.0064</v>
+        <v>0.0417</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>3238700</v>
+        <v>4352900</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.16</v>
+        <v>0.45</v>
       </c>
       <c r="H36" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="I36" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.06</v>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4.729</v>
+        <v>0.126</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>4.84</v>
+        <v>0.102</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2102,39 +2095,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>3.81</v>
+        <v>0.425</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0116</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>3219100</v>
+        <v>4246300</v>
       </c>
       <c r="G37" s="5" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H37" t="n">
+        <v>53.34</v>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>0.423</v>
+      </c>
+      <c r="K37" s="2" t="n">
         <v>0.37</v>
-      </c>
-      <c r="H37" t="n">
-        <v>57.75</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>3.667</v>
-      </c>
-      <c r="K37" s="2" t="n">
-        <v>3.055</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2156,19 +2149,19 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>-0.0143</v>
+        <v>-0.0286</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>3179400</v>
+        <v>4138800</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.41</v>
+        <v>0.54</v>
       </c>
       <c r="H38" t="n">
-        <v>48.17</v>
+        <v>46.04</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2176,7 +2169,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0.328</v>
@@ -2192,39 +2185,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0.0133</v>
+        <v>0.54</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2784200</v>
+        <v>3831200</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.38</v>
+        <v>0.42</v>
       </c>
       <c r="H39" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.82</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.372</v>
+        <v>0.636</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.369</v>
+        <v>0.619</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2237,28 +2230,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E40" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>4.73</v>
+      </c>
+      <c r="E40" s="8" t="n">
+        <v>0.0042</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>2751400</v>
+        <v>3566600</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H40" t="n">
-        <v>46.09</v>
+        <v>48.55</v>
       </c>
       <c r="I40" s="9" t="inlineStr">
         <is>
@@ -2266,10 +2259,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.868</v>
+        <v>4.729</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.869</v>
+        <v>4.84</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2282,28 +2275,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>-0.0147</v>
+        <v>0.14</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2648300</v>
+        <v>3501400</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.27</v>
+        <v>0.05</v>
       </c>
       <c r="H41" t="n">
-        <v>47.18</v>
+        <v>42.14</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2311,10 +2304,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.345</v>
+        <v>0.157</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.335</v>
+        <v>0.141</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2327,39 +2320,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0.0264</v>
+        <v>3.82</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>2529600</v>
+        <v>3474700</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.79</v>
+        <v>0.4</v>
       </c>
       <c r="H42" t="n">
-        <v>85.70999999999999</v>
-      </c>
-      <c r="I42" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.09</v>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>2.869</v>
+        <v>3.668</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>2.456</v>
+        <v>3.055</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2372,28 +2365,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.445</v>
+        <v>0.335</v>
       </c>
       <c r="E43" s="3" t="n">
-        <v>-0.022</v>
+        <v>-0.0147</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2501500</v>
+        <v>3356500</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.11</v>
+        <v>0.35</v>
       </c>
       <c r="H43" t="n">
-        <v>26.4</v>
+        <v>47.18</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2401,10 +2394,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.501</v>
+        <v>0.345</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.665</v>
+        <v>0.335</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2417,28 +2410,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.425</v>
+        <v>0.175</v>
       </c>
       <c r="E44" s="3" t="n">
-        <v>-0.0116</v>
+        <v>-0.0541</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>2488900</v>
+        <v>3349000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.12</v>
+        <v>0.82</v>
       </c>
       <c r="H44" t="n">
-        <v>53.34</v>
+        <v>24.82</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2446,10 +2439,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.423</v>
+        <v>0.197</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.37</v>
+        <v>0.207</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2462,28 +2455,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.465</v>
+        <v>0.275</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>-0.0312</v>
+        <v>-0.0179</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>2278700</v>
+        <v>3266900</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H45" t="n">
-        <v>35.11</v>
+        <v>44.46</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2491,10 +2484,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.503</v>
+        <v>0.289</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.523</v>
+        <v>0.283</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2507,39 +2500,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0</v>
+        <v>2.03</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0.005</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2262400</v>
+        <v>2919800</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.36</v>
+        <v>0.24</v>
       </c>
       <c r="H46" t="n">
-        <v>62.51</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.71</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.206</v>
+        <v>2.136</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.192</v>
+        <v>2.236</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2552,28 +2545,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0.0196</v>
+        <v>2.02</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2146700</v>
+        <v>2774200</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.26</v>
+        <v>0.84</v>
       </c>
       <c r="H47" t="n">
-        <v>33.4</v>
+        <v>44.31</v>
       </c>
       <c r="I47" s="6" t="inlineStr">
         <is>
@@ -2581,10 +2574,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>0.275</v>
+        <v>2.042</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0.3</v>
+        <v>2.069</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2597,28 +2590,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.93</v>
+        <v>0.42</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>-0.0653</v>
+        <v>-0.0345</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2020600</v>
+        <v>2638900</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.49</v>
+        <v>0.38</v>
       </c>
       <c r="H48" t="n">
-        <v>59.8</v>
+        <v>49.76</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2626,10 +2619,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.849</v>
+        <v>0.424</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.586</v>
+        <v>0.416</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2642,39 +2635,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>7.18</v>
+        <v>1.62</v>
       </c>
       <c r="E49" s="8" t="n">
-        <v>0.0042</v>
+        <v>0.0062</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>1998900</v>
+        <v>2584000</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.12</v>
+        <v>0.35</v>
       </c>
       <c r="H49" t="n">
-        <v>34.58</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.87</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>7.474</v>
+        <v>1.623</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>7.672</v>
+        <v>1.689</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2687,28 +2680,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>2562300</v>
+      </c>
+      <c r="G50" s="5" t="n">
         <v>0.41</v>
       </c>
-      <c r="E50" s="3" t="n">
-        <v>-0.04650000000000001</v>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>1839600</v>
-      </c>
-      <c r="G50" s="5" t="n">
-        <v>0.32</v>
-      </c>
       <c r="H50" t="n">
-        <v>55.66</v>
+        <v>62.51</v>
       </c>
       <c r="I50" s="9" t="inlineStr">
         <is>
@@ -2716,10 +2709,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.393</v>
+        <v>1.206</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.362</v>
+        <v>1.192</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2732,39 +2725,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E51" s="3" t="n">
-        <v>-0.0233</v>
+        <v>3.23</v>
+      </c>
+      <c r="E51" s="8" t="n">
+        <v>0.0264</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>1820800</v>
+        <v>2559200</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.12</v>
+        <v>0.8</v>
       </c>
       <c r="H51" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="I51" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.232</v>
+        <v>2.869</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.282</v>
+        <v>2.456</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2777,39 +2770,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.84</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>1819400</v>
+        <v>2552600</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>1.79</v>
+        <v>0.34</v>
       </c>
       <c r="H52" t="n">
-        <v>75.44</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.9</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.209</v>
+        <v>0.919</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.21</v>
+        <v>0.85</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2822,39 +2815,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.07539999999999999</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>1815600</v>
+        <v>2521900</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>10.13</v>
+        <v>0.62</v>
       </c>
       <c r="H53" t="n">
-        <v>78.03</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.05</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.848</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.546</v>
+        <v>0.586</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2867,28 +2860,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>2.04</v>
+        <v>7.18</v>
       </c>
       <c r="E54" s="8" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.0042</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>1793000</v>
+        <v>2348200</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H54" t="n">
-        <v>36.15</v>
+        <v>34.58</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2896,10 +2889,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>2.137</v>
+        <v>7.474</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>2.236</v>
+        <v>7.672</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2912,39 +2905,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E55" s="8" t="n">
-        <v>0.0062</v>
+        <v>0.47</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>1763100</v>
+        <v>2299700</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="H55" t="n">
-        <v>47.87</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.31</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>1.623</v>
+        <v>0.503</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>1.689</v>
+        <v>0.523</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2957,39 +2950,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="E56" s="8" t="n">
-        <v>0.0069</v>
+        <v>1.42</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>-0.0139</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>1642100</v>
+        <v>2291000</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H56" t="n">
-        <v>34.59</v>
-      </c>
-      <c r="I56" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.35</v>
+      </c>
+      <c r="I56" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>7.435</v>
+        <v>1.667</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>7.919</v>
+        <v>1.931</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -3002,39 +2995,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.855</v>
+        <v>0.41</v>
       </c>
       <c r="E57" s="3" t="n">
-        <v>-0.0172</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>1633300</v>
+        <v>2261100</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.22</v>
+        <v>0.4</v>
       </c>
       <c r="H57" t="n">
-        <v>41.56</v>
-      </c>
-      <c r="I57" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.66</v>
+      </c>
+      <c r="I57" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.921</v>
+        <v>0.393</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.85</v>
+        <v>0.362</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3047,39 +3040,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.255</v>
       </c>
       <c r="E58" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>1621800</v>
+        <v>2239000</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="H58" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I58" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.74</v>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.795</v>
+        <v>0.274</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.773</v>
+        <v>0.3</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3092,39 +3085,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.43</v>
+        <v>1.16</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>-0.0069</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>1618700</v>
+        <v>2212000</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="H59" t="n">
-        <v>21.73</v>
-      </c>
-      <c r="I59" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.26</v>
+      </c>
+      <c r="I59" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.668</v>
+        <v>1.226</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.931</v>
+        <v>1.316</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3137,28 +3130,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.43</v>
+        <v>1.22</v>
       </c>
       <c r="E60" s="3" t="n">
-        <v>-0.0115</v>
+        <v>-0.024</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>1541300</v>
+        <v>2200200</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="H60" t="n">
-        <v>52.29</v>
+        <v>37.52</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3166,10 +3159,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.425</v>
+        <v>1.291</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.417</v>
+        <v>1.314</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3182,39 +3175,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E61" s="3" t="n">
-        <v>-0.0183</v>
+        <v>7.25</v>
+      </c>
+      <c r="E61" s="8" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>1463000</v>
+        <v>2071700</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="H61" t="n">
-        <v>46.52</v>
-      </c>
-      <c r="I61" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>34.59</v>
+      </c>
+      <c r="I61" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.5580000000000001</v>
+        <v>7.435</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.518</v>
+        <v>7.919</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3227,39 +3220,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0</v>
+        <v>5.34</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>1421400</v>
+        <v>2069300</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H62" t="n">
-        <v>36.42</v>
-      </c>
-      <c r="I62" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.98</v>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>1.227</v>
+        <v>5.492</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.316</v>
+        <v>5.471</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3272,28 +3265,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.25</v>
+        <v>0.21</v>
       </c>
       <c r="E63" s="3" t="n">
-        <v>-0.0385</v>
+        <v>-0.0233</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>1416100</v>
+        <v>2021800</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="H63" t="n">
-        <v>38.79</v>
+        <v>30.1</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3301,10 +3294,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.271</v>
+        <v>0.232</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.292</v>
+        <v>0.282</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3317,28 +3310,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.215</v>
+        <v>0.91</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.0227</v>
+        <v>-0.0215</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>1383900</v>
+        <v>2015200</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>1.84</v>
+        <v>0.5</v>
       </c>
       <c r="H64" t="n">
-        <v>42.03</v>
+        <v>22.95</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3346,10 +3339,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.223</v>
+        <v>0.964</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.232</v>
+        <v>1.048</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3362,39 +3355,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1.23</v>
+        <v>0.615</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.016</v>
+        <v>-0.0391</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>1366600</v>
+        <v>2012300</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.16</v>
+        <v>11.22</v>
       </c>
       <c r="H65" t="n">
-        <v>38.68</v>
-      </c>
-      <c r="I65" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.55</v>
+      </c>
+      <c r="I65" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.292</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1.314</v>
+        <v>0.546</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3407,39 +3400,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.415</v>
+        <v>0.82</v>
       </c>
       <c r="E66" s="8" t="n">
-        <v>0.0247</v>
+        <v>0.0061</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1273100</v>
+        <v>1995300</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="H66" t="n">
-        <v>44.34</v>
-      </c>
-      <c r="I66" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>66.83</v>
+      </c>
+      <c r="I66" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.435</v>
+        <v>0.796</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.436</v>
+        <v>0.773</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3452,39 +3445,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E67" s="10" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1239300</v>
+        <v>1877600</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1.33</v>
+        <v>1.52</v>
       </c>
       <c r="H67" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.83</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.276</v>
+        <v>0.749</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.268</v>
+        <v>0.721</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3497,39 +3490,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>5.35</v>
+        <v>0.225</v>
       </c>
       <c r="E68" s="8" t="n">
-        <v>0.0171</v>
+        <v>0.04650000000000001</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1232800</v>
+        <v>1824400</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.09</v>
+        <v>1.79</v>
       </c>
       <c r="H68" t="n">
-        <v>44.39</v>
-      </c>
-      <c r="I68" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.44</v>
+      </c>
+      <c r="I68" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>5.493</v>
+        <v>0.209</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>5.471</v>
+        <v>0.21</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3542,28 +3535,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-0.0275</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1207600</v>
+        <v>1789400</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="H69" t="n">
-        <v>27.78</v>
+        <v>45.45</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3571,10 +3564,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.493</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.552</v>
+        <v>0.518</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3587,39 +3580,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E70" s="8" t="n">
-        <v>0.0357</v>
+        <v>0.865</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1205600</v>
+        <v>1763000</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="H70" t="n">
-        <v>58.96</v>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.48</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.419</v>
+        <v>0.865</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.433</v>
+        <v>0.86</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3632,28 +3625,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>-0.0233</v>
+        <v>0.77</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1198400</v>
+        <v>1548200</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H71" t="n">
-        <v>40</v>
+        <v>49.5</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3661,10 +3654,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.674</v>
+        <v>0.771</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.772</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3677,28 +3670,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.595</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>-0.0667</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1172100</v>
+        <v>1530700</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H72" t="n">
-        <v>50.22</v>
+        <v>52.01</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3706,10 +3699,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.598</v>
+        <v>0.569</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.586</v>
+        <v>0.473</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3722,28 +3715,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>-0.0097</v>
+        <v>2.7</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.0037</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1165100</v>
+        <v>1512500</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.44</v>
+        <v>0.12</v>
       </c>
       <c r="H73" t="n">
-        <v>31.58</v>
+        <v>45.7</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3751,10 +3744,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.54</v>
+        <v>2.756</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.569</v>
+        <v>2.741</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3767,39 +3760,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E74" s="3" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.44</v>
+      </c>
+      <c r="E74" s="8" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1154600</v>
+        <v>1499200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="H74" t="n">
-        <v>40.67</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.36</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.728</v>
+        <v>0.419</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.744</v>
+        <v>0.433</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3812,39 +3805,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1154500</v>
+        <v>1478400</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="H75" t="n">
-        <v>53.44</v>
-      </c>
-      <c r="I75" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.48</v>
+      </c>
+      <c r="I75" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.57</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.473</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3857,28 +3850,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1132500</v>
+        <v>1434100</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="H76" t="n">
-        <v>49.5</v>
+        <v>38.79</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3886,10 +3879,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.771</v>
+        <v>0.271</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.772</v>
+        <v>0.292</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3902,39 +3895,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.385</v>
+        <v>0.51</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>-0.0128</v>
+        <v>-0.0097</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1110100</v>
+        <v>1400100</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="H77" t="n">
-        <v>48.59</v>
-      </c>
-      <c r="I77" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.58</v>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.388</v>
+        <v>0.54</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.39</v>
+        <v>0.569</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3947,39 +3940,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.585</v>
+        <v>0.63</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>-0.0168</v>
+        <v>-0.0233</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1106600</v>
+        <v>1391500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.27</v>
+        <v>0.16</v>
       </c>
       <c r="H78" t="n">
-        <v>67.13</v>
-      </c>
-      <c r="I78" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40</v>
+      </c>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.517</v>
+        <v>0.674</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.472</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3992,28 +3985,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.825</v>
+        <v>0.215</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>-0.0237</v>
+        <v>-0.0227</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1095900</v>
+        <v>1383900</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.36</v>
+        <v>1.84</v>
       </c>
       <c r="H79" t="n">
-        <v>14.93</v>
+        <v>42.03</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4021,10 +4014,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.907</v>
+        <v>0.223</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.969</v>
+        <v>0.232</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4037,28 +4030,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>-0.0161</v>
+        <v>0.41</v>
+      </c>
+      <c r="E80" s="8" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1092800</v>
+        <v>1383500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="H80" t="n">
-        <v>23.81</v>
+        <v>42.88</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4066,10 +4059,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.965</v>
+        <v>0.435</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>1.049</v>
+        <v>0.435</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4082,28 +4075,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>1.06</v>
       </c>
       <c r="E81" s="3" t="n">
-        <v>-0.0121</v>
+        <v>-0.0275</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1085800</v>
+        <v>1380900</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.31</v>
+        <v>0.15</v>
       </c>
       <c r="H81" t="n">
-        <v>49.71</v>
+        <v>48.11</v>
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
@@ -4111,10 +4104,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.825</v>
+        <v>1.076</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.785</v>
+        <v>1.046</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4127,28 +4120,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="E82" s="8" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.825</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>-0.0237</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1059300</v>
+        <v>1335100</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.09</v>
+        <v>0.44</v>
       </c>
       <c r="H82" t="n">
-        <v>53.17</v>
+        <v>14.93</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4156,10 +4149,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>2.447</v>
+        <v>0.907</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>2.392</v>
+        <v>0.969</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4172,39 +4165,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2.1</v>
+        <v>2.46</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0.009599999999999999</v>
+        <v>0.008199999999999999</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1056000</v>
+        <v>1323300</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="H83" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.17</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>2.106</v>
+        <v>2.447</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2.103</v>
+        <v>2.392</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4217,28 +4210,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0261</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>-0.0361</v>
+        <v>2.08</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1026700</v>
+        <v>1303400</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>2.16</v>
+        <v>0.08</v>
       </c>
       <c r="H84" t="n">
-        <v>60.07</v>
+        <v>45.7</v>
       </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
@@ -4246,10 +4239,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.384</v>
+        <v>2.104</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.365</v>
+        <v>2.102</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4262,28 +4255,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>-0.0183</v>
+        <v>0.785</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0.0195</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>986100</v>
+        <v>1291300</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.11</v>
+        <v>0.52</v>
       </c>
       <c r="H85" t="n">
-        <v>49.53</v>
+        <v>58.96</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4291,10 +4284,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>1.077</v>
+        <v>0.741</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>1.047</v>
+        <v>0.705</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4307,28 +4300,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.865</v>
+        <v>0.705</v>
       </c>
       <c r="E86" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>978000</v>
+        <v>1274100</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.32</v>
+        <v>0.67</v>
       </c>
       <c r="H86" t="n">
-        <v>51.48</v>
+        <v>40.67</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4336,10 +4329,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.865</v>
+        <v>0.728</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.86</v>
+        <v>0.744</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4352,39 +4345,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>-0.0207</v>
+        <v>0.335</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>970700</v>
+        <v>1271300</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1.29</v>
+        <v>0.27</v>
       </c>
       <c r="H87" t="n">
-        <v>32.08</v>
-      </c>
-      <c r="I87" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.93</v>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.495</v>
+        <v>0.335</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1.503</v>
+        <v>0.343</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4397,28 +4390,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1.21</v>
+        <v>0.59</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>967200</v>
+        <v>1267800</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="H88" t="n">
-        <v>22.97</v>
+        <v>49.02</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4426,10 +4419,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.375</v>
+        <v>0.597</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1.551</v>
+        <v>0.586</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4442,28 +4435,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0261</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>2.42</v>
+        <v>0.35</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>-0.032</v>
+        <v>-0.1566</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>963400</v>
+        <v>1249600</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.19</v>
+        <v>2.63</v>
       </c>
       <c r="H89" t="n">
-        <v>30.24</v>
+        <v>42.14</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4471,10 +4464,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>2.771</v>
+        <v>0.379</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2.88</v>
+        <v>0.364</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4487,28 +4480,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>906700</v>
+        <v>1239800</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="H90" t="n">
-        <v>52.54</v>
+        <v>30.38</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4516,10 +4509,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>3.96</v>
+        <v>0.493</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>3.573</v>
+        <v>0.552</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4532,39 +4525,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1.2</v>
+        <v>0.28</v>
       </c>
       <c r="E91" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>890800</v>
+        <v>1239300</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.26</v>
+        <v>1.33</v>
       </c>
       <c r="H91" t="n">
-        <v>49.45</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.75</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>1.236</v>
+        <v>0.276</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>1.077</v>
+        <v>0.268</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4577,28 +4570,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.76</v>
+        <v>5.59</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>-0.0194</v>
+        <v>-0.0032</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>886700</v>
+        <v>1192000</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.39</v>
+        <v>0.16</v>
       </c>
       <c r="H92" t="n">
-        <v>62.26</v>
+        <v>28.6</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4606,10 +4599,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.733</v>
+        <v>5.874</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.652</v>
+        <v>6.164</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4622,39 +4615,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.64</v>
+        <v>0.585</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>-0.03759999999999999</v>
+        <v>-0.0168</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>881400</v>
+        <v>1181300</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
       <c r="H93" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.13</v>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.716</v>
+        <v>0.517</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.743</v>
+        <v>0.472</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4667,39 +4660,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0</v>
+        <v>1.21</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>867600</v>
+        <v>1153500</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.14</v>
+        <v>0.26</v>
       </c>
       <c r="H94" t="n">
-        <v>68.05</v>
-      </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.97</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.93</v>
+        <v>1.375</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0.88</v>
+        <v>1.551</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4712,28 +4705,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E95" s="3" t="n">
-        <v>-0.0035</v>
+        <v>6.73</v>
+      </c>
+      <c r="E95" s="8" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>849100</v>
+        <v>1133700</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
       <c r="H95" t="n">
-        <v>55.12</v>
+        <v>31.09</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4741,10 +4734,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>2.802</v>
+        <v>7.163</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>2.672</v>
+        <v>7.581</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4757,39 +4750,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.63</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0182</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>841600</v>
+        <v>1131700</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.38</v>
+        <v>0.32</v>
       </c>
       <c r="H96" t="n">
-        <v>47.44</v>
-      </c>
-      <c r="I96" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.87</v>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.637</v>
+        <v>0.825</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.624</v>
+        <v>0.784</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4802,39 +4795,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>796900</v>
+        <v>1126000</v>
       </c>
       <c r="G97" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H97" t="n">
+        <v>48.59</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="K97" s="2" t="n">
         <v>0.39</v>
-      </c>
-      <c r="H97" t="n">
-        <v>40.19</v>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="n">
-        <v>1.364</v>
-      </c>
-      <c r="K97" s="2" t="n">
-        <v>1.342</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4847,28 +4840,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E98" s="10" t="n">
-        <v>0</v>
+        <v>2.4</v>
+      </c>
+      <c r="E98" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>794600</v>
+        <v>1112000</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.06</v>
+        <v>0.22</v>
       </c>
       <c r="H98" t="n">
-        <v>44.85</v>
+        <v>29.66</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4876,10 +4869,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.755</v>
+        <v>2.769</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2.741</v>
+        <v>2.879</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4892,28 +4885,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>6.74</v>
-      </c>
-      <c r="E99" s="8" t="n">
-        <v>0.009000000000000001</v>
+        <v>3.9</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>787500</v>
+        <v>1104600</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H99" t="n">
-        <v>31.54</v>
+        <v>50.43</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4921,10 +4914,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>7.164</v>
+        <v>3.955</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>7.582</v>
+        <v>3.572</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4937,39 +4930,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>6.53</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>-0.0031</v>
+        <v>2.46</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>763900</v>
+        <v>1101000</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.13</v>
+        <v>0.37</v>
       </c>
       <c r="H100" t="n">
-        <v>57.37</v>
-      </c>
-      <c r="I100" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.65</v>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>6.211</v>
+        <v>2.546</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>5.932</v>
+        <v>2.676</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4982,28 +4975,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>1.42</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>-0.0207</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>735100</v>
+        <v>1064000</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.16</v>
+        <v>1.41</v>
       </c>
       <c r="H101" t="n">
-        <v>58.81</v>
+        <v>32.08</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5011,10 +5004,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.06</v>
+        <v>1.495</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.923</v>
+        <v>1.503</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5027,28 +5020,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>4.81</v>
+        <v>0.635</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0451</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>729500</v>
+        <v>1063700</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.03</v>
+        <v>0.32</v>
       </c>
       <c r="H102" t="n">
-        <v>46.62</v>
+        <v>31.55</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5056,10 +5049,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>4.894</v>
+        <v>0.716</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>4.736</v>
+        <v>0.743</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5072,39 +5065,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="E103" s="8" t="n">
-        <v>0.0051</v>
+        <v>2.85</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.0035</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>710800</v>
+        <v>1004400</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
       <c r="H103" t="n">
-        <v>44.98</v>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.12</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>9.996</v>
+        <v>2.802</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>10.137</v>
+        <v>2.672</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5117,39 +5110,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>-0.0049</v>
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E104" s="8" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>706400</v>
+        <v>1001800</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.21</v>
+        <v>0.08</v>
       </c>
       <c r="H104" t="n">
-        <v>44.31</v>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.98</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>2.042</v>
+        <v>9.996</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>2.069</v>
+        <v>10.137</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5162,28 +5155,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1.24</v>
+        <v>0.725</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>-0.0236</v>
+        <v>-0.0268</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>704300</v>
+        <v>996400</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.23</v>
+        <v>0.16</v>
       </c>
       <c r="H105" t="n">
-        <v>47.31</v>
+        <v>49.44</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5191,10 +5184,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.283</v>
+        <v>0.741</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>1.228</v>
+        <v>0.679</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5207,28 +5200,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.0227</v>
+        <v>-0.0083</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>678300</v>
+        <v>972900</v>
       </c>
       <c r="G106" s="5" t="n">
         <v>0.28</v>
       </c>
       <c r="H106" t="n">
-        <v>54.96</v>
+        <v>48.39</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5236,10 +5229,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.264</v>
+        <v>1.235</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1.176</v>
+        <v>1.076</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5252,39 +5245,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>0.013</v>
+        <v>6.46</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>-0.0137</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>655900</v>
+        <v>966100</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H107" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.07</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.74</v>
+        <v>6.204</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.705</v>
+        <v>5.93</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5297,28 +5290,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>-0.0066</v>
+        <v>2.55</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>650000</v>
+        <v>938700</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H108" t="n">
-        <v>50.71</v>
+        <v>45.14</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5326,10 +5319,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>3.025</v>
+        <v>2.603</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2.859</v>
+        <v>2.61</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5342,28 +5335,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>-0.0068</v>
+        <v>0.915</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>640600</v>
+        <v>936900</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.08</v>
+        <v>0.53</v>
       </c>
       <c r="H109" t="n">
-        <v>27.95</v>
+        <v>51.22</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5371,10 +5364,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>5.872</v>
+        <v>0.915</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>6.163</v>
+        <v>0.879</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5387,28 +5380,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E110" s="8" t="n">
-        <v>0.009000000000000001</v>
+        <v>1.23</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>-0.0315</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>627100</v>
+        <v>934900</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="H110" t="n">
-        <v>46.4</v>
+        <v>46.57</v>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
@@ -5416,10 +5409,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.152</v>
+        <v>1.282</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1.103</v>
+        <v>1.228</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5432,39 +5425,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="E111" s="8" t="n">
-        <v>0.0043</v>
+        <v>1.09</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>-0.018</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>608000</v>
+        <v>928800</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="H111" t="n">
-        <v>59.64</v>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.92</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>2.232</v>
+        <v>1.149</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>2.175</v>
+        <v>1.103</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5477,28 +5470,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>3.78</v>
+        <v>1.16</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0169</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>607200</v>
+        <v>901000</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="H112" t="n">
-        <v>48.34</v>
+        <v>49.53</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5506,10 +5499,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>3.844</v>
+        <v>1.169</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>3.699</v>
+        <v>1.139</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5522,39 +5515,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PARADIGM</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>-0.0062</v>
+        <v>0.975</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>603200</v>
+        <v>897900</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>1.57</v>
+        <v>0.15</v>
       </c>
       <c r="H113" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.05</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.819</v>
+        <v>0.93</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.848</v>
+        <v>0.88</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5567,39 +5560,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="E114" s="8" t="n">
-        <v>0.0068</v>
+        <v>0.76</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>-0.0194</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>581000</v>
+        <v>893100</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.11</v>
+        <v>0.39</v>
       </c>
       <c r="H114" t="n">
-        <v>52.02</v>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.26</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>4.363</v>
+        <v>0.733</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>4.43</v>
+        <v>0.652</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5612,39 +5605,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>-0.0076</v>
+        <v>1.11</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>572600</v>
+        <v>892100</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H115" t="n">
-        <v>55.77</v>
-      </c>
-      <c r="I115" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.81</v>
+      </c>
+      <c r="I115" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.647</v>
+        <v>1.06</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.923</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5657,39 +5650,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.65</v>
+        <v>1.27</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>-0.0076</v>
+        <v>-0.0379</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>571300</v>
+        <v>858500</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
       <c r="H116" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="I116" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.97</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.585</v>
+        <v>1.262</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.532</v>
+        <v>1.176</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5702,39 +5695,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.17</v>
+        <v>0.63</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>559200</v>
+        <v>842400</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.08</v>
+        <v>0.38</v>
       </c>
       <c r="H117" t="n">
-        <v>50.89</v>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.44</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.17</v>
+        <v>0.637</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.139</v>
+        <v>0.624</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5747,28 +5740,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E118" s="3" t="n">
-        <v>-0.0039</v>
+        <v>1.34</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>510900</v>
+        <v>796900</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.09</v>
+        <v>0.39</v>
       </c>
       <c r="H118" t="n">
-        <v>44.34</v>
+        <v>40.19</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5776,10 +5769,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>2.602</v>
+        <v>1.364</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2.61</v>
+        <v>1.342</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5792,28 +5785,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.735</v>
+        <v>4.81</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>-0.0134</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>503400</v>
+        <v>788700</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.08</v>
+        <v>0.03</v>
       </c>
       <c r="H119" t="n">
-        <v>51.15</v>
+        <v>46.62</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5821,10 +5814,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.742</v>
+        <v>4.894</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.679</v>
+        <v>4.736</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5837,28 +5830,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.905</v>
+        <v>3.78</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0182</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>500800</v>
+        <v>766600</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.29</v>
+        <v>0.26</v>
       </c>
       <c r="H120" t="n">
-        <v>32.37</v>
+        <v>48.34</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5866,16 +5859,871 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.9409999999999999</v>
+        <v>3.844</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.999</v>
+        <v>3.699</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F121" s="4" t="n">
+        <v>716200</v>
+      </c>
+      <c r="G121" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H121" t="n">
+        <v>58.91</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="2" t="n">
+        <v>2.231</v>
+      </c>
+      <c r="K121" s="2" t="n">
+        <v>2.175</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>-0.0066</v>
+      </c>
+      <c r="F122" s="4" t="n">
+        <v>689100</v>
+      </c>
+      <c r="G122" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H122" t="n">
+        <v>50.71</v>
+      </c>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="n">
+        <v>3.025</v>
+      </c>
+      <c r="K122" s="2" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F123" s="4" t="n">
+        <v>688800</v>
+      </c>
+      <c r="G123" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H123" t="n">
+        <v>27.88</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="2" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="K123" s="2" t="n">
+        <v>0.786</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>4.96</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>-0.006</v>
+      </c>
+      <c r="F124" s="4" t="n">
+        <v>675800</v>
+      </c>
+      <c r="G124" s="5" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H124" t="n">
+        <v>43.82</v>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="2" t="n">
+        <v>5.049</v>
+      </c>
+      <c r="K124" s="2" t="n">
+        <v>5.052</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F125" s="4" t="n">
+        <v>660300</v>
+      </c>
+      <c r="G125" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H125" t="n">
+        <v>52.02</v>
+      </c>
+      <c r="I125" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J125" s="2" t="n">
+        <v>4.363</v>
+      </c>
+      <c r="K125" s="2" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5338</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>PARADIGM</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>656600</v>
+      </c>
+      <c r="G126" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H126" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="2" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K126" s="2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="F127" s="4" t="n">
+        <v>642500</v>
+      </c>
+      <c r="G127" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H127" t="n">
+        <v>44.88</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="2" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="K127" s="2" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>0391</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>AMBEST</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.0315</v>
+      </c>
+      <c r="F128" s="4" t="n">
+        <v>642000</v>
+      </c>
+      <c r="G128" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H128" t="n">
+        <v>40.82</v>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="K128" s="2" t="n">
+        <v>1.288</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="F129" s="4" t="n">
+        <v>641900</v>
+      </c>
+      <c r="G129" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H129" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J129" s="2" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="K129" s="2" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E130" s="3" t="n">
+        <v>-0.0231</v>
+      </c>
+      <c r="F130" s="4" t="n">
+        <v>614700</v>
+      </c>
+      <c r="G130" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H130" t="n">
+        <v>22.86</v>
+      </c>
+      <c r="I130" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="2" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="K130" s="2" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="F131" s="4" t="n">
+        <v>611200</v>
+      </c>
+      <c r="G131" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H131" t="n">
+        <v>48.15</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J131" s="2" t="n">
+        <v>7.333</v>
+      </c>
+      <c r="K131" s="2" t="n">
+        <v>6.905</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>5331</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>PGLOBAL</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F132" s="4" t="n">
+        <v>582800</v>
+      </c>
+      <c r="G132" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H132" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="I132" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J132" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="K132" s="2" t="n">
+        <v>0.532</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F133" s="4" t="n">
+        <v>581200</v>
+      </c>
+      <c r="G133" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H133" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J133" s="2" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="K133" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="F134" s="4" t="n">
+        <v>572100</v>
+      </c>
+      <c r="G134" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H134" t="n">
+        <v>34.54</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="2" t="n">
+        <v>2.528</v>
+      </c>
+      <c r="K134" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F135" s="4" t="n">
+        <v>567000</v>
+      </c>
+      <c r="G135" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H135" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="I135" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J135" s="2" t="n">
+        <v>1.764</v>
+      </c>
+      <c r="K135" s="2" t="n">
+        <v>1.881</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>0233</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>PEKAT</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E136" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F136" s="4" t="n">
+        <v>533100</v>
+      </c>
+      <c r="G136" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H136" t="n">
+        <v>59.68</v>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="2" t="n">
+        <v>2.694</v>
+      </c>
+      <c r="K136" s="2" t="n">
+        <v>2.283</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F137" s="4" t="n">
+        <v>525000</v>
+      </c>
+      <c r="G137" s="5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="H137" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K137" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E138" s="8" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="F138" s="4" t="n">
+        <v>523300</v>
+      </c>
+      <c r="G138" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H138" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K138" s="2" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E139" s="3" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="F139" s="4" t="n">
+        <v>500800</v>
+      </c>
+      <c r="G139" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H139" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="K139" s="2" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M120"/>
+  <autoFilter ref="A1:M139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
+++ b/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-20" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M139"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.0294</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>39822800</v>
+        <v>41878100</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H2" t="n">
         <v>63.6</v>
@@ -603,10 +603,10 @@
         <v>0.0562</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>30297300</v>
+        <v>34456200</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.87</v>
+        <v>0.99</v>
       </c>
       <c r="H3" t="n">
         <v>81.92</v>
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>25283500</v>
+        <v>26710100</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0.07000000000000001</v>
@@ -693,10 +693,10 @@
         <v>-0.0112</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>20940600</v>
+        <v>24867000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="H5" t="n">
         <v>62.03</v>
@@ -723,39 +723,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E6" s="8" t="n">
-        <v>0.0217</v>
+        <v>1.49</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>-0.0745</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>17362300</v>
+        <v>18736000</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.68</v>
+        <v>3.74</v>
       </c>
       <c r="H6" t="n">
-        <v>80.01000000000001</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.37</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>0.626</v>
+        <v>1.7</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0.537</v>
+        <v>1.761</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="7" t="inlineStr"/>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>-0.08699999999999999</v>
+        <v>0.705</v>
+      </c>
+      <c r="E7" s="8" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17152100</v>
+        <v>17419600</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>3.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>24.38</v>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.01000000000001</v>
+      </c>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.698</v>
+        <v>0.626</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1.76</v>
+        <v>0.537</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -828,10 +828,10 @@
         <v>0.09720000000000001</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>14822900</v>
+        <v>16275400</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.61</v>
+        <v>1.77</v>
       </c>
       <c r="H8" t="n">
         <v>27.6</v>
@@ -873,10 +873,10 @@
         <v>-0.1078</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>14668500</v>
+        <v>15585800</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.31</v>
+        <v>1.4</v>
       </c>
       <c r="H9" t="n">
         <v>40.96</v>
@@ -903,28 +903,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>-0.0364</v>
+        <v>0.155</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>11779200</v>
+        <v>12685100</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1.2</v>
+        <v>0.36</v>
       </c>
       <c r="H10" t="n">
-        <v>38.24</v>
+        <v>48.61</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>0.295</v>
+        <v>0.155</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>0.28</v>
+        <v>0.156</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
@@ -948,28 +948,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.385</v>
+        <v>0.265</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.0128</v>
+        <v>-0.0364</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>10471200</v>
+        <v>11785700</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.05</v>
+        <v>1.2</v>
       </c>
       <c r="H11" t="n">
-        <v>28.49</v>
+        <v>38.24</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -977,10 +977,10 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.396</v>
+        <v>0.295</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>0.406</v>
+        <v>0.28</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
@@ -993,33 +993,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>9375000</v>
+        <v>10573700</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.4</v>
+        <v>1.06</v>
+      </c>
+      <c r="H12" t="n">
+        <v>28.49</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J12" s="2" t="n"/>
-      <c r="K12" s="2" t="n"/>
+      <c r="J12" s="2" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>0.406</v>
+      </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
     </row>
@@ -1031,38 +1038,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.385</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>0.0548</v>
+        <v>0.305</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>8467100</v>
+        <v>9980600</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>1.61</v>
+        <v>0.52</v>
       </c>
       <c r="H13" t="n">
-        <v>68.34</v>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.44</v>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="K13" s="2" t="n"/>
+        <v>0.308</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>0.301</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
     </row>
@@ -1074,40 +1083,33 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E14" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>-0.1667</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>8271800</v>
+        <v>9880600</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H14" t="n">
-        <v>36.45</v>
+        <v>0.25</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="K14" s="2" t="n">
-        <v>0.481</v>
-      </c>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
     </row>
@@ -1119,40 +1121,33 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OCR</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.045</v>
+        <v>0.25</v>
       </c>
       <c r="E15" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>7400200</v>
+        <v>9375000</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H15" t="n">
-        <v>29.14</v>
+        <v>0.4</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n">
-        <v>0.049</v>
-      </c>
-      <c r="K15" s="2" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="J15" s="2" t="n"/>
+      <c r="K15" s="2" t="n"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1164,28 +1159,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E16" s="3" t="n">
-        <v>-0.0146</v>
+        <v>0.39</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>0.06849999999999999</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>7255500</v>
+        <v>9296400</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.25</v>
+        <v>1.77</v>
       </c>
       <c r="H16" t="n">
-        <v>58.58</v>
+        <v>69.2</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -1193,11 +1188,9 @@
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.941</v>
-      </c>
-      <c r="K16" s="2" t="n">
-        <v>1.754</v>
-      </c>
+        <v>0.326</v>
+      </c>
+      <c r="K16" s="2" t="n"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
     </row>
@@ -1209,33 +1202,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.745</v>
+        <v>0.43</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.0132</v>
+        <v>-0.0115</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>7234600</v>
+        <v>8410400</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.12</v>
+        <v>0.23</v>
+      </c>
+      <c r="H17" t="n">
+        <v>35.32</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n"/>
-      <c r="K17" s="2" t="n"/>
+      <c r="J17" s="2" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>0.481</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1247,39 +1247,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.205</v>
+        <v>0.82</v>
       </c>
       <c r="E18" s="3" t="n">
-        <v>-0.0238</v>
+        <v>-0.0061</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>7018500</v>
+        <v>8052400</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.31</v>
+        <v>0.51</v>
       </c>
       <c r="H18" t="n">
-        <v>40.25</v>
-      </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.61</v>
+      </c>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.217</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>0.234</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
@@ -1292,28 +1292,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>0.305</v>
+        <v>2.02</v>
       </c>
       <c r="E19" s="3" t="n">
-        <v>-0.0161</v>
+        <v>-0.0146</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>6527600</v>
+        <v>7884900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.34</v>
+        <v>0.27</v>
       </c>
       <c r="H19" t="n">
-        <v>47.44</v>
+        <v>58.58</v>
       </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>0.308</v>
+        <v>1.941</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0.301</v>
+        <v>1.754</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1337,40 +1337,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.0061</v>
+        <v>0.755</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>6412400</v>
+        <v>7808000</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H20" t="n">
-        <v>55.61</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>0.8110000000000001</v>
-      </c>
+        <v>0.13</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
     </row>
@@ -1382,39 +1375,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>PUNCAK</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>0.0256</v>
+        <v>0.205</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>6339400</v>
+        <v>7581500</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>16.64</v>
+        <v>0.34</v>
       </c>
       <c r="H21" t="n">
-        <v>82.42</v>
-      </c>
-      <c r="I21" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.25</v>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.177</v>
+        <v>0.217</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.171</v>
+        <v>0.234</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1427,28 +1420,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>OCR</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.0193</v>
+        <v>0.045</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6235000</v>
+        <v>7400300</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.34</v>
+        <v>3</v>
       </c>
       <c r="H22" t="n">
-        <v>45.11</v>
+        <v>29.14</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1456,10 +1449,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>2.634</v>
+        <v>0.049</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>2.556</v>
+        <v>0.05</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1472,39 +1465,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>-0.0172</v>
+        <v>0.775</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>6123600</v>
+        <v>7183100</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.97</v>
+        <v>0.47</v>
       </c>
       <c r="H23" t="n">
-        <v>35.29</v>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.91</v>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.312</v>
+        <v>0.775</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.334</v>
+        <v>0.776</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1517,39 +1510,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E24" s="10" t="n">
-        <v>0</v>
+        <v>0.18</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6117000</v>
+        <v>6940100</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.4</v>
+        <v>1.34</v>
       </c>
       <c r="H24" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I24" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.69</v>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.775</v>
+        <v>0.175</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.776</v>
+        <v>0.182</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1562,28 +1555,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.53</v>
+        <v>2.54</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-0.0364</v>
+        <v>-0.0193</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>5967300</v>
+        <v>6851800</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="H25" t="n">
-        <v>43.63</v>
+        <v>45.11</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1591,10 +1584,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>0.569</v>
+        <v>2.634</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.542</v>
+        <v>2.556</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1607,28 +1600,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.97</v>
+        <v>0.285</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-0.0251</v>
+        <v>-0.0172</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>5349700</v>
+        <v>6474400</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.66</v>
+        <v>1.02</v>
       </c>
       <c r="H26" t="n">
-        <v>41.14</v>
+        <v>35.29</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1636,10 +1629,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1.042</v>
+        <v>0.312</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.964</v>
+        <v>0.334</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1652,28 +1645,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>PUNCAK</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E27" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.2</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5345600</v>
+        <v>6389400</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.27</v>
+        <v>16.77</v>
       </c>
       <c r="H27" t="n">
-        <v>46.09</v>
+        <v>82.42</v>
       </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
@@ -1681,10 +1674,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.868</v>
+        <v>0.177</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.869</v>
+        <v>0.171</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1697,39 +1690,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.435</v>
+        <v>0.865</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-0.044</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>5242100</v>
+        <v>6326000</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="H28" t="n">
-        <v>25.17</v>
-      </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.09</v>
+      </c>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.5</v>
+        <v>0.868</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.665</v>
+        <v>0.869</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1742,39 +1735,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>0.535</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.0273</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>5230900</v>
+        <v>6185500</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.48</v>
+        <v>0.3</v>
       </c>
       <c r="H29" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.44</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.619</v>
+        <v>0.57</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.616</v>
+        <v>0.543</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1787,33 +1780,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.11</v>
+        <v>0.98</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-0.0833</v>
+        <v>-0.0151</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5143200</v>
+        <v>6093900</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.13</v>
+        <v>0.75</v>
+      </c>
+      <c r="H30" t="n">
+        <v>42.3</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J30" s="2" t="n"/>
-      <c r="K30" s="2" t="n"/>
+      <c r="J30" s="2" t="n">
+        <v>1.043</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>0.964</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
     </row>
@@ -1825,28 +1825,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E31" s="8" t="n">
-        <v>0.0294</v>
+        <v>0.44</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0.033</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5092000</v>
+        <v>5914200</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.98</v>
+        <v>0.26</v>
       </c>
       <c r="H31" t="n">
-        <v>48.66</v>
+        <v>25.77</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.174</v>
+        <v>0.501</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.181</v>
+        <v>0.665</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1870,39 +1870,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.415</v>
+        <v>0.17</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.0247</v>
+        <v>0.0303</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4931700</v>
+        <v>5845400</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.4</v>
+        <v>1.95</v>
       </c>
       <c r="H32" t="n">
-        <v>57.67</v>
-      </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.394</v>
+        <v>0.157</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.379</v>
+        <v>0.155</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,39 +1915,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.175</v>
+        <v>0.63</v>
       </c>
       <c r="E33" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>4875000</v>
+        <v>5721400</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.22</v>
+        <v>0.52</v>
       </c>
       <c r="H33" t="n">
-        <v>40.18</v>
-      </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.52</v>
+      </c>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.188</v>
+        <v>0.619</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.185</v>
+        <v>0.616</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,28 +1960,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.415</v>
+      </c>
+      <c r="E34" s="8" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4586500</v>
+        <v>5566400</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.89</v>
+        <v>0.46</v>
       </c>
       <c r="H34" t="n">
-        <v>37.19</v>
+        <v>57.67</v>
       </c>
       <c r="I34" s="6" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.75</v>
+        <v>0.394</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.379</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2005,39 +2005,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E35" s="8" t="n">
-        <v>0.0133</v>
+        <v>0.665</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.0828</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>4448200</v>
+        <v>5251600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.6</v>
+        <v>1.02</v>
       </c>
       <c r="H35" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.29</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.372</v>
+        <v>0.751</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.369</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2050,28 +2050,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.125</v>
+        <v>0.18</v>
       </c>
       <c r="E36" s="8" t="n">
-        <v>0.0417</v>
+        <v>0.0286</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>4352900</v>
+        <v>5028700</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="H36" t="n">
-        <v>53.06</v>
+        <v>44.12</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.126</v>
+        <v>0.188</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.102</v>
+        <v>0.186</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2110,10 +2110,10 @@
         <v>-0.0116</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4246300</v>
+        <v>4848000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="H37" t="n">
         <v>53.34</v>
@@ -2149,19 +2149,19 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.34</v>
+        <v>0.345</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>-0.0286</v>
+        <v>-0.0143</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>4138800</v>
+        <v>4779400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.54</v>
+        <v>0.62</v>
       </c>
       <c r="H38" t="n">
-        <v>46.04</v>
+        <v>48.17</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.352</v>
+        <v>0.353</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0.328</v>
@@ -2185,39 +2185,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E39" s="3" t="n">
-        <v>-0.0357</v>
+        <v>0.38</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>3831200</v>
+        <v>4605200</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.42</v>
+        <v>0.63</v>
       </c>
       <c r="H39" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.65</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.636</v>
+        <v>0.372</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.619</v>
+        <v>0.369</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2230,39 +2230,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>4.73</v>
+        <v>0.13</v>
       </c>
       <c r="E40" s="8" t="n">
-        <v>0.0042</v>
+        <v>0.0833</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>3566600</v>
+        <v>4362900</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.17</v>
+        <v>0.45</v>
       </c>
       <c r="H40" t="n">
-        <v>48.55</v>
-      </c>
-      <c r="I40" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.88</v>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>4.729</v>
+        <v>0.126</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4.84</v>
+        <v>0.102</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2275,28 +2275,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3501400</v>
+        <v>3950900</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.05</v>
+        <v>0.43</v>
       </c>
       <c r="H41" t="n">
-        <v>42.14</v>
+        <v>32.82</v>
       </c>
       <c r="I41" s="6" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.157</v>
+        <v>0.636</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.141</v>
+        <v>0.619</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2320,39 +2320,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>-0.0052</v>
+        <v>4.72</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3474700</v>
+        <v>3882900</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.4</v>
+        <v>0.19</v>
       </c>
       <c r="H42" t="n">
-        <v>58.09</v>
-      </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.71</v>
+      </c>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>3.668</v>
+        <v>4.728</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3.055</v>
+        <v>4.84</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2365,28 +2365,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E43" s="3" t="n">
-        <v>-0.0147</v>
+        <v>3.88</v>
+      </c>
+      <c r="E43" s="8" t="n">
+        <v>0.0104</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3356500</v>
+        <v>3763700</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="H43" t="n">
-        <v>47.18</v>
+        <v>59.72</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2394,10 +2394,10 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>0.345</v>
+        <v>3.674</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0.335</v>
+        <v>3.057</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2410,28 +2410,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="E44" s="3" t="n">
-        <v>-0.0541</v>
+        <v>0.14</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3349000</v>
+        <v>3578000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.82</v>
+        <v>0.06</v>
       </c>
       <c r="H44" t="n">
-        <v>24.82</v>
+        <v>42.14</v>
       </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
@@ -2439,10 +2439,10 @@
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.197</v>
+        <v>0.157</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.207</v>
+        <v>0.141</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2455,28 +2455,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.275</v>
+        <v>2.01</v>
       </c>
       <c r="E45" s="3" t="n">
-        <v>-0.0179</v>
+        <v>-0.005</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3266900</v>
+        <v>3573600</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="H45" t="n">
-        <v>44.46</v>
+        <v>32.46</v>
       </c>
       <c r="I45" s="6" t="inlineStr">
         <is>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.289</v>
+        <v>2.134</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.283</v>
+        <v>2.235</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2500,39 +2500,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>0.005</v>
+        <v>1.17</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>2919800</v>
+        <v>3536500</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.24</v>
+        <v>0.45</v>
       </c>
       <c r="H46" t="n">
-        <v>34.71</v>
-      </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.42</v>
+      </c>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>2.136</v>
+        <v>1.227</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2.236</v>
+        <v>1.316</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2545,39 +2545,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>-0.0049</v>
+        <v>7.26</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.0083</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2774200</v>
+        <v>3405000</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.84</v>
+        <v>0.34</v>
       </c>
       <c r="H47" t="n">
-        <v>44.31</v>
-      </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.26</v>
+      </c>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>2.042</v>
+        <v>7.435</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>2.069</v>
+        <v>7.919</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2590,28 +2590,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.42</v>
+        <v>0.18</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>-0.0345</v>
+        <v>-0.027</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2638900</v>
+        <v>3376400</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.38</v>
+        <v>0.82</v>
       </c>
       <c r="H48" t="n">
-        <v>49.76</v>
+        <v>27.5</v>
       </c>
       <c r="I48" s="6" t="inlineStr">
         <is>
@@ -2619,10 +2619,10 @@
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.424</v>
+        <v>0.197</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.416</v>
+        <v>0.207</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2635,39 +2635,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E49" s="8" t="n">
-        <v>0.0062</v>
+        <v>0.335</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>2584000</v>
+        <v>3356500</v>
       </c>
       <c r="G49" s="5" t="n">
         <v>0.35</v>
       </c>
       <c r="H49" t="n">
-        <v>47.87</v>
-      </c>
-      <c r="I49" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.18</v>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.623</v>
+        <v>0.345</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>1.689</v>
+        <v>0.335</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2680,39 +2680,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0</v>
+        <v>0.275</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>2562300</v>
+        <v>3322100</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.41</v>
+        <v>0.29</v>
       </c>
       <c r="H50" t="n">
-        <v>62.51</v>
-      </c>
-      <c r="I50" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.46</v>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.206</v>
+        <v>0.289</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1.192</v>
+        <v>0.283</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2725,28 +2725,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="E51" s="8" t="n">
-        <v>0.0264</v>
+        <v>1.28</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2559200</v>
+        <v>2908400</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.8</v>
+        <v>0.46</v>
       </c>
       <c r="H51" t="n">
-        <v>85.70999999999999</v>
+        <v>62.51</v>
       </c>
       <c r="I51" s="9" t="inlineStr">
         <is>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>2.869</v>
+        <v>1.206</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>2.456</v>
+        <v>1.192</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2770,39 +2770,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>-0.0345</v>
+        <v>1.62</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2552600</v>
+        <v>2874700</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.34</v>
+        <v>0.39</v>
       </c>
       <c r="H52" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="I52" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.87</v>
+      </c>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.919</v>
+        <v>1.623</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.85</v>
+        <v>1.689</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2815,28 +2815,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E53" s="3" t="n">
-        <v>-0.07539999999999999</v>
+        <v>2.03</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2521900</v>
+        <v>2834500</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.62</v>
+        <v>0.85</v>
       </c>
       <c r="H53" t="n">
-        <v>59.05</v>
+        <v>46.01</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.848</v>
+        <v>2.043</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.586</v>
+        <v>2.069</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2860,28 +2860,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="E54" s="8" t="n">
-        <v>0.0042</v>
+        <v>0.76</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2348200</v>
+        <v>2823900</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.14</v>
+        <v>2.28</v>
       </c>
       <c r="H54" t="n">
-        <v>34.58</v>
+        <v>58.88</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>7.474</v>
+        <v>0.748</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>7.672</v>
+        <v>0.72</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2905,28 +2905,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
       <c r="E55" s="3" t="n">
-        <v>-0.0208</v>
+        <v>-0.0115</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2299700</v>
+        <v>2819200</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.27</v>
+        <v>0.4</v>
       </c>
       <c r="H55" t="n">
-        <v>36.31</v>
+        <v>52.29</v>
       </c>
       <c r="I55" s="6" t="inlineStr">
         <is>
@@ -2934,10 +2934,10 @@
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.503</v>
+        <v>0.425</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.523</v>
+        <v>0.417</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2950,28 +2950,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1.42</v>
+        <v>0.84</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>-0.0139</v>
+        <v>-0.0345</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2291000</v>
+        <v>2783400</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.2</v>
+        <v>0.37</v>
       </c>
       <c r="H56" t="n">
-        <v>21.35</v>
+        <v>39.9</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>1.667</v>
+        <v>0.919</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>1.931</v>
+        <v>0.85</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2995,28 +2995,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>-0.04650000000000001</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2261100</v>
+        <v>2766200</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.4</v>
+        <v>0.49</v>
       </c>
       <c r="H57" t="n">
-        <v>55.66</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="I57" s="9" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.393</v>
+        <v>0.795</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.362</v>
+        <v>0.773</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3040,28 +3040,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>5.33</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0.0133</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2239000</v>
+        <v>2718600</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.27</v>
+        <v>0.2</v>
       </c>
       <c r="H58" t="n">
-        <v>27.74</v>
+        <v>43.56</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.274</v>
+        <v>5.491</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.3</v>
+        <v>5.471</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3085,39 +3085,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1.16</v>
+        <v>0.21</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0233</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2212000</v>
+        <v>2606300</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="H59" t="n">
-        <v>35.26</v>
-      </c>
-      <c r="I59" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.1</v>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>1.226</v>
+        <v>0.232</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>1.316</v>
+        <v>0.282</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3130,28 +3130,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E60" s="3" t="n">
-        <v>-0.024</v>
+        <v>7.17</v>
+      </c>
+      <c r="E60" s="8" t="n">
+        <v>0.0028</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2200200</v>
+        <v>2572700</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H60" t="n">
-        <v>37.52</v>
+        <v>34.03</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.291</v>
+        <v>7.473</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>1.314</v>
+        <v>7.672</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3175,39 +3175,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>7.25</v>
-      </c>
-      <c r="E61" s="8" t="n">
-        <v>0.0069</v>
+        <v>0.915</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>-0.08039999999999999</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2071700</v>
+        <v>2567900</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.2</v>
+        <v>0.63</v>
       </c>
       <c r="H61" t="n">
-        <v>34.59</v>
-      </c>
-      <c r="I61" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>58.69</v>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>7.435</v>
+        <v>0.848</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>7.919</v>
+        <v>0.586</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3220,28 +3220,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="E62" s="8" t="n">
-        <v>0.0152</v>
+        <v>0.865</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2069300</v>
+        <v>2563000</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.15</v>
+        <v>0.84</v>
       </c>
       <c r="H62" t="n">
-        <v>43.98</v>
+        <v>51.48</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>5.492</v>
+        <v>0.865</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>5.471</v>
+        <v>0.86</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3265,39 +3265,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E63" s="3" t="n">
-        <v>-0.0233</v>
+        <v>3.23</v>
+      </c>
+      <c r="E63" s="8" t="n">
+        <v>0.0264</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2021800</v>
+        <v>2562500</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.13</v>
+        <v>0.8</v>
       </c>
       <c r="H63" t="n">
-        <v>30.1</v>
-      </c>
-      <c r="I63" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>85.70999999999999</v>
+      </c>
+      <c r="I63" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.232</v>
+        <v>2.869</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.282</v>
+        <v>2.456</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3310,28 +3310,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.91</v>
+        <v>1.42</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.0215</v>
+        <v>-0.0139</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2015200</v>
+        <v>2543000</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.5</v>
+        <v>0.22</v>
       </c>
       <c r="H64" t="n">
-        <v>22.95</v>
+        <v>21.35</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.964</v>
+        <v>1.667</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1.048</v>
+        <v>1.931</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3355,39 +3355,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.615</v>
+        <v>0.47</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.0391</v>
+        <v>-0.0208</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2012300</v>
+        <v>2439700</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>11.22</v>
+        <v>0.28</v>
       </c>
       <c r="H65" t="n">
-        <v>67.55</v>
-      </c>
-      <c r="I65" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.31</v>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.503</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.546</v>
+        <v>0.523</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3400,39 +3400,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E66" s="8" t="n">
-        <v>0.0061</v>
+        <v>1.24</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>1995300</v>
+        <v>2365900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
       <c r="H66" t="n">
-        <v>66.83</v>
-      </c>
-      <c r="I66" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.92</v>
+      </c>
+      <c r="I66" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.796</v>
+        <v>1.293</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0.773</v>
+        <v>1.314</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3445,39 +3445,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.765</v>
+        <v>0.41</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>1877600</v>
+        <v>2311100</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>1.52</v>
+        <v>0.41</v>
       </c>
       <c r="H67" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="I67" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.66</v>
+      </c>
+      <c r="I67" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.749</v>
+        <v>0.393</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.721</v>
+        <v>0.362</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3490,39 +3490,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E68" s="8" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.915</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>1824400</v>
+        <v>2252700</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>1.79</v>
+        <v>0.55</v>
       </c>
       <c r="H68" t="n">
-        <v>75.44</v>
-      </c>
-      <c r="I68" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>23.81</v>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.209</v>
+        <v>0.965</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.21</v>
+        <v>1.049</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3535,28 +3535,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E69" s="3" t="n">
-        <v>-0.0275</v>
+        <v>0.255</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>1789400</v>
+        <v>2249000</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
       <c r="H69" t="n">
-        <v>45.45</v>
+        <v>27.74</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.274</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.518</v>
+        <v>0.3</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3580,28 +3580,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.865</v>
+        <v>0.54</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0092</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>1763000</v>
+        <v>2104500</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.58</v>
+        <v>0.39</v>
       </c>
       <c r="H70" t="n">
-        <v>51.48</v>
+        <v>47.65</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.865</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.86</v>
+        <v>0.518</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3625,39 +3625,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0</v>
+        <v>0.61</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>-0.0469</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1548200</v>
+        <v>2053500</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.19</v>
+        <v>11.45</v>
       </c>
       <c r="H71" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="I71" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.78</v>
+      </c>
+      <c r="I71" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.771</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.772</v>
+        <v>0.545</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3670,28 +3670,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E72" s="3" t="n">
-        <v>-0.0667</v>
+        <v>2.69</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1530700</v>
+        <v>1996800</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H72" t="n">
-        <v>52.01</v>
+        <v>44.85</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.569</v>
+        <v>2.755</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0.473</v>
+        <v>2.741</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3715,28 +3715,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E73" s="8" t="n">
-        <v>0.0037</v>
+        <v>0.45</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1512500</v>
+        <v>1937200</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.12</v>
+        <v>0.26</v>
       </c>
       <c r="H73" t="n">
-        <v>45.7</v>
+        <v>27.78</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>2.756</v>
+        <v>0.493</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>2.741</v>
+        <v>0.552</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3760,39 +3760,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E74" s="8" t="n">
-        <v>0.0476</v>
+        <v>0.76</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1499200</v>
+        <v>1928200</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.71</v>
+        <v>0.23</v>
       </c>
       <c r="H74" t="n">
-        <v>61.36</v>
-      </c>
-      <c r="I74" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47</v>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.419</v>
+        <v>0.77</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.433</v>
+        <v>0.771</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         <v>0.009000000000000001</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1478400</v>
+        <v>1893800</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.72</v>
+        <v>0.93</v>
       </c>
       <c r="H75" t="n">
         <v>48.48</v>
@@ -3850,39 +3850,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E76" s="3" t="n">
-        <v>-0.0385</v>
+        <v>0.23</v>
+      </c>
+      <c r="E76" s="8" t="n">
+        <v>0.0698</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1434100</v>
+        <v>1825500</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.2</v>
+        <v>1.79</v>
       </c>
       <c r="H76" t="n">
-        <v>38.79</v>
-      </c>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.56</v>
+      </c>
+      <c r="I76" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.271</v>
+        <v>0.21</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.292</v>
+        <v>0.21</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3895,28 +3895,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.51</v>
+        <v>1.07</v>
       </c>
       <c r="E77" s="3" t="n">
-        <v>-0.0097</v>
+        <v>-0.0183</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1400100</v>
+        <v>1765400</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="H77" t="n">
-        <v>31.58</v>
+        <v>49.53</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.54</v>
+        <v>1.077</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.569</v>
+        <v>1.047</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.63</v>
+        <v>0.835</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>-0.0233</v>
+        <v>-0.0118</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1391500</v>
+        <v>1727400</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.16</v>
+        <v>0.57</v>
       </c>
       <c r="H78" t="n">
-        <v>40</v>
+        <v>15.99</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.674</v>
+        <v>0.908</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.97</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3985,28 +3985,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>-0.0227</v>
+        <v>2.47</v>
+      </c>
+      <c r="E79" s="8" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1383900</v>
+        <v>1726500</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>1.84</v>
+        <v>0.15</v>
       </c>
       <c r="H79" t="n">
-        <v>42.03</v>
+        <v>54.36</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.223</v>
+        <v>2.448</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.232</v>
+        <v>2.392</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4030,28 +4030,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E80" s="8" t="n">
-        <v>0.0123</v>
+        <v>0.515</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1383500</v>
+        <v>1688500</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.15</v>
+        <v>0.63</v>
       </c>
       <c r="H80" t="n">
-        <v>42.88</v>
+        <v>33.15</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.435</v>
+        <v>0.54</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.435</v>
+        <v>0.569</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4075,39 +4075,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>-0.0275</v>
+        <v>1.94</v>
+      </c>
+      <c r="E81" s="8" t="n">
+        <v>0.0211</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1380900</v>
+        <v>1670500</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
       <c r="H81" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.67</v>
+      </c>
+      <c r="I81" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.076</v>
+        <v>1.922</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1.046</v>
+        <v>1.95</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4120,28 +4120,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.825</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>-0.0237</v>
+        <v>-0.0583</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1335100</v>
+        <v>1629600</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.44</v>
+        <v>0.28</v>
       </c>
       <c r="H82" t="n">
-        <v>14.93</v>
+        <v>52.71</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.907</v>
+        <v>0.57</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.969</v>
+        <v>0.473</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>2.46</v>
+        <v>0.435</v>
       </c>
       <c r="E83" s="8" t="n">
-        <v>0.008199999999999999</v>
+        <v>0.0357</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1323300</v>
+        <v>1622500</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.12</v>
+        <v>0.76</v>
       </c>
       <c r="H83" t="n">
-        <v>53.17</v>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.96</v>
+      </c>
+      <c r="I83" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>2.447</v>
+        <v>0.419</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2.392</v>
+        <v>0.433</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4210,39 +4210,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0</v>
+        <v>5.57</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1303400</v>
+        <v>1604900</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.08</v>
+        <v>0.21</v>
       </c>
       <c r="H84" t="n">
-        <v>45.7</v>
-      </c>
-      <c r="I84" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.95</v>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>2.104</v>
+        <v>5.872</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>2.102</v>
+        <v>6.163</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4255,28 +4255,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.25</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>-0.0385</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1291300</v>
+        <v>1541000</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.52</v>
+        <v>0.22</v>
       </c>
       <c r="H85" t="n">
-        <v>58.96</v>
+        <v>38.79</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.741</v>
+        <v>0.271</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.705</v>
+        <v>0.292</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4300,39 +4300,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.0195</v>
+      </c>
+      <c r="F86" s="4" t="n">
+        <v>1537900</v>
+      </c>
+      <c r="G86" s="5" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H86" t="n">
+        <v>58.96</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K86" s="2" t="n">
         <v>0.705</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>-0.006999999999999999</v>
-      </c>
-      <c r="F86" s="4" t="n">
-        <v>1274100</v>
-      </c>
-      <c r="G86" s="5" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H86" t="n">
-        <v>40.67</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="n">
-        <v>0.728</v>
-      </c>
-      <c r="K86" s="2" t="n">
-        <v>0.744</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4345,39 +4345,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SKYWLD</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
         <v>0.335</v>
       </c>
-      <c r="E87" s="8" t="n">
-        <v>0.0152</v>
+      <c r="E87" s="3" t="n">
+        <v>-0.08220000000000001</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1271300</v>
+        <v>1465300</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.27</v>
+        <v>1.26</v>
       </c>
       <c r="H87" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="I87" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.71</v>
+      </c>
+      <c r="I87" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.335</v>
+        <v>0.379</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.343</v>
+        <v>0.391</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4390,28 +4390,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.59</v>
+        <v>1.21</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>-0.008399999999999999</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1267800</v>
+        <v>1437800</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="H88" t="n">
-        <v>49.02</v>
+        <v>22.97</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.597</v>
+        <v>1.375</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.586</v>
+        <v>1.551</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4435,28 +4435,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0261</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.35</v>
+        <v>0.63</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>-0.1566</v>
+        <v>-0.0233</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1249600</v>
+        <v>1436900</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>2.63</v>
+        <v>0.16</v>
       </c>
       <c r="H89" t="n">
-        <v>42.14</v>
+        <v>40</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.379</v>
+        <v>0.674</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.364</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4480,28 +4480,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.455</v>
+        <v>0.41</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>0.0111</v>
+        <v>0.0123</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1239800</v>
+        <v>1418100</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H90" t="n">
-        <v>30.38</v>
+        <v>42.88</v>
       </c>
       <c r="I90" s="6" t="inlineStr">
         <is>
@@ -4509,10 +4509,10 @@
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.493</v>
+        <v>0.435</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.552</v>
+        <v>0.435</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4525,39 +4525,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0</v>
+        <v>6.74</v>
+      </c>
+      <c r="E91" s="8" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1239300</v>
+        <v>1414500</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1.33</v>
+        <v>0.14</v>
       </c>
       <c r="H91" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.54</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.276</v>
+        <v>7.164</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.268</v>
+        <v>7.582</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4570,28 +4570,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>5.59</v>
-      </c>
-      <c r="E92" s="3" t="n">
-        <v>-0.0032</v>
+        <v>0.71</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1192000</v>
+        <v>1402500</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.16</v>
+        <v>0.73</v>
       </c>
       <c r="H92" t="n">
-        <v>28.6</v>
+        <v>42.1</v>
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>5.874</v>
+        <v>0.728</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>6.164</v>
+        <v>0.744</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4615,39 +4615,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.585</v>
+        <v>0.215</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>-0.0168</v>
+        <v>-0.0227</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1181300</v>
+        <v>1383900</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.29</v>
+        <v>1.84</v>
       </c>
       <c r="H93" t="n">
-        <v>67.13</v>
-      </c>
-      <c r="I93" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.03</v>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.517</v>
+        <v>0.223</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.472</v>
+        <v>0.232</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4660,39 +4660,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E94" s="3" t="n">
-        <v>-0.008199999999999999</v>
+        <v>2.09</v>
+      </c>
+      <c r="E94" s="8" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1153500</v>
+        <v>1365800</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.26</v>
+        <v>0.08</v>
       </c>
       <c r="H94" t="n">
-        <v>22.97</v>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.56</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>1.375</v>
+        <v>2.105</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>1.551</v>
+        <v>2.102</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4705,39 +4705,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>6.73</v>
+        <v>0.335</v>
       </c>
       <c r="E95" s="8" t="n">
-        <v>0.0075</v>
+        <v>0.0152</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1133700</v>
+        <v>1348900</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.11</v>
+        <v>0.28</v>
       </c>
       <c r="H95" t="n">
-        <v>31.09</v>
-      </c>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.93</v>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>7.163</v>
+        <v>0.335</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>7.581</v>
+        <v>0.343</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4750,28 +4750,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0261</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.39</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0602</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1131700</v>
+        <v>1321800</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.32</v>
+        <v>2.78</v>
       </c>
       <c r="H96" t="n">
-        <v>48.87</v>
+        <v>55.36</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.825</v>
+        <v>0.383</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.784</v>
+        <v>0.365</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.385</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E97" s="3" t="n">
-        <v>-0.0128</v>
+        <v>-0.0121</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1126000</v>
+        <v>1289800</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.45</v>
+        <v>0.37</v>
       </c>
       <c r="H97" t="n">
-        <v>48.59</v>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.71</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.388</v>
+        <v>0.825</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.39</v>
+        <v>0.785</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4840,28 +4840,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>2.4</v>
+        <v>0.585</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>-0.04</v>
+        <v>-0.0168</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1112000</v>
+        <v>1279000</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="H98" t="n">
-        <v>29.66</v>
+        <v>47.87</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>2.769</v>
+        <v>0.597</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>2.879</v>
+        <v>0.586</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4894,19 +4894,19 @@
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.0152</v>
+        <v>-0.0101</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1104600</v>
+        <v>1263900</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="H99" t="n">
-        <v>50.43</v>
+        <v>51.12</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>3.955</v>
+        <v>3.957</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>3.572</v>
@@ -4945,10 +4945,10 @@
         <v>0</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1101000</v>
+        <v>1243500</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.37</v>
+        <v>0.41</v>
       </c>
       <c r="H100" t="n">
         <v>35.65</v>
@@ -4975,39 +4975,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E101" s="3" t="n">
-        <v>-0.0207</v>
+        <v>0.28</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1064000</v>
+        <v>1239300</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="H101" t="n">
-        <v>32.08</v>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.75</v>
+      </c>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>1.495</v>
+        <v>0.276</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>1.503</v>
+        <v>0.268</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5020,28 +5020,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.635</v>
+        <v>2.85</v>
       </c>
       <c r="E102" s="3" t="n">
-        <v>-0.0451</v>
+        <v>-0.0035</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1063700</v>
+        <v>1227400</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.32</v>
+        <v>0.13</v>
       </c>
       <c r="H102" t="n">
-        <v>31.55</v>
+        <v>55.12</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.716</v>
+        <v>2.802</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.743</v>
+        <v>2.672</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5065,39 +5065,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>2.85</v>
+        <v>0.585</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-0.0035</v>
+        <v>-0.0168</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1004400</v>
+        <v>1214800</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H103" t="n">
-        <v>55.12</v>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.13</v>
+      </c>
+      <c r="I103" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>2.802</v>
+        <v>0.517</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>2.672</v>
+        <v>0.472</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5110,28 +5110,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="E104" s="8" t="n">
-        <v>0.0051</v>
+        <v>0.965</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1001800</v>
+        <v>1204400</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.08</v>
+        <v>0.2</v>
       </c>
       <c r="H104" t="n">
-        <v>44.98</v>
+        <v>64.12</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>9.996</v>
+        <v>0.929</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>10.137</v>
+        <v>0.88</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5155,28 +5155,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.725</v>
+        <v>2.38</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>-0.0268</v>
+        <v>-0.048</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>996400</v>
+        <v>1201000</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H105" t="n">
-        <v>49.44</v>
+        <v>29.11</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.741</v>
+        <v>2.768</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.679</v>
+        <v>2.879</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5200,28 +5200,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1.19</v>
+        <v>0.275</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.0083</v>
+        <v>-0.0179</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>972900</v>
+        <v>1189600</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.28</v>
+        <v>0.2</v>
       </c>
       <c r="H106" t="n">
-        <v>48.39</v>
+        <v>20.38</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>1.235</v>
+        <v>0.327</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>1.076</v>
+        <v>0.369</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5245,28 +5245,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>6.46</v>
-      </c>
-      <c r="E107" s="3" t="n">
-        <v>-0.0137</v>
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E107" s="8" t="n">
+        <v>0.0051</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>966100</v>
+        <v>1179000</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="H107" t="n">
-        <v>56.07</v>
+        <v>44.98</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>6.204</v>
+        <v>9.996</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>5.93</v>
+        <v>10.137</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5290,28 +5290,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>2.55</v>
+        <v>4.99</v>
       </c>
       <c r="E108" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>938700</v>
+        <v>1173100</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.16</v>
+        <v>0.3</v>
       </c>
       <c r="H108" t="n">
-        <v>45.14</v>
+        <v>45.7</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>2.603</v>
+        <v>5.052</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>2.61</v>
+        <v>5.053</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5335,28 +5335,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>0</v>
+        <v>1.42</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>-0.0207</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>936900</v>
+        <v>1142700</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.53</v>
+        <v>1.52</v>
       </c>
       <c r="H109" t="n">
-        <v>51.22</v>
+        <v>32.08</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.915</v>
+        <v>1.495</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.879</v>
+        <v>1.503</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5380,39 +5380,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1.23</v>
+        <v>0.385</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>-0.0315</v>
+        <v>-0.0128</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>934900</v>
+        <v>1126000</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="H110" t="n">
-        <v>46.57</v>
-      </c>
-      <c r="I110" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.59</v>
+      </c>
+      <c r="I110" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.282</v>
+        <v>0.388</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1.228</v>
+        <v>0.39</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5440,10 +5440,10 @@
         <v>-0.018</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>928800</v>
+        <v>1104000</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H111" t="n">
         <v>41.92</v>
@@ -5470,28 +5470,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>1.16</v>
+        <v>0.725</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>-0.0169</v>
+        <v>-0.0268</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>901000</v>
+        <v>1084000</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="H112" t="n">
-        <v>49.53</v>
+        <v>49.44</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>1.169</v>
+        <v>0.741</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>1.139</v>
+        <v>0.679</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5515,39 +5515,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E113" s="10" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>-0.0451</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>897900</v>
+        <v>1073700</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="H113" t="n">
-        <v>68.05</v>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.55</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.93</v>
+        <v>0.716</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.88</v>
+        <v>0.743</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5560,39 +5560,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.76</v>
+        <v>6.46</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-0.0194</v>
+        <v>-0.0137</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>893100</v>
+        <v>1067000</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.39</v>
+        <v>0.18</v>
       </c>
       <c r="H114" t="n">
-        <v>62.26</v>
-      </c>
-      <c r="I114" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.07</v>
+      </c>
+      <c r="I114" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.733</v>
+        <v>6.204</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.652</v>
+        <v>5.93</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5620,10 +5620,10 @@
         <v>0</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>892100</v>
+        <v>1036600</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
       <c r="H115" t="n">
         <v>58.81</v>
@@ -5650,28 +5650,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1.27</v>
+        <v>3.78</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>-0.0379</v>
+        <v>-0.0182</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>858500</v>
+        <v>1030000</v>
       </c>
       <c r="G116" s="5" t="n">
         <v>0.35</v>
       </c>
       <c r="H116" t="n">
-        <v>52.97</v>
+        <v>48.34</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>1.262</v>
+        <v>3.844</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>1.176</v>
+        <v>3.699</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5695,39 +5695,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.63</v>
+        <v>1.19</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0083</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>842400</v>
+        <v>1021500</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.38</v>
+        <v>0.3</v>
       </c>
       <c r="H117" t="n">
-        <v>47.44</v>
-      </c>
-      <c r="I117" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.39</v>
+      </c>
+      <c r="I117" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.637</v>
+        <v>1.235</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.624</v>
+        <v>1.076</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5740,28 +5740,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>0</v>
+        <v>1.22</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>-0.0394</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>796900</v>
+        <v>1016400</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.39</v>
+        <v>0.33</v>
       </c>
       <c r="H118" t="n">
-        <v>40.19</v>
+        <v>45.85</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.364</v>
+        <v>1.281</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.342</v>
+        <v>1.228</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5785,28 +5785,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>4.81</v>
+        <v>0.985</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0343</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>788700</v>
+        <v>995300</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.03</v>
+        <v>0.25</v>
       </c>
       <c r="H119" t="n">
-        <v>46.62</v>
+        <v>44.23</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>4.894</v>
+        <v>1.039</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>4.736</v>
+        <v>0.949</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5830,28 +5830,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="E120" s="3" t="n">
-        <v>-0.0182</v>
+        <v>2.55</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>766600</v>
+        <v>976700</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.26</v>
+        <v>0.16</v>
       </c>
       <c r="H120" t="n">
-        <v>48.34</v>
+        <v>45.14</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>3.844</v>
+        <v>2.603</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>3.699</v>
+        <v>2.61</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5875,39 +5875,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0</v>
+        <v>4.81</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>716200</v>
+        <v>947600</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="H121" t="n">
-        <v>58.91</v>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.62</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>2.231</v>
+        <v>4.894</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>2.175</v>
+        <v>4.736</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5920,28 +5920,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="E122" s="3" t="n">
-        <v>-0.0066</v>
+        <v>0.915</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>689100</v>
+        <v>936900</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.23</v>
+        <v>0.53</v>
       </c>
       <c r="H122" t="n">
-        <v>50.71</v>
+        <v>51.22</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>3.025</v>
+        <v>0.915</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>2.859</v>
+        <v>0.879</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5965,28 +5965,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0</v>
+        <v>0.755</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>-0.0258</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>688800</v>
+        <v>931100</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.1</v>
+        <v>0.41</v>
       </c>
       <c r="H123" t="n">
-        <v>27.88</v>
+        <v>60.75</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.719</v>
+        <v>0.732</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.786</v>
+        <v>0.652</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6010,28 +6010,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>4.96</v>
+        <v>1.16</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-0.006</v>
+        <v>-0.0169</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>675800</v>
+        <v>918800</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="H124" t="n">
-        <v>43.82</v>
+        <v>49.53</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>5.049</v>
+        <v>1.169</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>5.052</v>
+        <v>1.139</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6055,39 +6055,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>0.0068</v>
+        <v>1.29</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>660300</v>
+        <v>898000</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.13</v>
+        <v>0.37</v>
       </c>
       <c r="H125" t="n">
-        <v>52.02</v>
-      </c>
-      <c r="I125" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.96</v>
+      </c>
+      <c r="I125" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>4.363</v>
+        <v>1.264</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>4.43</v>
+        <v>1.176</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6100,39 +6100,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>PARADIGM</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.8</v>
+        <v>0.63</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>-0.0062</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>656600</v>
+        <v>842400</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>1.71</v>
+        <v>0.38</v>
       </c>
       <c r="H126" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="I126" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.44</v>
+      </c>
+      <c r="I126" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.819</v>
+        <v>0.637</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.848</v>
+        <v>0.624</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6145,39 +6145,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E127" s="3" t="n">
-        <v>-0.0294</v>
+        <v>2.33</v>
+      </c>
+      <c r="E127" s="8" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>642500</v>
+        <v>812100</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H127" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.34</v>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>1.04</v>
+        <v>2.233</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.949</v>
+        <v>2.175</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6190,28 +6190,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>-0.0315</v>
+        <v>1.34</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>642000</v>
+        <v>796900</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.29</v>
+        <v>0.39</v>
       </c>
       <c r="H128" t="n">
-        <v>40.82</v>
+        <v>40.19</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.316</v>
+        <v>1.364</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1.288</v>
+        <v>1.342</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6235,39 +6235,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>-0.0152</v>
+        <v>0.675</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>641900</v>
+        <v>770800</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.23</v>
+        <v>0.11</v>
       </c>
       <c r="H129" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.88</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.646</v>
+        <v>0.719</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.786</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6280,28 +6280,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>1.27</v>
+        <v>7.15</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>-0.0231</v>
+        <v>-0.0205</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>614700</v>
+        <v>763200</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="H130" t="n">
-        <v>22.86</v>
+        <v>47.94</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>1.39</v>
+        <v>7.332</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>1.459</v>
+        <v>6.905</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6325,28 +6325,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>7.16</v>
+        <v>2.99</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>-0.0192</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>611200</v>
+        <v>752600</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="H131" t="n">
-        <v>48.15</v>
+        <v>50.24</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>7.333</v>
+        <v>3.024</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>6.905</v>
+        <v>2.858</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6370,39 +6370,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.65</v>
+        <v>1.23</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>-0.0076</v>
+        <v>-0.0315</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>582800</v>
+        <v>723200</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.53</v>
+        <v>0.33</v>
       </c>
       <c r="H132" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="I132" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.82</v>
+      </c>
+      <c r="I132" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.585</v>
+        <v>1.316</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.532</v>
+        <v>1.288</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6415,39 +6415,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>4.44</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>581200</v>
+        <v>712400</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.26</v>
+        <v>0.13</v>
       </c>
       <c r="H133" t="n">
-        <v>38.72</v>
-      </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.4</v>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.602</v>
+        <v>4.364</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0.63</v>
+        <v>4.43</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6475,10 +6475,10 @@
         <v>-0.0124</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>572100</v>
+        <v>709400</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H134" t="n">
         <v>34.54</v>
@@ -6505,28 +6505,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>1.68</v>
+        <v>0.585</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.0175</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>567000</v>
+        <v>691200</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.1</v>
+        <v>0.31</v>
       </c>
       <c r="H135" t="n">
-        <v>32.26</v>
+        <v>38.72</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>1.764</v>
+        <v>0.602</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>1.881</v>
+        <v>0.63</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         <v>0</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>533100</v>
+        <v>687900</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="H136" t="n">
         <v>59.68</v>
@@ -6595,28 +6595,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E137" s="10" t="n">
-        <v>0</v>
+        <v>5.23</v>
+      </c>
+      <c r="E137" s="3" t="n">
+        <v>-0.0113</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>525000</v>
+        <v>674900</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.47</v>
+        <v>0.53</v>
       </c>
       <c r="H137" t="n">
-        <v>45.03</v>
+        <v>31.94</v>
       </c>
       <c r="I137" s="6" t="inlineStr">
         <is>
@@ -6624,10 +6624,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.631</v>
+        <v>5.464</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.631</v>
+        <v>5.8</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6640,39 +6640,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="E138" s="8" t="n">
-        <v>0.0307</v>
+        <v>0.65</v>
+      </c>
+      <c r="E138" s="3" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>523300</v>
+        <v>674600</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="H138" t="n">
-        <v>34.41</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.56</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.89</v>
+        <v>0.646</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.949</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6685,45 +6685,630 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.905</v>
+        <v>0.65</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.0076</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>500800</v>
+        <v>664100</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.29</v>
+        <v>0.6</v>
       </c>
       <c r="H139" t="n">
-        <v>32.37</v>
-      </c>
-      <c r="I139" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.56</v>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.585</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.999</v>
+        <v>0.532</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>5338</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>PARADIGM</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F140" s="4" t="n">
+        <v>656600</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H140" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K140" s="2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>0.0307</v>
+      </c>
+      <c r="F141" s="4" t="n">
+        <v>637200</v>
+      </c>
+      <c r="G141" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H141" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J141" s="2" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K141" s="2" t="n">
+        <v>0.949</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E142" s="3" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F142" s="4" t="n">
+        <v>622700</v>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H142" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="2" t="n">
+        <v>1.764</v>
+      </c>
+      <c r="K142" s="2" t="n">
+        <v>1.881</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E143" s="3" t="n">
+        <v>-0.0154</v>
+      </c>
+      <c r="F143" s="4" t="n">
+        <v>619300</v>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H143" t="n">
+        <v>23.72</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="n">
+        <v>1.391</v>
+      </c>
+      <c r="K143" s="2" t="n">
+        <v>1.459</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="4" t="n">
+        <v>595000</v>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H144" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="I144" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J144" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K144" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E145" s="3" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="F145" s="4" t="n">
+        <v>594900</v>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="H145" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J145" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K145" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>TAKAFUL</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E146" s="3" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F146" s="4" t="n">
+        <v>592200</v>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H146" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="I146" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="2" t="n">
+        <v>2.916</v>
+      </c>
+      <c r="K146" s="2" t="n">
+        <v>3.056</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="E147" s="3" t="n">
+        <v>-0.0075</v>
+      </c>
+      <c r="F147" s="4" t="n">
+        <v>562400</v>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H147" t="n">
+        <v>37.7</v>
+      </c>
+      <c r="I147" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J147" s="2" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K147" s="2" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>TIMECOM</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="E148" s="8" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F148" s="4" t="n">
+        <v>549400</v>
+      </c>
+      <c r="G148" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H148" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="I148" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="2" t="n">
+        <v>5.554</v>
+      </c>
+      <c r="K148" s="2" t="n">
+        <v>5.793</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F149" s="4" t="n">
+        <v>543500</v>
+      </c>
+      <c r="G149" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H149" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="I149" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>1.113</v>
+      </c>
+      <c r="K149" s="2" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>-0.0242</v>
+      </c>
+      <c r="F150" s="4" t="n">
+        <v>522200</v>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H150" t="n">
+        <v>40.73</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
+        <v>4.261</v>
+      </c>
+      <c r="K150" s="2" t="n">
+        <v>4.314</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="F151" s="4" t="n">
+        <v>505600</v>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H151" t="n">
+        <v>54.94</v>
+      </c>
+      <c r="I151" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="2" t="n">
+        <v>10.423</v>
+      </c>
+      <c r="K151" s="2" t="n">
+        <v>9.782999999999999</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>4383</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>JTIASA</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>0.905</v>
+      </c>
+      <c r="E152" s="3" t="n">
+        <v>-0.005500000000000001</v>
+      </c>
+      <c r="F152" s="4" t="n">
+        <v>500800</v>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H152" t="n">
+        <v>32.37</v>
+      </c>
+      <c r="I152" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J152" s="2" t="n">
+        <v>0.9409999999999999</v>
+      </c>
+      <c r="K152" s="2" t="n">
+        <v>0.999</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M139"/>
+  <autoFilter ref="A1:M152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
+++ b/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-20" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -558,10 +558,10 @@
         <v>-0.0294</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>41878100</v>
+        <v>47320400</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H2" t="n">
         <v>63.6</v>
@@ -603,10 +603,10 @@
         <v>0.0562</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>34456200</v>
+        <v>35686100</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.99</v>
+        <v>1.03</v>
       </c>
       <c r="H3" t="n">
         <v>81.92</v>
@@ -633,39 +633,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0138</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ZETRIX</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0</v>
+        <v>0.9</v>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>0.0112</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>26710100</v>
+        <v>31936300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="H4" t="n">
-        <v>22.63</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.36</v>
+      </c>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.116</v>
+        <v>0.834</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0.309</v>
+        <v>0.742</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="7" t="inlineStr"/>
@@ -678,39 +678,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>ZETRIX</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>-0.0112</v>
+        <v>0.05</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>24867000</v>
+        <v>28264000</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.35</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>62.03</v>
-      </c>
-      <c r="I5" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>22.63</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>0.832</v>
+        <v>0.116</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>0.741</v>
+        <v>0.309</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="7" t="inlineStr"/>
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>-0.0745</v>
+        <v>-0.0559</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>18736000</v>
+        <v>22245300</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>3.74</v>
+        <v>4.44</v>
       </c>
       <c r="H6" t="n">
-        <v>25.37</v>
+        <v>27.02</v>
       </c>
       <c r="I6" s="6" t="inlineStr">
         <is>
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="J6" s="2" t="n">
-        <v>1.7</v>
+        <v>1.703</v>
       </c>
       <c r="K6" s="2" t="n">
         <v>1.761</v>
@@ -768,39 +768,39 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.705</v>
+        <v>0.4</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.0217</v>
+        <v>0.1111</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17419600</v>
+        <v>17856300</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.94</v>
       </c>
       <c r="H7" t="n">
-        <v>80.01000000000001</v>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.68</v>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>0.626</v>
+        <v>0.51</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0.537</v>
+        <v>0.607</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="7" t="inlineStr"/>
@@ -813,39 +813,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.395</v>
+        <v>0.705</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.09720000000000001</v>
+        <v>0.0217</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>16275400</v>
+        <v>17465400</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>1.77</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>80.01000000000001</v>
+      </c>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>0.51</v>
+        <v>0.626</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0.607</v>
+        <v>0.537</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="7" t="inlineStr"/>
@@ -867,19 +867,19 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.455</v>
+        <v>0.46</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>-0.1078</v>
+        <v>-0.098</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>15585800</v>
+        <v>16315300</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="H9" t="n">
-        <v>40.96</v>
+        <v>41.67</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.513</v>
+        <v>0.514</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0.463</v>
@@ -918,10 +918,10 @@
         <v>0</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>12685100</v>
+        <v>16135400</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="H10" t="n">
         <v>48.61</v>
@@ -948,40 +948,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.265</v>
+        <v>0.095</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.0364</v>
+        <v>-0.2083</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>11785700</v>
+        <v>14867000</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="H11" t="n">
-        <v>38.24</v>
+        <v>0.38</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="K11" s="2" t="n">
-        <v>0.28</v>
-      </c>
+      <c r="J11" s="2" t="n"/>
+      <c r="K11" s="2" t="n"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -993,28 +986,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.385</v>
+        <v>0.27</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.0128</v>
+        <v>-0.0182</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>10573700</v>
+        <v>13040900</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.06</v>
+        <v>1.33</v>
       </c>
       <c r="H12" t="n">
-        <v>28.49</v>
+        <v>39.85</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1022,10 +1015,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.396</v>
+        <v>0.295</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.406</v>
+        <v>0.28</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1038,39 +1031,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.305</v>
+        <v>0.82</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0.0161</v>
+        <v>-0.0061</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>9980600</v>
+        <v>11555100</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.52</v>
+        <v>0.73</v>
       </c>
       <c r="H13" t="n">
-        <v>47.44</v>
-      </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.61</v>
+      </c>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.308</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.301</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1083,33 +1076,40 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.1</v>
+        <v>0.305</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>-0.1667</v>
+        <v>-0.0161</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>9880600</v>
+        <v>11273800</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.25</v>
+        <v>0.59</v>
+      </c>
+      <c r="H14" t="n">
+        <v>47.44</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
+      <c r="J14" s="2" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>0.301</v>
+      </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
     </row>
@@ -1121,33 +1121,40 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>9375000</v>
+        <v>11096800</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.4</v>
+        <v>1.11</v>
+      </c>
+      <c r="H15" t="n">
+        <v>28.49</v>
       </c>
       <c r="I15" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J15" s="2" t="n"/>
-      <c r="K15" s="2" t="n"/>
+      <c r="J15" s="2" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>0.406</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
     </row>
@@ -1159,37 +1166,32 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.39</v>
+        <v>0.765</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0.06849999999999999</v>
+        <v>0.0132</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>9296400</v>
+        <v>10138500</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="H16" t="n">
-        <v>69.2</v>
-      </c>
-      <c r="I16" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="n">
-        <v>0.326</v>
-      </c>
+        <v>0.17</v>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n"/>
       <c r="K16" s="2" t="n"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
@@ -1202,40 +1204,33 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E17" s="3" t="n">
-        <v>-0.0115</v>
+        <v>0.25</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>8410400</v>
+        <v>9941900</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H17" t="n">
-        <v>35.32</v>
+        <v>0.42</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J17" s="2" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="K17" s="2" t="n">
-        <v>0.481</v>
-      </c>
+      <c r="J17" s="2" t="n"/>
+      <c r="K17" s="2" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="7" t="inlineStr"/>
     </row>
@@ -1247,28 +1242,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E18" s="3" t="n">
-        <v>-0.0061</v>
+        <v>0.39</v>
+      </c>
+      <c r="E18" s="8" t="n">
+        <v>0.06849999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>8052400</v>
+        <v>9931800</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.51</v>
+        <v>1.89</v>
       </c>
       <c r="H18" t="n">
-        <v>55.61</v>
+        <v>69.2</v>
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
@@ -1276,11 +1271,9 @@
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="K18" s="2" t="n">
-        <v>0.8110000000000001</v>
-      </c>
+        <v>0.326</v>
+      </c>
+      <c r="K18" s="2" t="n"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="7" t="inlineStr"/>
     </row>
@@ -1292,39 +1285,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E19" s="3" t="n">
-        <v>-0.0146</v>
+        <v>0.13</v>
+      </c>
+      <c r="E19" s="8" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>7884900</v>
+        <v>9888900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.27</v>
+        <v>1.03</v>
       </c>
       <c r="H19" t="n">
-        <v>58.58</v>
-      </c>
-      <c r="I19" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.88</v>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.941</v>
+        <v>0.126</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>1.754</v>
+        <v>0.102</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="7" t="inlineStr"/>
@@ -1337,33 +1330,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>7808000</v>
+        <v>9341700</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n"/>
-      <c r="K20" s="2" t="n"/>
+        <v>0.47</v>
+      </c>
+      <c r="H20" t="n">
+        <v>46.09</v>
+      </c>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>0.868</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>0.869</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
     </row>
@@ -1375,28 +1375,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
         <v>0.205</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>-0.0238</v>
+        <v>-0.04650000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>7581500</v>
+        <v>9272800</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.34</v>
+        <v>0.59</v>
       </c>
       <c r="H21" t="n">
-        <v>40.25</v>
+        <v>28.47</v>
       </c>
       <c r="I21" s="6" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>0.217</v>
+        <v>0.232</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0.234</v>
+        <v>0.282</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="7" t="inlineStr"/>
@@ -1420,28 +1420,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OCR</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.045</v>
+        <v>0.435</v>
       </c>
       <c r="E22" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>7400300</v>
+        <v>8424100</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>3</v>
+        <v>0.23</v>
       </c>
       <c r="H22" t="n">
-        <v>29.14</v>
+        <v>36.45</v>
       </c>
       <c r="I22" s="6" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.049</v>
+        <v>0.473</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.05</v>
+        <v>0.481</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1465,28 +1465,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>2.04</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>7183100</v>
+        <v>8368100</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.47</v>
+        <v>0.29</v>
       </c>
       <c r="H23" t="n">
-        <v>49.91</v>
+        <v>60.07</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.775</v>
+        <v>1.943</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.776</v>
+        <v>1.754</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1510,28 +1510,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>0.0588</v>
+        <v>0.205</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>6940100</v>
+        <v>8357700</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>1.34</v>
+        <v>0.37</v>
       </c>
       <c r="H24" t="n">
-        <v>56.69</v>
+        <v>40.25</v>
       </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.175</v>
+        <v>0.217</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0.182</v>
+        <v>0.234</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="7" t="inlineStr"/>
@@ -1555,28 +1555,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>2.54</v>
+        <v>0.97</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-0.0193</v>
+        <v>-0.0251</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>6851800</v>
+        <v>8286000</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.38</v>
+        <v>1.02</v>
       </c>
       <c r="H25" t="n">
-        <v>45.11</v>
+        <v>41.14</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2.634</v>
+        <v>1.042</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>2.556</v>
+        <v>0.964</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1600,39 +1600,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E26" s="3" t="n">
-        <v>-0.0172</v>
+        <v>0.775</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>6474400</v>
+        <v>7990100</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>1.02</v>
+        <v>0.52</v>
       </c>
       <c r="H26" t="n">
-        <v>35.29</v>
-      </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.91</v>
+      </c>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.312</v>
+        <v>0.775</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.334</v>
+        <v>0.776</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1645,39 +1645,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PUNCAK</t>
+          <t>OCR</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E27" s="8" t="n">
-        <v>0.0256</v>
+        <v>0.045</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>6389400</v>
+        <v>7400300</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>16.77</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>82.42</v>
-      </c>
-      <c r="I27" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.14</v>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.177</v>
+        <v>0.049</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.171</v>
+        <v>0.05</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1690,39 +1690,39 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.865</v>
+        <v>0.285</v>
       </c>
       <c r="E28" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0172</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>6326000</v>
+        <v>7189400</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.32</v>
+        <v>1.14</v>
       </c>
       <c r="H28" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I28" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.29</v>
+      </c>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.868</v>
+        <v>0.312</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.869</v>
+        <v>0.334</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1735,28 +1735,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.535</v>
+        <v>2.55</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.0273</v>
+        <v>-0.0154</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>6185500</v>
+        <v>7109400</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.3</v>
+        <v>0.39</v>
       </c>
       <c r="H29" t="n">
-        <v>44.44</v>
+        <v>45.65</v>
       </c>
       <c r="I29" s="6" t="inlineStr">
         <is>
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.57</v>
+        <v>2.635</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.543</v>
+        <v>2.556</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1780,28 +1780,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.98</v>
+        <v>0.44</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-0.0151</v>
+        <v>-0.033</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>6093900</v>
+        <v>7053900</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.75</v>
+        <v>0.31</v>
       </c>
       <c r="H30" t="n">
-        <v>42.3</v>
+        <v>25.77</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.043</v>
+        <v>0.501</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.964</v>
+        <v>0.665</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1825,28 +1825,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.033</v>
+        <v>-0.0182</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>5914200</v>
+        <v>7014900</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H31" t="n">
-        <v>25.77</v>
+        <v>45.28</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.501</v>
+        <v>0.57</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.665</v>
+        <v>0.543</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1870,39 +1870,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.0303</v>
+        <v>0.0588</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>5845400</v>
+        <v>6986200</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>1.95</v>
+        <v>1.35</v>
       </c>
       <c r="H32" t="n">
-        <v>64.43000000000001</v>
-      </c>
-      <c r="I32" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.69</v>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.157</v>
+        <v>0.175</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.155</v>
+        <v>0.182</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,39 +1915,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E33" s="8" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>5721400</v>
+        <v>6648200</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="H33" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="I33" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.67</v>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.619</v>
+        <v>0.394</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.616</v>
+        <v>0.379</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,39 +1960,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>PUNCAK</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.415</v>
+        <v>0.2</v>
       </c>
       <c r="E34" s="8" t="n">
-        <v>0.0247</v>
+        <v>0.0256</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>5566400</v>
+        <v>6390800</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.46</v>
+        <v>16.77</v>
       </c>
       <c r="H34" t="n">
-        <v>57.67</v>
-      </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.42</v>
+      </c>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.394</v>
+        <v>0.177</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.379</v>
+        <v>0.171</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2005,39 +2005,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.665</v>
-      </c>
-      <c r="E35" s="3" t="n">
-        <v>-0.0828</v>
+        <v>0.63</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>5251600</v>
+        <v>6366600</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>1.02</v>
+        <v>0.58</v>
       </c>
       <c r="H35" t="n">
-        <v>38.29</v>
-      </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.52</v>
+      </c>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.751</v>
+        <v>0.619</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.616</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2050,28 +2050,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E36" s="8" t="n">
-        <v>0.0286</v>
+        <v>0.43</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>5028700</v>
+        <v>6008500</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H36" t="n">
-        <v>44.12</v>
+        <v>54.75</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.188</v>
+        <v>0.423</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.186</v>
+        <v>0.371</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2095,28 +2095,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.425</v>
+        <v>0.655</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>-0.0116</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>4848000</v>
+        <v>5990200</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.24</v>
+        <v>1.16</v>
       </c>
       <c r="H37" t="n">
-        <v>53.34</v>
+        <v>37.19</v>
       </c>
       <c r="I37" s="6" t="inlineStr">
         <is>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.423</v>
+        <v>0.75</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.37</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2140,39 +2140,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E38" s="3" t="n">
-        <v>-0.0143</v>
+        <v>0.17</v>
+      </c>
+      <c r="E38" s="8" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>4779400</v>
+        <v>5925400</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.62</v>
+        <v>1.98</v>
       </c>
       <c r="H38" t="n">
-        <v>48.17</v>
-      </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.353</v>
+        <v>0.157</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.328</v>
+        <v>0.155</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2185,39 +2185,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E39" s="8" t="n">
-        <v>0.0133</v>
+        <v>0.35</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>4605200</v>
+        <v>5162000</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
       <c r="H39" t="n">
-        <v>60.65</v>
-      </c>
-      <c r="I39" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.51</v>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.372</v>
+        <v>0.353</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.369</v>
+        <v>0.328</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2230,28 +2230,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E40" s="8" t="n">
-        <v>0.0833</v>
+        <v>0.175</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4362900</v>
+        <v>5065700</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.45</v>
+        <v>0.23</v>
       </c>
       <c r="H40" t="n">
-        <v>55.88</v>
+        <v>40.18</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.126</v>
+        <v>0.188</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.102</v>
+        <v>0.185</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2275,39 +2275,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E41" s="3" t="n">
-        <v>-0.0357</v>
+        <v>1.62</v>
+      </c>
+      <c r="E41" s="8" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>3950900</v>
+        <v>5057600</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.43</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>32.82</v>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.87</v>
+      </c>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>0.636</v>
+        <v>1.623</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0.619</v>
+        <v>1.689</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2320,28 +2320,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>4.72</v>
+        <v>0.38</v>
       </c>
       <c r="E42" s="8" t="n">
-        <v>0.0021</v>
+        <v>0.0133</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>3882900</v>
+        <v>4812200</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.19</v>
+        <v>0.65</v>
       </c>
       <c r="H42" t="n">
-        <v>47.71</v>
+        <v>60.65</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>4.728</v>
+        <v>0.372</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>4.84</v>
+        <v>0.369</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2374,19 +2374,19 @@
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0.0104</v>
+        <v>0.013</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>3763700</v>
+        <v>4417500</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
       <c r="H43" t="n">
-        <v>59.72</v>
+        <v>59.95</v>
       </c>
       <c r="I43" s="6" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>3.674</v>
+        <v>3.675</v>
       </c>
       <c r="K43" s="2" t="n">
         <v>3.057</v>
@@ -2410,39 +2410,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0</v>
+        <v>4.72</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>3578000</v>
+        <v>4392500</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.06</v>
+        <v>0.21</v>
       </c>
       <c r="H44" t="n">
-        <v>42.14</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.71</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.157</v>
+        <v>4.728</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.141</v>
+        <v>4.84</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         <v>-0.005</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>3573600</v>
+        <v>4332600</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="H45" t="n">
         <v>32.46</v>
@@ -2500,28 +2500,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0</v>
+        <v>7.27</v>
+      </c>
+      <c r="E46" s="8" t="n">
+        <v>0.0097</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>3536500</v>
+        <v>4328600</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="H46" t="n">
-        <v>36.42</v>
+        <v>35.91</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.227</v>
+        <v>7.436</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1.316</v>
+        <v>7.919</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2545,25 +2545,25 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7.26</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0.0083</v>
+        <v>1.16</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>3405000</v>
+        <v>4170500</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.34</v>
+        <v>0.53</v>
       </c>
       <c r="H47" t="n">
         <v>35.26</v>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7.435</v>
+        <v>1.226</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>7.919</v>
+        <v>1.316</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2590,39 +2590,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>-0.027</v>
+        <v>1.29</v>
+      </c>
+      <c r="E48" s="8" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>3376400</v>
+        <v>4132300</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.82</v>
+        <v>0.66</v>
       </c>
       <c r="H48" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.52</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.197</v>
+        <v>1.207</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.207</v>
+        <v>1.192</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2635,28 +2635,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.335</v>
+        <v>0.545</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>-0.0147</v>
+        <v>-0.0268</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3356500</v>
+        <v>4069400</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.35</v>
+        <v>0.44</v>
       </c>
       <c r="H49" t="n">
-        <v>47.18</v>
+        <v>33.38</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.345</v>
+        <v>0.637</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.335</v>
+        <v>0.619</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2680,28 +2680,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>-0.0179</v>
+        <v>0.34</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3322100</v>
+        <v>3969800</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="H50" t="n">
-        <v>44.46</v>
+        <v>49.14</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.289</v>
+        <v>0.346</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.283</v>
+        <v>0.335</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2725,39 +2725,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0</v>
+        <v>0.135</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>2908400</v>
+        <v>3878000</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.46</v>
+        <v>0.06</v>
       </c>
       <c r="H51" t="n">
-        <v>62.51</v>
-      </c>
-      <c r="I51" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.16</v>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>1.206</v>
+        <v>0.157</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1.192</v>
+        <v>0.141</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2770,39 +2770,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0.0062</v>
+        <v>0.115</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2874700</v>
+        <v>3865300</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.39</v>
+        <v>0.18</v>
       </c>
       <c r="H52" t="n">
-        <v>47.87</v>
-      </c>
-      <c r="I52" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.68</v>
+      </c>
+      <c r="I52" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.623</v>
+        <v>0.14</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1.689</v>
+        <v>0.149</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2815,39 +2815,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>2.03</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2834500</v>
+        <v>3774000</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.85</v>
+        <v>0.67</v>
       </c>
       <c r="H53" t="n">
-        <v>46.01</v>
-      </c>
-      <c r="I53" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>2.043</v>
+        <v>0.795</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>2.069</v>
+        <v>0.773</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2860,28 +2860,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>-0.013</v>
+        <v>0.165</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2823900</v>
+        <v>3512500</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>2.28</v>
+        <v>0.61</v>
       </c>
       <c r="H54" t="n">
-        <v>58.88</v>
+        <v>34.49</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.748</v>
+        <v>0.176</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.72</v>
+        <v>0.196</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         <v>-0.0115</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>2819200</v>
+        <v>3492700</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="H55" t="n">
         <v>52.29</v>
@@ -2950,28 +2950,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.84</v>
+        <v>0.18</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>-0.0345</v>
+        <v>-0.027</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>2783400</v>
+        <v>3416500</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.37</v>
+        <v>0.83</v>
       </c>
       <c r="H56" t="n">
-        <v>39.9</v>
+        <v>27.5</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.919</v>
+        <v>0.197</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.85</v>
+        <v>0.207</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2995,39 +2995,39 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0</v>
+        <v>0.275</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>2766200</v>
+        <v>3352100</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.49</v>
+        <v>0.29</v>
       </c>
       <c r="H57" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I57" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.46</v>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.795</v>
+        <v>0.289</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.773</v>
+        <v>0.283</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3040,28 +3040,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>5.33</v>
-      </c>
-      <c r="E58" s="8" t="n">
-        <v>0.0133</v>
+        <v>0.125</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>2718600</v>
+        <v>3336000</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.2</v>
+        <v>2.37</v>
       </c>
       <c r="H58" t="n">
-        <v>43.56</v>
+        <v>41.4</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>5.491</v>
+        <v>0.129</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>5.471</v>
+        <v>0.13</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3085,28 +3085,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.21</v>
+        <v>0.85</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>-0.0233</v>
+        <v>-0.023</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>2606300</v>
+        <v>3273500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.17</v>
+        <v>0.44</v>
       </c>
       <c r="H59" t="n">
-        <v>30.1</v>
+        <v>40.99</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.232</v>
+        <v>0.92</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.282</v>
+        <v>0.85</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3130,28 +3130,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>7.17</v>
+        <v>5.29</v>
       </c>
       <c r="E60" s="8" t="n">
-        <v>0.0028</v>
+        <v>0.005699999999999999</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>2572700</v>
+        <v>3257700</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.16</v>
+        <v>0.24</v>
       </c>
       <c r="H60" t="n">
-        <v>34.03</v>
+        <v>41.82</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>7.473</v>
+        <v>5.488</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>7.672</v>
+        <v>5.47</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3175,28 +3175,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>0.915</v>
+        <v>1.43</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.0069</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>2567900</v>
+        <v>3197600</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.63</v>
+        <v>0.28</v>
       </c>
       <c r="H61" t="n">
-        <v>58.69</v>
+        <v>21.73</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>0.848</v>
+        <v>1.668</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0.586</v>
+        <v>1.931</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3220,28 +3220,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>0.865</v>
+        <v>2.02</v>
       </c>
       <c r="E62" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0049</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>2563000</v>
+        <v>3004500</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="H62" t="n">
-        <v>51.48</v>
+        <v>44.31</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.865</v>
+        <v>2.042</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>0.86</v>
+        <v>2.069</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3274,19 +3274,19 @@
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>3.23</v>
+        <v>3.27</v>
       </c>
       <c r="E63" s="8" t="n">
-        <v>0.0264</v>
+        <v>0.0391</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2562500</v>
+        <v>2943300</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.8</v>
+        <v>0.92</v>
       </c>
       <c r="H63" t="n">
-        <v>85.70999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="I63" s="9" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.869</v>
+        <v>2.873</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>2.456</v>
@@ -3310,28 +3310,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E64" s="3" t="n">
-        <v>-0.0139</v>
+        <v>7.17</v>
+      </c>
+      <c r="E64" s="8" t="n">
+        <v>0.0028</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2543000</v>
+        <v>2909500</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="H64" t="n">
-        <v>21.35</v>
+        <v>34.03</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>1.667</v>
+        <v>7.473</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1.931</v>
+        <v>7.672</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3355,28 +3355,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.47</v>
+        <v>0.76</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.0208</v>
+        <v>-0.013</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2439700</v>
+        <v>2883400</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.28</v>
+        <v>2.33</v>
       </c>
       <c r="H65" t="n">
-        <v>36.31</v>
+        <v>58.88</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.503</v>
+        <v>0.748</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.523</v>
+        <v>0.72</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3400,28 +3400,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1.24</v>
+        <v>2.68</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>-0.008</v>
+        <v>-0.0037</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2365900</v>
+        <v>2791500</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="H66" t="n">
-        <v>39.92</v>
+        <v>44.15</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>1.293</v>
+        <v>2.754</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.314</v>
+        <v>2.741</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3454,19 +3454,19 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.41</v>
+        <v>0.405</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.04650000000000001</v>
+        <v>-0.0581</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2311100</v>
+        <v>2746200</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="H67" t="n">
-        <v>55.66</v>
+        <v>54.56</v>
       </c>
       <c r="I67" s="9" t="inlineStr">
         <is>
@@ -3490,28 +3490,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
         <v>0.915</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>-0.0161</v>
+        <v>-0.08039999999999999</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2252700</v>
+        <v>2705800</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.55</v>
+        <v>0.66</v>
       </c>
       <c r="H68" t="n">
-        <v>23.81</v>
+        <v>58.69</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.965</v>
+        <v>0.848</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>1.049</v>
+        <v>0.586</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3535,28 +3535,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0</v>
+        <v>0.91</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>-0.0215</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2249000</v>
+        <v>2684800</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.27</v>
+        <v>0.66</v>
       </c>
       <c r="H69" t="n">
-        <v>27.74</v>
+        <v>22.95</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.274</v>
+        <v>0.964</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0.3</v>
+        <v>1.048</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3589,19 +3589,19 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.54</v>
+        <v>0.525</v>
       </c>
       <c r="E70" s="3" t="n">
-        <v>-0.0092</v>
+        <v>-0.0367</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2104500</v>
+        <v>2646800</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.39</v>
+        <v>0.5</v>
       </c>
       <c r="H70" t="n">
-        <v>47.65</v>
+        <v>44.43</v>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
@@ -3609,7 +3609,7 @@
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.5570000000000001</v>
       </c>
       <c r="K70" s="2" t="n">
         <v>0.518</v>
@@ -3625,39 +3625,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.61</v>
+        <v>0.865</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>-0.0469</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2053500</v>
+        <v>2563000</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>11.45</v>
+        <v>0.84</v>
       </c>
       <c r="H71" t="n">
-        <v>65.78</v>
-      </c>
-      <c r="I71" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.48</v>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.545</v>
+        <v>0.86</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3670,28 +3670,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0</v>
+        <v>6.72</v>
+      </c>
+      <c r="E72" s="8" t="n">
+        <v>0.006</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>1996800</v>
+        <v>2543400</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.16</v>
+        <v>0.25</v>
       </c>
       <c r="H72" t="n">
-        <v>44.85</v>
+        <v>30.63</v>
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2.755</v>
+        <v>7.162</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>2.741</v>
+        <v>7.581</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3715,28 +3715,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0</v>
+        <v>0.835</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>1937200</v>
+        <v>2504200</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.26</v>
+        <v>0.83</v>
       </c>
       <c r="H73" t="n">
-        <v>27.78</v>
+        <v>15.99</v>
       </c>
       <c r="I73" s="6" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.493</v>
+        <v>0.908</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.552</v>
+        <v>0.97</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3760,28 +3760,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.76</v>
+        <v>0.465</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>-0.013</v>
+        <v>-0.0312</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>1928200</v>
+        <v>2482700</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.23</v>
+        <v>0.29</v>
       </c>
       <c r="H74" t="n">
-        <v>47</v>
+        <v>35.11</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.77</v>
+        <v>0.503</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.771</v>
+        <v>0.523</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3805,39 +3805,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E75" s="8" t="n">
-        <v>0.009000000000000001</v>
+        <v>1.24</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>1893800</v>
+        <v>2433800</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.93</v>
+        <v>0.28</v>
       </c>
       <c r="H75" t="n">
-        <v>48.48</v>
-      </c>
-      <c r="I75" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.92</v>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.293</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.314</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3850,39 +3850,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E76" s="8" t="n">
-        <v>0.0698</v>
+        <v>5.6</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>-0.0014</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>1825500</v>
+        <v>2403100</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>1.79</v>
+        <v>0.31</v>
       </c>
       <c r="H76" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="I76" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.93</v>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.21</v>
+        <v>5.875</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.21</v>
+        <v>6.164</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3895,28 +3895,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E77" s="3" t="n">
-        <v>-0.0183</v>
+        <v>0.255</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>1765400</v>
+        <v>2298900</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
       <c r="H77" t="n">
-        <v>49.53</v>
+        <v>27.74</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.077</v>
+        <v>0.274</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1.047</v>
+        <v>0.3</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>-0.0118</v>
+        <v>1.09</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>1727400</v>
+        <v>2185100</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.57</v>
+        <v>0.23</v>
       </c>
       <c r="H78" t="n">
-        <v>15.99</v>
+        <v>52.65</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.908</v>
+        <v>1.079</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.97</v>
+        <v>1.047</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3985,28 +3985,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>2.47</v>
+        <v>0.455</v>
       </c>
       <c r="E79" s="8" t="n">
-        <v>0.0123</v>
+        <v>0.0111</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>1726500</v>
+        <v>2136000</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="H79" t="n">
-        <v>54.36</v>
+        <v>30.38</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>2.448</v>
+        <v>0.493</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>2.392</v>
+        <v>0.552</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4030,28 +4030,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0</v>
+        <v>0.76</v>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>1688500</v>
+        <v>2083200</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.63</v>
+        <v>0.25</v>
       </c>
       <c r="H80" t="n">
-        <v>33.15</v>
+        <v>47</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.54</v>
+        <v>0.77</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.569</v>
+        <v>0.771</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4075,28 +4075,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1.94</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E81" s="8" t="n">
-        <v>0.0211</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>1670500</v>
+        <v>2060400</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>0.28</v>
+        <v>1.01</v>
       </c>
       <c r="H81" t="n">
-        <v>51.67</v>
+        <v>48.48</v>
       </c>
       <c r="I81" s="9" t="inlineStr">
         <is>
@@ -4104,10 +4104,10 @@
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.922</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>1.95</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4120,39 +4120,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.62</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>-0.0583</v>
+        <v>-0.0313</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1629600</v>
+        <v>2054800</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.28</v>
+        <v>11.46</v>
       </c>
       <c r="H82" t="n">
-        <v>52.71</v>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.41</v>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.473</v>
+        <v>0.546</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4165,28 +4165,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E83" s="8" t="n">
-        <v>0.0357</v>
+        <v>0.625</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>1622500</v>
+        <v>2042800</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.76</v>
+        <v>0.61</v>
       </c>
       <c r="H83" t="n">
-        <v>58.96</v>
+        <v>70.16</v>
       </c>
       <c r="I83" s="9" t="inlineStr">
         <is>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.419</v>
+        <v>0.618</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.433</v>
+        <v>0.606</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4210,28 +4210,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>5.57</v>
-      </c>
-      <c r="E84" s="3" t="n">
-        <v>-0.0068</v>
+        <v>0.795</v>
+      </c>
+      <c r="E84" s="8" t="n">
+        <v>0.0325</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>1604900</v>
+        <v>2032800</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.21</v>
+        <v>0.82</v>
       </c>
       <c r="H84" t="n">
-        <v>27.95</v>
+        <v>60.16</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>5.872</v>
+        <v>0.742</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>6.163</v>
+        <v>0.706</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4255,28 +4255,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.25</v>
+        <v>4.8</v>
       </c>
       <c r="E85" s="3" t="n">
-        <v>-0.0385</v>
+        <v>-0.0103</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1541000</v>
+        <v>1995900</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.22</v>
+        <v>0.08</v>
       </c>
       <c r="H85" t="n">
-        <v>38.79</v>
+        <v>46.11</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.271</v>
+        <v>4.893</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.292</v>
+        <v>4.736</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4300,28 +4300,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SKYWLD</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>0.0195</v>
+        <v>0.34</v>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>-0.06849999999999999</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1537900</v>
+        <v>1994900</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.62</v>
+        <v>1.71</v>
       </c>
       <c r="H86" t="n">
-        <v>58.96</v>
+        <v>26</v>
       </c>
       <c r="I86" s="6" t="inlineStr">
         <is>
@@ -4329,10 +4329,10 @@
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.741</v>
+        <v>0.38</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.705</v>
+        <v>0.391</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4345,28 +4345,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SKYWLD</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.335</v>
+        <v>0.57</v>
       </c>
       <c r="E87" s="3" t="n">
-        <v>-0.08220000000000001</v>
+        <v>-0.05</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1465300</v>
+        <v>1902300</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>1.26</v>
+        <v>0.33</v>
       </c>
       <c r="H87" t="n">
-        <v>24.71</v>
+        <v>53.44</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4374,10 +4374,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.379</v>
+        <v>0.57</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.391</v>
+        <v>0.473</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4390,28 +4390,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E88" s="3" t="n">
-        <v>-0.008199999999999999</v>
+        <v>2.47</v>
+      </c>
+      <c r="E88" s="8" t="n">
+        <v>0.0123</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1437800</v>
+        <v>1891900</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="H88" t="n">
-        <v>22.97</v>
+        <v>54.36</v>
       </c>
       <c r="I88" s="6" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>1.375</v>
+        <v>2.448</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>1.551</v>
+        <v>2.392</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4435,28 +4435,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.63</v>
+        <v>0.51</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>-0.0233</v>
+        <v>-0.0097</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1436900</v>
+        <v>1879700</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.16</v>
+        <v>0.71</v>
       </c>
       <c r="H89" t="n">
-        <v>40</v>
+        <v>31.58</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.674</v>
+        <v>0.54</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.569</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4480,39 +4480,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.41</v>
+        <v>1.94</v>
       </c>
       <c r="E90" s="8" t="n">
-        <v>0.0123</v>
+        <v>0.0211</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1418100</v>
+        <v>1869800</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.15</v>
+        <v>0.32</v>
       </c>
       <c r="H90" t="n">
-        <v>42.88</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.67</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.435</v>
+        <v>1.922</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.435</v>
+        <v>1.95</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4525,39 +4525,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>6.74</v>
+        <v>0.23</v>
       </c>
       <c r="E91" s="8" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0698</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1414500</v>
+        <v>1825500</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>0.14</v>
+        <v>1.79</v>
       </c>
       <c r="H91" t="n">
-        <v>31.54</v>
-      </c>
-      <c r="I91" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.56</v>
+      </c>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>7.164</v>
+        <v>0.21</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>7.582</v>
+        <v>0.21</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4570,39 +4570,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E92" s="8" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1402500</v>
+        <v>1772500</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.73</v>
+        <v>0.84</v>
       </c>
       <c r="H92" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.36</v>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.728</v>
+        <v>0.419</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.744</v>
+        <v>0.433</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4615,28 +4615,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>0.215</v>
+        <v>1.2</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>-0.0227</v>
+        <v>-0.0164</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1383900</v>
+        <v>1740200</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>1.84</v>
+        <v>0.39</v>
       </c>
       <c r="H93" t="n">
-        <v>42.03</v>
+        <v>22.42</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>0.223</v>
+        <v>1.374</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0.232</v>
+        <v>1.55</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4660,28 +4660,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>2.09</v>
+        <v>9.98</v>
       </c>
       <c r="E94" s="8" t="n">
-        <v>0.0048</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1365800</v>
+        <v>1727900</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.08</v>
+        <v>0.13</v>
       </c>
       <c r="H94" t="n">
-        <v>47.56</v>
+        <v>46.87</v>
       </c>
       <c r="I94" s="9" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>2.105</v>
+        <v>9.999000000000001</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2.102</v>
+        <v>10.138</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4705,39 +4705,39 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E95" s="8" t="n">
-        <v>0.0152</v>
+        <v>3.92</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>-0.0101</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1348900</v>
+        <v>1676600</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.28</v>
+        <v>0.17</v>
       </c>
       <c r="H95" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="I95" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.12</v>
+      </c>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.335</v>
+        <v>3.957</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0.343</v>
+        <v>3.572</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4750,28 +4750,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0261</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>0.39</v>
+        <v>4.95</v>
       </c>
       <c r="E96" s="3" t="n">
-        <v>-0.0602</v>
+        <v>-0.008</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1321800</v>
+        <v>1638400</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>2.78</v>
+        <v>0.41</v>
       </c>
       <c r="H96" t="n">
-        <v>55.36</v>
+        <v>43.23</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.383</v>
+        <v>5.048</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>0.365</v>
+        <v>5.052</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4795,28 +4795,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E97" s="3" t="n">
-        <v>-0.0121</v>
+        <v>2.48</v>
+      </c>
+      <c r="E97" s="8" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1289800</v>
+        <v>1618300</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.37</v>
+        <v>0.54</v>
       </c>
       <c r="H97" t="n">
-        <v>49.71</v>
+        <v>38.57</v>
       </c>
       <c r="I97" s="6" t="inlineStr">
         <is>
@@ -4824,10 +4824,10 @@
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.825</v>
+        <v>2.548</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.785</v>
+        <v>2.676</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4840,28 +4840,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.585</v>
+        <v>0.275</v>
       </c>
       <c r="E98" s="3" t="n">
-        <v>-0.0168</v>
+        <v>-0.0179</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1279000</v>
+        <v>1610800</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="H98" t="n">
-        <v>47.87</v>
+        <v>20.38</v>
       </c>
       <c r="I98" s="6" t="inlineStr">
         <is>
@@ -4869,10 +4869,10 @@
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.597</v>
+        <v>0.327</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.586</v>
+        <v>0.369</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4885,28 +4885,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>3.92</v>
+        <v>0.63</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.0101</v>
+        <v>-0.0233</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1263900</v>
+        <v>1605100</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="H99" t="n">
-        <v>51.12</v>
+        <v>40</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4914,10 +4914,10 @@
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>3.957</v>
+        <v>0.674</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>3.572</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4930,28 +4930,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1243500</v>
+        <v>1542600</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.41</v>
+        <v>0.22</v>
       </c>
       <c r="H100" t="n">
-        <v>35.65</v>
+        <v>40.54</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2.546</v>
+        <v>0.272</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.676</v>
+        <v>0.292</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4975,39 +4975,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0</v>
+        <v>2.36</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>-0.05599999999999999</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1239300</v>
+        <v>1511300</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>1.33</v>
+        <v>0.29</v>
       </c>
       <c r="H101" t="n">
-        <v>55.75</v>
-      </c>
-      <c r="I101" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.57</v>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.276</v>
+        <v>2.766</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.268</v>
+        <v>2.879</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5020,28 +5020,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="E102" s="3" t="n">
-        <v>-0.0035</v>
+        <v>0.405</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1227400</v>
+        <v>1454800</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H102" t="n">
-        <v>55.12</v>
+        <v>41.34</v>
       </c>
       <c r="I102" s="6" t="inlineStr">
         <is>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>2.802</v>
+        <v>0.434</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2.672</v>
+        <v>0.435</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5065,39 +5065,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.585</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-0.0168</v>
+        <v>-0.0121</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1214800</v>
+        <v>1427700</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.3</v>
+        <v>0.41</v>
       </c>
       <c r="H103" t="n">
-        <v>67.13</v>
-      </c>
-      <c r="I103" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.71</v>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.517</v>
+        <v>0.825</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.472</v>
+        <v>0.785</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5110,39 +5110,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0261</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.965</v>
+        <v>0.365</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>-0.0103</v>
+        <v>-0.1205</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1204400</v>
+        <v>1408400</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.2</v>
+        <v>2.97</v>
       </c>
       <c r="H104" t="n">
-        <v>64.12</v>
-      </c>
-      <c r="I104" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.29</v>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.929</v>
+        <v>0.38</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.88</v>
+        <v>0.365</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5155,28 +5155,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E105" s="3" t="n">
-        <v>-0.048</v>
+        <v>0.71</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1201000</v>
+        <v>1407300</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.23</v>
+        <v>0.74</v>
       </c>
       <c r="H105" t="n">
-        <v>29.11</v>
+        <v>42.1</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>2.768</v>
+        <v>0.728</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>2.879</v>
+        <v>0.744</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5200,28 +5200,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.275</v>
+        <v>0.235</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.0179</v>
+        <v>-0.0208</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1189600</v>
+        <v>1405700</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H106" t="n">
-        <v>20.38</v>
+        <v>36.08</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.327</v>
+        <v>0.252</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.369</v>
+        <v>0.273</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5245,28 +5245,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>9.949999999999999</v>
+        <v>0.335</v>
       </c>
       <c r="E107" s="8" t="n">
-        <v>0.0051</v>
+        <v>0.0152</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1179000</v>
+        <v>1397300</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="H107" t="n">
-        <v>44.98</v>
+        <v>47.93</v>
       </c>
       <c r="I107" s="9" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>9.996</v>
+        <v>0.335</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>10.137</v>
+        <v>0.343</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5290,28 +5290,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1173100</v>
+        <v>1383900</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.3</v>
+        <v>1.84</v>
       </c>
       <c r="H108" t="n">
-        <v>45.7</v>
+        <v>42.03</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>5.052</v>
+        <v>0.223</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>5.053</v>
+        <v>0.232</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5335,39 +5335,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="E109" s="3" t="n">
-        <v>-0.0207</v>
+        <v>2.09</v>
+      </c>
+      <c r="E109" s="8" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1142700</v>
+        <v>1377100</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>1.52</v>
+        <v>0.08</v>
       </c>
       <c r="H109" t="n">
-        <v>32.08</v>
-      </c>
-      <c r="I109" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.56</v>
+      </c>
+      <c r="I109" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.495</v>
+        <v>2.105</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>1.503</v>
+        <v>2.102</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5380,39 +5380,39 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>0.385</v>
+        <v>1.09</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>-0.0128</v>
+        <v>-0.018</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1126000</v>
+        <v>1362600</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="H110" t="n">
-        <v>48.59</v>
-      </c>
-      <c r="I110" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.92</v>
+      </c>
+      <c r="I110" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.388</v>
+        <v>1.149</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>0.39</v>
+        <v>1.103</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5425,39 +5425,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>1.09</v>
+        <v>0.96</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>-0.018</v>
+        <v>-0.0154</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1104000</v>
+        <v>1360900</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.27</v>
+        <v>0.22</v>
       </c>
       <c r="H111" t="n">
-        <v>41.92</v>
-      </c>
-      <c r="I111" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.32</v>
+      </c>
+      <c r="I111" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>1.149</v>
+        <v>0.929</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>1.103</v>
+        <v>0.88</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5470,28 +5470,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.725</v>
+        <v>2.85</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>-0.0268</v>
+        <v>-0.0035</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1084000</v>
+        <v>1359900</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="H112" t="n">
-        <v>49.44</v>
+        <v>55.12</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.741</v>
+        <v>2.802</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.679</v>
+        <v>2.672</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5515,39 +5515,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>0.635</v>
+        <v>6.5</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>-0.0451</v>
+        <v>-0.0076</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1073700</v>
+        <v>1355200</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.32</v>
+        <v>0.23</v>
       </c>
       <c r="H113" t="n">
-        <v>31.55</v>
-      </c>
-      <c r="I113" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.8</v>
+      </c>
+      <c r="I113" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.716</v>
+        <v>6.208</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>0.743</v>
+        <v>5.931</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5560,39 +5560,39 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>6.46</v>
+        <v>0.22</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-0.0137</v>
+        <v>-0.0435</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1067000</v>
+        <v>1309200</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.18</v>
+        <v>0.67</v>
       </c>
       <c r="H114" t="n">
-        <v>56.07</v>
-      </c>
-      <c r="I114" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.76</v>
+      </c>
+      <c r="I114" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>6.204</v>
+        <v>0.221</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>5.93</v>
+        <v>0.185</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5605,28 +5605,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>-0.008399999999999999</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1036600</v>
+        <v>1308100</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="H115" t="n">
-        <v>58.81</v>
+        <v>49.02</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.06</v>
+        <v>0.597</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.923</v>
+        <v>0.586</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5650,28 +5650,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>3.78</v>
+        <v>0.725</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0268</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1030000</v>
+        <v>1284800</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="H116" t="n">
-        <v>48.34</v>
+        <v>49.44</v>
       </c>
       <c r="I116" s="6" t="inlineStr">
         <is>
@@ -5679,10 +5679,10 @@
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>3.844</v>
+        <v>0.741</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>3.699</v>
+        <v>0.679</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5695,28 +5695,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.19</v>
+        <v>1.4</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-0.0083</v>
+        <v>-0.0345</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1021500</v>
+        <v>1281200</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.3</v>
+        <v>1.7</v>
       </c>
       <c r="H117" t="n">
-        <v>48.39</v>
+        <v>29.57</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.235</v>
+        <v>1.494</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.076</v>
+        <v>1.503</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5749,19 +5749,19 @@
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.0394</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1016400</v>
+        <v>1271800</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="H118" t="n">
-        <v>45.85</v>
+        <v>48.87</v>
       </c>
       <c r="I118" s="6" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.281</v>
+        <v>1.285</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.228</v>
+        <v>1.229</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5785,28 +5785,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.985</v>
+        <v>0.64</v>
       </c>
       <c r="E119" s="3" t="n">
-        <v>-0.0343</v>
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>995300</v>
+        <v>1258100</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.25</v>
+        <v>0.38</v>
       </c>
       <c r="H119" t="n">
-        <v>44.23</v>
+        <v>32.17</v>
       </c>
       <c r="I119" s="6" t="inlineStr">
         <is>
@@ -5814,10 +5814,10 @@
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>1.039</v>
+        <v>0.716</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.949</v>
+        <v>0.743</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5830,28 +5830,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>2.55</v>
+        <v>1.2</v>
       </c>
       <c r="E120" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>976700</v>
+        <v>1252400</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.16</v>
+        <v>0.37</v>
       </c>
       <c r="H120" t="n">
-        <v>45.14</v>
+        <v>49.45</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>2.603</v>
+        <v>1.236</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>2.61</v>
+        <v>1.077</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5875,39 +5875,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>4.81</v>
+        <v>0.58</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0252</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>947600</v>
+        <v>1252100</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.04</v>
+        <v>0.3</v>
       </c>
       <c r="H121" t="n">
-        <v>46.62</v>
-      </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.84</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>4.894</v>
+        <v>0.517</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>4.736</v>
+        <v>0.472</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5920,28 +5920,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>0</v>
+        <v>0.675</v>
+      </c>
+      <c r="E122" s="8" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>936900</v>
+        <v>1246000</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.53</v>
+        <v>0.08</v>
       </c>
       <c r="H122" t="n">
-        <v>51.22</v>
+        <v>39.24</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.915</v>
+        <v>0.742</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.879</v>
+        <v>0.723</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5965,39 +5965,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.755</v>
+        <v>0.275</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>-0.0258</v>
+        <v>-0.0179</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>931100</v>
+        <v>1239800</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.41</v>
+        <v>1.33</v>
       </c>
       <c r="H123" t="n">
-        <v>60.75</v>
-      </c>
-      <c r="I123" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.1</v>
+      </c>
+      <c r="I123" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.732</v>
+        <v>0.276</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.652</v>
+        <v>0.268</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6010,28 +6010,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E124" s="3" t="n">
-        <v>-0.0169</v>
+        <v>1.34</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>918800</v>
+        <v>1218400</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.13</v>
+        <v>0.6</v>
       </c>
       <c r="H124" t="n">
-        <v>49.53</v>
+        <v>40.19</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.169</v>
+        <v>1.364</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1.139</v>
+        <v>1.342</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6055,28 +6055,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E125" s="3" t="n">
-        <v>-0.0227</v>
+        <v>1.19</v>
+      </c>
+      <c r="E125" s="8" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>898000</v>
+        <v>1212400</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.37</v>
+        <v>0.17</v>
       </c>
       <c r="H125" t="n">
-        <v>54.96</v>
+        <v>53.65</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.264</v>
+        <v>1.172</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1.176</v>
+        <v>1.14</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6100,28 +6100,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.63</v>
+        <v>0.38</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0256</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>842400</v>
+        <v>1172000</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="H126" t="n">
-        <v>47.44</v>
+        <v>46.47</v>
       </c>
       <c r="I126" s="9" t="inlineStr">
         <is>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.637</v>
+        <v>0.387</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.624</v>
+        <v>0.39</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6145,39 +6145,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="E127" s="8" t="n">
-        <v>0.008699999999999999</v>
+        <v>3.78</v>
+      </c>
+      <c r="E127" s="3" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>812100</v>
+        <v>1169900</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.23</v>
+        <v>0.39</v>
       </c>
       <c r="H127" t="n">
-        <v>60.34</v>
-      </c>
-      <c r="I127" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.34</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>2.233</v>
+        <v>3.844</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>2.175</v>
+        <v>3.699</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6190,28 +6190,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1.34</v>
+        <v>1.11</v>
       </c>
       <c r="E128" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>796900</v>
+        <v>1131600</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="H128" t="n">
-        <v>40.19</v>
+        <v>58.81</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.364</v>
+        <v>1.06</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>1.342</v>
+        <v>0.923</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6235,39 +6235,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.675</v>
+        <v>0.225</v>
       </c>
       <c r="E129" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>770800</v>
+        <v>1126700</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.11</v>
+        <v>1.08</v>
       </c>
       <c r="H129" t="n">
-        <v>27.88</v>
-      </c>
-      <c r="I129" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.78</v>
+      </c>
+      <c r="I129" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.719</v>
+        <v>0.229</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.786</v>
+        <v>0.238</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6280,28 +6280,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>7.15</v>
+        <v>0.985</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>-0.0205</v>
+        <v>-0.0343</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>763200</v>
+        <v>1084100</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="H130" t="n">
-        <v>47.94</v>
+        <v>44.23</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>7.332</v>
+        <v>1.039</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>6.905</v>
+        <v>0.949</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6325,28 +6325,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="E131" s="3" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.675</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>752600</v>
+        <v>1031900</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="H131" t="n">
-        <v>50.24</v>
+        <v>27.88</v>
       </c>
       <c r="I131" s="6" t="inlineStr">
         <is>
@@ -6354,10 +6354,10 @@
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>3.024</v>
+        <v>0.719</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>2.858</v>
+        <v>0.786</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6379,19 +6379,19 @@
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>-0.0315</v>
+        <v>-0.0157</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>723200</v>
+        <v>1003500</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="H132" t="n">
-        <v>40.82</v>
+        <v>42.62</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6399,7 +6399,7 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>1.316</v>
+        <v>1.317</v>
       </c>
       <c r="K132" s="2" t="n">
         <v>1.288</v>
@@ -6415,39 +6415,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="E133" s="8" t="n">
-        <v>0.0091</v>
+        <v>2.55</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>712400</v>
+        <v>986200</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="H133" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="I133" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.14</v>
+      </c>
+      <c r="I133" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>4.364</v>
+        <v>2.603</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>4.43</v>
+        <v>2.61</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6460,28 +6460,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>2.39</v>
+        <v>0.76</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>-0.0124</v>
+        <v>-0.0194</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>709400</v>
+        <v>972500</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.15</v>
+        <v>0.43</v>
       </c>
       <c r="H134" t="n">
-        <v>34.54</v>
+        <v>62.26</v>
       </c>
       <c r="I134" s="6" t="inlineStr">
         <is>
@@ -6489,10 +6489,10 @@
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>2.528</v>
+        <v>0.733</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>2.7</v>
+        <v>0.652</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6505,28 +6505,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>0.585</v>
+        <v>7.13</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0233</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>691200</v>
+        <v>964700</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="H135" t="n">
-        <v>38.72</v>
+        <v>47.51</v>
       </c>
       <c r="I135" s="6" t="inlineStr">
         <is>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>0.602</v>
+        <v>7.33</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>0.63</v>
+        <v>6.905</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6550,39 +6550,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="E136" s="10" t="n">
-        <v>0</v>
+        <v>10.44</v>
+      </c>
+      <c r="E136" s="3" t="n">
+        <v>-0.0038</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>687900</v>
+        <v>950600</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.19</v>
+        <v>0.27</v>
       </c>
       <c r="H136" t="n">
-        <v>59.68</v>
-      </c>
-      <c r="I136" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.73</v>
+      </c>
+      <c r="I136" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>2.694</v>
+        <v>10.417</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2.283</v>
+        <v>9.781000000000001</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6595,39 +6595,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="E137" s="3" t="n">
-        <v>-0.0113</v>
+        <v>4.48</v>
+      </c>
+      <c r="E137" s="8" t="n">
+        <v>0.0182</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>674900</v>
+        <v>944000</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.53</v>
+        <v>0.18</v>
       </c>
       <c r="H137" t="n">
-        <v>31.94</v>
-      </c>
-      <c r="I137" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.85</v>
+      </c>
+      <c r="I137" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>5.464</v>
+        <v>4.368</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>5.8</v>
+        <v>4.431</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6640,39 +6640,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E138" s="3" t="n">
-        <v>-0.0152</v>
+        <v>0.915</v>
+      </c>
+      <c r="E138" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>674600</v>
+        <v>936900</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="H138" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="I138" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.22</v>
+      </c>
+      <c r="I138" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.646</v>
+        <v>0.915</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>0.879</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6685,39 +6685,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>0.65</v>
+        <v>1.29</v>
       </c>
       <c r="E139" s="3" t="n">
-        <v>-0.0076</v>
+        <v>-0.0227</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>664100</v>
+        <v>936200</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.6</v>
+        <v>0.39</v>
       </c>
       <c r="H139" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="I139" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>54.96</v>
+      </c>
+      <c r="I139" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.585</v>
+        <v>1.264</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>0.532</v>
+        <v>1.176</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6730,39 +6730,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PARADIGM</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.8</v>
+        <v>2.8</v>
       </c>
       <c r="E140" s="3" t="n">
-        <v>-0.0062</v>
+        <v>-0.0071</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>656600</v>
+        <v>934700</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>1.71</v>
+        <v>0.26</v>
       </c>
       <c r="H140" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="I140" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.65</v>
+      </c>
+      <c r="I140" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.819</v>
+        <v>2.693</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.848</v>
+        <v>2.283</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6775,39 +6775,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>0.84</v>
+        <v>2.32</v>
       </c>
       <c r="E141" s="8" t="n">
-        <v>0.0307</v>
+        <v>0.0043</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>637200</v>
+        <v>912100</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.19</v>
+        <v>0.26</v>
       </c>
       <c r="H141" t="n">
-        <v>34.41</v>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.64</v>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>0.89</v>
+        <v>2.232</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>0.949</v>
+        <v>2.175</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6820,39 +6820,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1.68</v>
+        <v>1.26</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>-0.0175</v>
+        <v>-0.0156</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>622700</v>
+        <v>879900</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="H142" t="n">
-        <v>32.26</v>
-      </c>
-      <c r="I142" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.37</v>
+      </c>
+      <c r="I142" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>1.764</v>
+        <v>1.26</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1.881</v>
+        <v>1.276</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6874,19 +6874,19 @@
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>-0.0154</v>
+        <v>-0.0077</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>619300</v>
+        <v>877000</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.3</v>
+        <v>0.43</v>
       </c>
       <c r="H143" t="n">
-        <v>23.72</v>
+        <v>24.64</v>
       </c>
       <c r="I143" s="6" t="inlineStr">
         <is>
@@ -6894,10 +6894,10 @@
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>1.391</v>
+        <v>1.392</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>1.459</v>
+        <v>1.46</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6910,28 +6910,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E144" s="10" t="n">
-        <v>0</v>
+        <v>3.11</v>
+      </c>
+      <c r="E144" s="3" t="n">
+        <v>-0.0127</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>595000</v>
+        <v>845400</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="H144" t="n">
-        <v>45.03</v>
+        <v>49.79</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.631</v>
+        <v>3.167</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>0.631</v>
+        <v>2.894</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6955,39 +6955,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1.02</v>
+        <v>0.63</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>-0.0192</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>594900</v>
+        <v>842400</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="H145" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.44</v>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>1.08</v>
+        <v>0.637</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>1.13</v>
+        <v>0.624</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -7015,10 +7015,10 @@
         <v>-0.0175</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>592200</v>
+        <v>834400</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="H146" t="n">
         <v>29.07</v>
@@ -7045,28 +7045,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.665</v>
+        <v>2.99</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>-0.0075</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>562400</v>
+        <v>818200</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.04</v>
+        <v>0.27</v>
       </c>
       <c r="H147" t="n">
-        <v>37.7</v>
+        <v>50.24</v>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.741</v>
+        <v>3.024</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0.723</v>
+        <v>2.858</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7090,28 +7090,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>5.34</v>
+        <v>0.835</v>
       </c>
       <c r="E148" s="8" t="n">
-        <v>0.0114</v>
+        <v>0.0245</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>549400</v>
+        <v>817900</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="H148" t="n">
-        <v>33.84</v>
+        <v>32.77</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>5.554</v>
+        <v>0.889</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>5.793</v>
+        <v>0.949</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7135,28 +7135,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>0</v>
+        <v>5.23</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>-0.0113</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>543500</v>
+        <v>814000</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.64</v>
       </c>
       <c r="H149" t="n">
-        <v>55.71</v>
+        <v>31.94</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>1.113</v>
+        <v>5.464</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0.896</v>
+        <v>5.8</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7180,39 +7180,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>4.03</v>
+        <v>0.65</v>
       </c>
       <c r="E150" s="3" t="n">
-        <v>-0.0242</v>
+        <v>-0.0076</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>522200</v>
+        <v>790500</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.2</v>
+        <v>0.72</v>
       </c>
       <c r="H150" t="n">
-        <v>40.73</v>
-      </c>
-      <c r="I150" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.56</v>
+      </c>
+      <c r="I150" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>4.261</v>
+        <v>0.585</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>4.314</v>
+        <v>0.532</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7225,28 +7225,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="E151" s="8" t="n">
-        <v>0.0019</v>
+        <v>2.38</v>
+      </c>
+      <c r="E151" s="3" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>505600</v>
+        <v>770700</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="H151" t="n">
-        <v>54.94</v>
+        <v>33.98</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>10.423</v>
+        <v>2.527</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>9.782999999999999</v>
+        <v>2.699</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7279,19 +7279,19 @@
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>0.905</v>
+        <v>0.9</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>-0.005500000000000001</v>
+        <v>-0.011</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>500800</v>
+        <v>763600</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.29</v>
+        <v>0.44</v>
       </c>
       <c r="H152" t="n">
-        <v>32.37</v>
+        <v>31.3</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K152" s="2" t="n">
         <v>0.999</v>
@@ -7307,8 +7307,953 @@
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E153" s="3" t="n">
+        <v>-0.0175</v>
+      </c>
+      <c r="F153" s="4" t="n">
+        <v>752800</v>
+      </c>
+      <c r="G153" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H153" t="n">
+        <v>32.26</v>
+      </c>
+      <c r="I153" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="2" t="n">
+        <v>1.764</v>
+      </c>
+      <c r="K153" s="2" t="n">
+        <v>1.881</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>TIMECOM</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="E154" s="8" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F154" s="4" t="n">
+        <v>730400</v>
+      </c>
+      <c r="G154" s="5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H154" t="n">
+        <v>33.84</v>
+      </c>
+      <c r="I154" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="n">
+        <v>5.554</v>
+      </c>
+      <c r="K154" s="2" t="n">
+        <v>5.793</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E155" s="3" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="F155" s="4" t="n">
+        <v>725900</v>
+      </c>
+      <c r="G155" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H155" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="I155" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="2" t="n">
+        <v>0.646</v>
+      </c>
+      <c r="K155" s="2" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E156" s="3" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F156" s="4" t="n">
+        <v>710300</v>
+      </c>
+      <c r="G156" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H156" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="2" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K156" s="2" t="n">
+        <v>0.616</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>3662</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>MFLOUR</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E157" s="3" t="n">
+        <v>-0.0169</v>
+      </c>
+      <c r="F157" s="4" t="n">
+        <v>700300</v>
+      </c>
+      <c r="G157" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H157" t="n">
+        <v>36.97</v>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J157" s="2" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="K157" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>5338</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>PARADIGM</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E158" s="3" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F158" s="4" t="n">
+        <v>657100</v>
+      </c>
+      <c r="G158" s="5" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="H158" t="n">
+        <v>25.89</v>
+      </c>
+      <c r="I158" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J158" s="2" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="K158" s="2" t="n">
+        <v>0.848</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>0340</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>NORTHERN</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E159" s="3" t="n">
+        <v>-0.008800000000000001</v>
+      </c>
+      <c r="F159" s="4" t="n">
+        <v>638100</v>
+      </c>
+      <c r="G159" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H159" t="n">
+        <v>54.69</v>
+      </c>
+      <c r="I159" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="2" t="n">
+        <v>1.112</v>
+      </c>
+      <c r="K159" s="2" t="n">
+        <v>0.896</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>4.04</v>
+      </c>
+      <c r="E160" s="3" t="n">
+        <v>-0.0218</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>621500</v>
+      </c>
+      <c r="G160" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H160" t="n">
+        <v>41.01</v>
+      </c>
+      <c r="I160" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="n">
+        <v>4.262</v>
+      </c>
+      <c r="K160" s="2" t="n">
+        <v>4.315</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>5236</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>MATRIX</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E161" s="3" t="n">
+        <v>-0.0192</v>
+      </c>
+      <c r="F161" s="4" t="n">
+        <v>609200</v>
+      </c>
+      <c r="G161" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H161" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="I161" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J161" s="2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K161" s="2" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F162" s="4" t="n">
+        <v>595000</v>
+      </c>
+      <c r="G162" s="5" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H162" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="I162" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="K162" s="2" t="n">
+        <v>0.631</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5302</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>ATECH</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="E163" s="3" t="n">
+        <v>-0.0197</v>
+      </c>
+      <c r="F163" s="4" t="n">
+        <v>562500</v>
+      </c>
+      <c r="G163" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H163" t="n">
+        <v>44.35</v>
+      </c>
+      <c r="I163" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J163" s="2" t="n">
+        <v>0.772</v>
+      </c>
+      <c r="K163" s="2" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F164" s="4" t="n">
+        <v>541100</v>
+      </c>
+      <c r="G164" s="5" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H164" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="I164" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="2" t="n">
+        <v>2.112</v>
+      </c>
+      <c r="K164" s="2" t="n">
+        <v>2.066</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>7235</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>SUPERLN</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="E165" s="8" t="n">
+        <v>0.0167</v>
+      </c>
+      <c r="F165" s="4" t="n">
+        <v>540700</v>
+      </c>
+      <c r="G165" s="5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="H165" t="n">
+        <v>64.01000000000001</v>
+      </c>
+      <c r="I165" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J165" s="2" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="K165" s="2" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E166" s="3" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F166" s="4" t="n">
+        <v>539300</v>
+      </c>
+      <c r="G166" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H166" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J166" s="2" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="K166" s="2" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>0291</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>CHB</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E167" s="3" t="n">
+        <v>-0.0325</v>
+      </c>
+      <c r="F167" s="4" t="n">
+        <v>526000</v>
+      </c>
+      <c r="G167" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H167" t="n">
+        <v>46.03</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="2" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="K167" s="2" t="n">
+        <v>2.256</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>-0.0016</v>
+      </c>
+      <c r="F168" s="4" t="n">
+        <v>523900</v>
+      </c>
+      <c r="G168" s="5" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H168" t="n">
+        <v>36.16</v>
+      </c>
+      <c r="I168" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="n">
+        <v>6.371</v>
+      </c>
+      <c r="K168" s="2" t="n">
+        <v>6.731</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="E169" s="3" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="F169" s="4" t="n">
+        <v>518000</v>
+      </c>
+      <c r="G169" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H169" t="n">
+        <v>31.51</v>
+      </c>
+      <c r="I169" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K169" s="2" t="n">
+        <v>3.593</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E170" s="3" t="n">
+        <v>-0.0431</v>
+      </c>
+      <c r="F170" s="4" t="n">
+        <v>517100</v>
+      </c>
+      <c r="G170" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H170" t="n">
+        <v>45.15</v>
+      </c>
+      <c r="I170" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="n">
+        <v>2.102</v>
+      </c>
+      <c r="K170" s="2" t="n">
+        <v>1.994</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>5246</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>WPRTS</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="E171" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="4" t="n">
+        <v>506600</v>
+      </c>
+      <c r="G171" s="5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H171" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="I171" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="n">
+        <v>6.755</v>
+      </c>
+      <c r="K171" s="2" t="n">
+        <v>6.824</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5223</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>MENTIGA</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="E172" s="8" t="n">
+        <v>0.0462</v>
+      </c>
+      <c r="F172" s="4" t="n">
+        <v>505500</v>
+      </c>
+      <c r="G172" s="5" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H172" t="n">
+        <v>84.15000000000001</v>
+      </c>
+      <c r="I172" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="K172" s="2" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>-0.0164</v>
+      </c>
+      <c r="F173" s="4" t="n">
+        <v>500600</v>
+      </c>
+      <c r="G173" s="5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H173" t="n">
+        <v>48.4</v>
+      </c>
+      <c r="I173" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="n">
+        <v>5.503</v>
+      </c>
+      <c r="K173" s="2" t="n">
+        <v>5.388</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M152"/>
+  <autoFilter ref="A1:M173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
+++ b/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-20" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$185</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M173"/>
+  <dimension ref="A1:M185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.33</v>
+        <v>0.335</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.0294</v>
+        <v>-0.0147</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>47320400</v>
+        <v>49989000</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="H2" t="n">
-        <v>63.6</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.307</v>
+        <v>0.308</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.259</v>
@@ -597,19 +597,19 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.47</v>
+        <v>0.465</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0.0562</v>
+        <v>0.0449</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>35686100</v>
+        <v>36601200</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="H3" t="n">
-        <v>81.92</v>
+        <v>81.36</v>
       </c>
       <c r="I3" s="9" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="J3" s="2" t="n">
-        <v>0.393</v>
+        <v>0.392</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>0.286</v>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.9</v>
+        <v>0.905</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>0.0112</v>
+        <v>0.0169</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>31936300</v>
+        <v>35432500</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
       <c r="H4" t="n">
-        <v>65.36</v>
+        <v>65.92</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -662,7 +662,7 @@
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>0.834</v>
+        <v>0.835</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>0.742</v>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>28264000</v>
+        <v>32309600</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="H5" t="n">
         <v>22.63</v>
@@ -738,10 +738,10 @@
         <v>-0.0559</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>22245300</v>
+        <v>22575200</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4.44</v>
+        <v>4.51</v>
       </c>
       <c r="H6" t="n">
         <v>27.02</v>
@@ -783,10 +783,10 @@
         <v>0.1111</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>17856300</v>
+        <v>18537800</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="H7" t="n">
         <v>28.68</v>
@@ -828,10 +828,10 @@
         <v>0.0217</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>17465400</v>
+        <v>18016900</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="H8" t="n">
         <v>80.01000000000001</v>
@@ -858,28 +858,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>-0.098</v>
+        <v>0.155</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>16315300</v>
+        <v>17585400</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1.46</v>
+        <v>0.5</v>
       </c>
       <c r="H9" t="n">
-        <v>41.67</v>
+        <v>48.61</v>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
@@ -887,10 +887,10 @@
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>0.514</v>
+        <v>0.155</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>0.463</v>
+        <v>0.156</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="7" t="inlineStr"/>
@@ -903,40 +903,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0</v>
+        <v>0.1</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>-0.1667</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>16135400</v>
+        <v>17133200</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="H10" t="n">
-        <v>48.61</v>
+        <v>0.44</v>
       </c>
       <c r="I10" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J10" s="2" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="K10" s="2" t="n">
-        <v>0.156</v>
-      </c>
+      <c r="J10" s="2" t="n"/>
+      <c r="K10" s="2" t="n"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="7" t="inlineStr"/>
     </row>
@@ -948,33 +941,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.095</v>
+        <v>0.46</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.2083</v>
+        <v>-0.098</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>14867000</v>
+        <v>16963500</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.38</v>
+        <v>1.52</v>
+      </c>
+      <c r="H11" t="n">
+        <v>41.67</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
+      <c r="J11" s="2" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>0.463</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="7" t="inlineStr"/>
     </row>
@@ -986,28 +986,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>0.27</v>
+        <v>0.305</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0161</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>13040900</v>
+        <v>14517400</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>1.33</v>
+        <v>0.76</v>
       </c>
       <c r="H12" t="n">
-        <v>39.85</v>
+        <v>47.44</v>
       </c>
       <c r="I12" s="6" t="inlineStr">
         <is>
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>0.295</v>
+        <v>0.308</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0.28</v>
+        <v>0.301</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="7" t="inlineStr"/>
@@ -1031,28 +1031,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.82</v>
+        <v>0.865</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0.0061</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>11555100</v>
+        <v>13104000</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.73</v>
+        <v>0.66</v>
       </c>
       <c r="H13" t="n">
-        <v>55.61</v>
+        <v>46.09</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1060,10 +1060,10 @@
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.868</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>0.8110000000000001</v>
+        <v>0.869</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="7" t="inlineStr"/>
@@ -1076,28 +1076,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E14" s="3" t="n">
-        <v>-0.0161</v>
+        <v>0.275</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>11273800</v>
+        <v>13101800</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.59</v>
+        <v>1.33</v>
       </c>
       <c r="H14" t="n">
-        <v>47.44</v>
+        <v>41.61</v>
       </c>
       <c r="I14" s="6" t="inlineStr">
         <is>
@@ -1105,10 +1105,10 @@
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>0.308</v>
+        <v>0.296</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>0.301</v>
+        <v>0.28</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="7" t="inlineStr"/>
@@ -1121,39 +1121,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>0.385</v>
+        <v>0.82</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>-0.0128</v>
+        <v>-0.0061</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>11096800</v>
+        <v>12737100</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>1.11</v>
+        <v>0.8</v>
       </c>
       <c r="H15" t="n">
-        <v>28.49</v>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.61</v>
+      </c>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>0.396</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0.406</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="7" t="inlineStr"/>
@@ -1166,33 +1166,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.765</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>0.0132</v>
+        <v>0.39</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10138500</v>
+        <v>11303800</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.17</v>
+        <v>1.13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>33.85</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J16" s="2" t="n"/>
-      <c r="K16" s="2" t="n"/>
+      <c r="J16" s="2" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>0.406</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="7" t="inlineStr"/>
     </row>
@@ -1204,25 +1211,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>0.0132</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9941900</v>
+        <v>10810900</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.42</v>
+        <v>0.18</v>
       </c>
       <c r="I17" s="6" t="inlineStr">
         <is>
@@ -1257,10 +1264,10 @@
         <v>0.06849999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>9931800</v>
+        <v>10087200</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="H18" t="n">
         <v>69.2</v>
@@ -1300,10 +1307,10 @@
         <v>0.0833</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>9888900</v>
+        <v>9958900</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="H19" t="n">
         <v>55.88</v>
@@ -1330,40 +1337,33 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E20" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.25</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9341700</v>
+        <v>9941900</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="H20" t="n">
-        <v>46.09</v>
-      </c>
-      <c r="I20" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="n">
-        <v>0.868</v>
-      </c>
-      <c r="K20" s="2" t="n">
-        <v>0.869</v>
-      </c>
+        <v>0.42</v>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="n"/>
+      <c r="K20" s="2" t="n"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="7" t="inlineStr"/>
     </row>
@@ -1390,10 +1390,10 @@
         <v>-0.04650000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9272800</v>
+        <v>9713500</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="H21" t="n">
         <v>28.47</v>
@@ -1420,39 +1420,39 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0</v>
+        <v>2.02</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>-0.0146</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>8424100</v>
+        <v>9561000</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H22" t="n">
-        <v>36.45</v>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.58</v>
+      </c>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>0.473</v>
+        <v>1.941</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>0.481</v>
+        <v>1.754</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1465,28 +1465,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E23" s="3" t="n">
-        <v>-0.0049</v>
+        <v>0.775</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>8368100</v>
+        <v>9403400</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.29</v>
+        <v>0.61</v>
       </c>
       <c r="H23" t="n">
-        <v>60.07</v>
+        <v>49.91</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>1.943</v>
+        <v>0.775</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1.754</v>
+        <v>0.776</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1525,10 +1525,10 @@
         <v>-0.0238</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>8357700</v>
+        <v>9395800</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.37</v>
+        <v>0.42</v>
       </c>
       <c r="H24" t="n">
         <v>40.25</v>
@@ -1564,19 +1564,19 @@
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.97</v>
+        <v>0.975</v>
       </c>
       <c r="E25" s="3" t="n">
-        <v>-0.0251</v>
+        <v>-0.0201</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8286000</v>
+        <v>8830700</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="H25" t="n">
-        <v>41.14</v>
+        <v>41.71</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1600,39 +1600,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E26" s="8" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>7990100</v>
+        <v>8579900</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="H26" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="I26" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.67</v>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.775</v>
+        <v>0.394</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.776</v>
+        <v>0.379</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1645,28 +1645,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>7071</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>OCR</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.045</v>
+        <v>0.435</v>
       </c>
       <c r="E27" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>7400300</v>
+        <v>8518400</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>3</v>
+        <v>0.23</v>
       </c>
       <c r="H27" t="n">
-        <v>29.14</v>
+        <v>36.45</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.049</v>
+        <v>0.473</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.05</v>
+        <v>0.481</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1690,28 +1690,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="E28" s="3" t="n">
-        <v>-0.0172</v>
+        <v>0.435</v>
+      </c>
+      <c r="E28" s="8" t="n">
+        <v>0.0116</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>7189400</v>
+        <v>8396500</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>1.14</v>
+        <v>0.41</v>
       </c>
       <c r="H28" t="n">
-        <v>35.29</v>
+        <v>55.91</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.312</v>
+        <v>0.424</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0.334</v>
+        <v>0.371</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="7" t="inlineStr"/>
@@ -1735,39 +1735,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E29" s="3" t="n">
-        <v>-0.0154</v>
+        <v>0.63</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>7109400</v>
+        <v>8288800</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.39</v>
+        <v>0.76</v>
       </c>
       <c r="H29" t="n">
-        <v>45.65</v>
-      </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.52</v>
+      </c>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>2.635</v>
+        <v>0.619</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>2.556</v>
+        <v>0.616</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1780,28 +1780,28 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>0.44</v>
+        <v>2.55</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-0.033</v>
+        <v>-0.0154</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>7053900</v>
+        <v>8103600</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.31</v>
+        <v>0.45</v>
       </c>
       <c r="H30" t="n">
-        <v>25.77</v>
+        <v>45.65</v>
       </c>
       <c r="I30" s="6" t="inlineStr">
         <is>
@@ -1809,10 +1809,10 @@
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.501</v>
+        <v>2.635</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0.665</v>
+        <v>2.556</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1840,10 +1840,10 @@
         <v>-0.0182</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7014900</v>
+        <v>7889500</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.34</v>
+        <v>0.38</v>
       </c>
       <c r="H31" t="n">
         <v>45.28</v>
@@ -1870,28 +1870,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8877</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>EKOVEST</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="E32" s="8" t="n">
-        <v>0.0588</v>
+        <v>0.0286</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>6986200</v>
+        <v>7775400</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>1.35</v>
+        <v>0.35</v>
       </c>
       <c r="H32" t="n">
-        <v>56.69</v>
+        <v>44.12</v>
       </c>
       <c r="I32" s="6" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.175</v>
+        <v>0.188</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0.182</v>
+        <v>0.186</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="7" t="inlineStr"/>
@@ -1915,28 +1915,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>7071</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>OCR</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E33" s="8" t="n">
-        <v>0.0247</v>
+        <v>0.045</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>6648200</v>
+        <v>7400400</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.54</v>
+        <v>3</v>
       </c>
       <c r="H33" t="n">
-        <v>57.67</v>
+        <v>29.14</v>
       </c>
       <c r="I33" s="6" t="inlineStr">
         <is>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0.394</v>
+        <v>0.049</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>0.379</v>
+        <v>0.05</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="7" t="inlineStr"/>
@@ -1960,39 +1960,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>6807</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PUNCAK</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E34" s="8" t="n">
-        <v>0.0256</v>
+        <v>0.44</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>-0.033</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>6390800</v>
+        <v>7332500</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>16.77</v>
+        <v>0.32</v>
       </c>
       <c r="H34" t="n">
-        <v>82.42</v>
-      </c>
-      <c r="I34" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.77</v>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.177</v>
+        <v>0.501</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0.171</v>
+        <v>0.665</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="7" t="inlineStr"/>
@@ -2005,39 +2005,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E35" s="10" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>6366600</v>
+        <v>7320700</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.58</v>
+        <v>1.16</v>
       </c>
       <c r="H35" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="I35" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.77</v>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>0.619</v>
+        <v>0.312</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>0.616</v>
+        <v>0.334</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="7" t="inlineStr"/>
@@ -2050,28 +2050,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>8877</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>EKOVEST</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0</v>
+        <v>0.18</v>
+      </c>
+      <c r="E36" s="8" t="n">
+        <v>0.0588</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>6008500</v>
+        <v>6986200</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.29</v>
+        <v>1.35</v>
       </c>
       <c r="H36" t="n">
-        <v>54.75</v>
+        <v>56.69</v>
       </c>
       <c r="I36" s="6" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>0.423</v>
+        <v>0.175</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0.371</v>
+        <v>0.182</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="7" t="inlineStr"/>
@@ -2095,39 +2095,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>6807</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>PUNCAK</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.655</v>
-      </c>
-      <c r="E37" s="3" t="n">
-        <v>-0.09660000000000001</v>
+        <v>0.2</v>
+      </c>
+      <c r="E37" s="8" t="n">
+        <v>0.0256</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>5990200</v>
+        <v>6391000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1.16</v>
+        <v>16.77</v>
       </c>
       <c r="H37" t="n">
-        <v>37.19</v>
-      </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>82.42</v>
+      </c>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.75</v>
+        <v>0.177</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.171</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="7" t="inlineStr"/>
@@ -2140,39 +2140,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E38" s="8" t="n">
-        <v>0.0303</v>
+        <v>0.66</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>-0.0897</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>5925400</v>
+        <v>6133700</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1.98</v>
+        <v>1.19</v>
       </c>
       <c r="H38" t="n">
-        <v>64.43000000000001</v>
-      </c>
-      <c r="I38" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.73</v>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.157</v>
+        <v>0.751</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.155</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2185,39 +2185,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E39" s="8" t="n">
+        <v>0.0303</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>5162000</v>
+        <v>6093800</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.67</v>
+        <v>2.03</v>
       </c>
       <c r="H39" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.43000000000001</v>
+      </c>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>0.353</v>
+        <v>0.157</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>0.328</v>
+        <v>0.155</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="7" t="inlineStr"/>
@@ -2230,28 +2230,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
         <v>0.175</v>
       </c>
-      <c r="E40" s="10" t="n">
-        <v>0</v>
+      <c r="E40" s="3" t="n">
+        <v>-0.0541</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5065700</v>
+        <v>5810900</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.23</v>
+        <v>1.42</v>
       </c>
       <c r="H40" t="n">
-        <v>40.18</v>
+        <v>24.82</v>
       </c>
       <c r="I40" s="6" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.188</v>
+        <v>0.197</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.185</v>
+        <v>0.207</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2275,28 +2275,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.62</v>
+        <v>1.3</v>
       </c>
       <c r="E41" s="8" t="n">
-        <v>0.0062</v>
+        <v>0.0156</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5057600</v>
+        <v>5614400</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="H41" t="n">
-        <v>47.87</v>
+        <v>64.47</v>
       </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
@@ -2304,10 +2304,10 @@
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.623</v>
+        <v>1.208</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.689</v>
+        <v>1.193</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2320,28 +2320,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E42" s="8" t="n">
-        <v>0.0133</v>
+        <v>1.15</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>4812200</v>
+        <v>5340200</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="H42" t="n">
-        <v>60.65</v>
+        <v>34.18</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.372</v>
+        <v>1.225</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>0.369</v>
+        <v>1.316</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2365,39 +2365,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>3.89</v>
+        <v>1.62</v>
       </c>
       <c r="E43" s="8" t="n">
-        <v>0.013</v>
+        <v>0.0062</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>4417500</v>
+        <v>5289600</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.51</v>
+        <v>0.72</v>
       </c>
       <c r="H43" t="n">
-        <v>59.95</v>
-      </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.87</v>
+      </c>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>3.675</v>
+        <v>1.623</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3.057</v>
+        <v>1.689</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2410,39 +2410,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E44" s="8" t="n">
-        <v>0.0021</v>
+        <v>0.35</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>4392500</v>
+        <v>5193000</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.21</v>
+        <v>0.67</v>
       </c>
       <c r="H44" t="n">
-        <v>47.71</v>
-      </c>
-      <c r="I44" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.51</v>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>4.728</v>
+        <v>0.353</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>4.84</v>
+        <v>0.328</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2455,39 +2455,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E45" s="3" t="n">
-        <v>-0.005</v>
+        <v>0.375</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4332600</v>
+        <v>4988200</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.36</v>
+        <v>0.68</v>
       </c>
       <c r="H45" t="n">
-        <v>32.46</v>
-      </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.92</v>
+      </c>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>2.134</v>
+        <v>0.371</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.235</v>
+        <v>0.369</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2500,28 +2500,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>7.27</v>
+        <v>4.74</v>
       </c>
       <c r="E46" s="8" t="n">
-        <v>0.0097</v>
+        <v>0.0064</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4328600</v>
+        <v>4927400</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.43</v>
+        <v>0.24</v>
       </c>
       <c r="H46" t="n">
-        <v>35.91</v>
+        <v>49.36</v>
       </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
@@ -2529,10 +2529,10 @@
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>7.436</v>
+        <v>4.729</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>7.919</v>
+        <v>4.84</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2545,28 +2545,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E47" s="3" t="n">
-        <v>-0.008500000000000001</v>
+        <v>7.3</v>
+      </c>
+      <c r="E47" s="8" t="n">
+        <v>0.0139</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4170500</v>
+        <v>4847400</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.53</v>
+        <v>0.48</v>
       </c>
       <c r="H47" t="n">
-        <v>35.26</v>
+        <v>37.79</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.226</v>
+        <v>7.439</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>1.316</v>
+        <v>7.92</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2590,39 +2590,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>1.29</v>
+        <v>3.87</v>
       </c>
       <c r="E48" s="8" t="n">
         <v>0.007800000000000001</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4132300</v>
+        <v>4618000</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.66</v>
+        <v>0.53</v>
       </c>
       <c r="H48" t="n">
-        <v>63.52</v>
-      </c>
-      <c r="I48" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.48</v>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.207</v>
+        <v>3.673</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1.192</v>
+        <v>3.056</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2635,28 +2635,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.545</v>
+        <v>0.335</v>
       </c>
       <c r="E49" s="3" t="n">
-        <v>-0.0268</v>
+        <v>-0.0147</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>4069400</v>
+        <v>4604300</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="H49" t="n">
-        <v>33.38</v>
+        <v>47.18</v>
       </c>
       <c r="I49" s="6" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.637</v>
+        <v>0.345</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.619</v>
+        <v>0.335</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2680,28 +2680,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3969800</v>
+        <v>4601700</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
       <c r="H50" t="n">
-        <v>49.14</v>
+        <v>31.74</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.346</v>
+        <v>2.134</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0.335</v>
+        <v>2.235</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2725,28 +2725,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.135</v>
+        <v>0.27</v>
       </c>
       <c r="E51" s="3" t="n">
         <v>-0.0357</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3878000</v>
+        <v>4584600</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.06</v>
+        <v>0.78</v>
       </c>
       <c r="H51" t="n">
-        <v>40.16</v>
+        <v>19.52</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.157</v>
+        <v>0.327</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.141</v>
+        <v>0.369</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2770,28 +2770,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="E52" s="3" t="n">
-        <v>-0.0417</v>
+        <v>5.32</v>
+      </c>
+      <c r="E52" s="8" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>3865300</v>
+        <v>4460100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="H52" t="n">
-        <v>32.68</v>
+        <v>43.13</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.14</v>
+        <v>5.49</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>0.149</v>
+        <v>5.47</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2815,39 +2815,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>0.14</v>
       </c>
       <c r="E53" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>3774000</v>
+        <v>4331000</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.67</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I53" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.14</v>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.795</v>
+        <v>0.157</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.773</v>
+        <v>0.141</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2860,28 +2860,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>3512500</v>
+        <v>4319500</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.61</v>
+        <v>0.47</v>
       </c>
       <c r="H54" t="n">
-        <v>34.49</v>
+        <v>32.82</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.176</v>
+        <v>0.636</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.196</v>
+        <v>0.619</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2905,39 +2905,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E55" s="3" t="n">
-        <v>-0.0115</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>3492700</v>
+        <v>4074000</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.5</v>
+        <v>0.72</v>
       </c>
       <c r="H55" t="n">
-        <v>52.29</v>
-      </c>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I55" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.425</v>
+        <v>0.795</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.417</v>
+        <v>0.773</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2950,28 +2950,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.18</v>
+        <v>0.845</v>
       </c>
       <c r="E56" s="3" t="n">
-        <v>-0.027</v>
+        <v>-0.0287</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>3416500</v>
+        <v>4006100</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.83</v>
+        <v>0.54</v>
       </c>
       <c r="H56" t="n">
-        <v>27.5</v>
+        <v>40.43</v>
       </c>
       <c r="I56" s="6" t="inlineStr">
         <is>
@@ -2979,10 +2979,10 @@
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.197</v>
+        <v>0.92</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.207</v>
+        <v>0.85</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2995,28 +2995,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E57" s="3" t="n">
-        <v>-0.0179</v>
+        <v>7.16</v>
+      </c>
+      <c r="E57" s="8" t="n">
+        <v>0.0014</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3352100</v>
+        <v>3956100</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="H57" t="n">
-        <v>44.46</v>
+        <v>33.47</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.289</v>
+        <v>7.472</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0.283</v>
+        <v>7.672</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3040,28 +3040,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0</v>
+        <v>0.11</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>-0.0833</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3336000</v>
+        <v>3926300</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>2.37</v>
+        <v>0.19</v>
       </c>
       <c r="H58" t="n">
-        <v>41.4</v>
+        <v>30.91</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.129</v>
+        <v>0.14</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.13</v>
+        <v>0.148</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3085,28 +3085,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.85</v>
+        <v>0.43</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>-0.023</v>
+        <v>-0.0115</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3273500</v>
+        <v>3752000</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="H59" t="n">
-        <v>40.99</v>
+        <v>52.29</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.92</v>
+        <v>0.425</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.85</v>
+        <v>0.417</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3130,28 +3130,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="E60" s="8" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.165</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3257700</v>
+        <v>3543300</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.24</v>
+        <v>0.62</v>
       </c>
       <c r="H60" t="n">
-        <v>41.82</v>
+        <v>34.49</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>5.488</v>
+        <v>0.176</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>5.47</v>
+        <v>0.196</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3175,28 +3175,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1.43</v>
+        <v>2.67</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>-0.0069</v>
+        <v>-0.0074</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3197600</v>
+        <v>3459800</v>
       </c>
       <c r="G61" s="5" t="n">
         <v>0.28</v>
       </c>
       <c r="H61" t="n">
-        <v>21.73</v>
+        <v>43.48</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.668</v>
+        <v>2.754</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>1.931</v>
+        <v>2.741</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3220,28 +3220,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E62" s="3" t="n">
-        <v>-0.0049</v>
+        <v>6.69</v>
+      </c>
+      <c r="E62" s="8" t="n">
+        <v>0.0015</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3004500</v>
+        <v>3457000</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.91</v>
+        <v>0.33</v>
       </c>
       <c r="H62" t="n">
-        <v>44.31</v>
+        <v>29.21</v>
       </c>
       <c r="I62" s="6" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>2.042</v>
+        <v>7.159</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2.069</v>
+        <v>7.581</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="7" t="inlineStr"/>
@@ -3265,39 +3265,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="E63" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.125</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>2943300</v>
+        <v>3371000</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.92</v>
+        <v>2.4</v>
       </c>
       <c r="H63" t="n">
-        <v>86.5</v>
-      </c>
-      <c r="I63" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.4</v>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2.873</v>
+        <v>0.129</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>2.456</v>
+        <v>0.13</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3310,28 +3310,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>7.17</v>
-      </c>
-      <c r="E64" s="8" t="n">
-        <v>0.0028</v>
+        <v>0.275</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>-0.0179</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>2909500</v>
+        <v>3355300</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.18</v>
+        <v>0.29</v>
       </c>
       <c r="H64" t="n">
-        <v>34.03</v>
+        <v>44.46</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>7.473</v>
+        <v>0.289</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>7.672</v>
+        <v>0.283</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3355,28 +3355,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>0.76</v>
+        <v>1.43</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.013</v>
+        <v>-0.0069</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>2883400</v>
+        <v>3329200</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>2.33</v>
+        <v>0.29</v>
       </c>
       <c r="H65" t="n">
-        <v>58.88</v>
+        <v>21.73</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>0.748</v>
+        <v>1.668</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0.72</v>
+        <v>1.931</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3400,28 +3400,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>2.68</v>
+        <v>0.91</v>
       </c>
       <c r="E66" s="3" t="n">
-        <v>-0.0037</v>
+        <v>-0.0215</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>2791500</v>
+        <v>3177900</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.22</v>
+        <v>0.78</v>
       </c>
       <c r="H66" t="n">
-        <v>44.15</v>
+        <v>22.95</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>2.754</v>
+        <v>0.964</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>2.741</v>
+        <v>1.048</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3445,39 +3445,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.405</v>
+        <v>0.52</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.0581</v>
+        <v>-0.0459</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>2746200</v>
+        <v>3144100</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.48</v>
+        <v>0.59</v>
       </c>
       <c r="H67" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="I67" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.45</v>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.393</v>
+        <v>0.556</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.362</v>
+        <v>0.518</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3490,28 +3490,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E68" s="3" t="n">
-        <v>-0.08039999999999999</v>
+        <v>2.03</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>2705800</v>
+        <v>3080100</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.66</v>
+        <v>0.93</v>
       </c>
       <c r="H68" t="n">
-        <v>58.69</v>
+        <v>46.01</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.848</v>
+        <v>2.043</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0.586</v>
+        <v>2.069</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3535,28 +3535,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>0.91</v>
+        <v>5.6</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>-0.0215</v>
+        <v>-0.0014</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2684800</v>
+        <v>2985000</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.66</v>
+        <v>0.39</v>
       </c>
       <c r="H69" t="n">
-        <v>22.95</v>
+        <v>28.93</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.964</v>
+        <v>5.875</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1.048</v>
+        <v>6.164</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3580,39 +3580,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E70" s="3" t="n">
-        <v>-0.0367</v>
+        <v>0.625</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2646800</v>
+        <v>2979000</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.5</v>
+        <v>0.89</v>
       </c>
       <c r="H70" t="n">
-        <v>44.43</v>
-      </c>
-      <c r="I70" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>70.16</v>
+      </c>
+      <c r="I70" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.618</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.518</v>
+        <v>0.606</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3625,28 +3625,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.865</v>
+        <v>0.765</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2563000</v>
+        <v>2955800</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>0.84</v>
+        <v>2.39</v>
       </c>
       <c r="H71" t="n">
-        <v>51.48</v>
+        <v>61.83</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.865</v>
+        <v>0.749</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.86</v>
+        <v>0.721</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3670,39 +3670,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>6.72</v>
+        <v>3.27</v>
       </c>
       <c r="E72" s="8" t="n">
-        <v>0.006</v>
+        <v>0.0391</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2543400</v>
+        <v>2950500</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.25</v>
+        <v>0.93</v>
       </c>
       <c r="H72" t="n">
-        <v>30.63</v>
-      </c>
-      <c r="I72" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>86.5</v>
+      </c>
+      <c r="I72" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>7.162</v>
+        <v>2.873</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>7.581</v>
+        <v>2.456</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3715,39 +3715,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.835</v>
+        <v>0.405</v>
       </c>
       <c r="E73" s="3" t="n">
-        <v>-0.0118</v>
+        <v>-0.0581</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2504200</v>
+        <v>2927800</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.83</v>
+        <v>0.52</v>
       </c>
       <c r="H73" t="n">
-        <v>15.99</v>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.56</v>
+      </c>
+      <c r="I73" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.908</v>
+        <v>0.393</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.97</v>
+        <v>0.362</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3760,28 +3760,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.465</v>
+        <v>0.915</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>-0.0312</v>
+        <v>-0.08039999999999999</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2482700</v>
+        <v>2764000</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.29</v>
+        <v>0.67</v>
       </c>
       <c r="H74" t="n">
-        <v>35.11</v>
+        <v>58.69</v>
       </c>
       <c r="I74" s="6" t="inlineStr">
         <is>
@@ -3789,10 +3789,10 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.503</v>
+        <v>0.848</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.523</v>
+        <v>0.586</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3805,28 +3805,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="E75" s="3" t="n">
-        <v>-0.008</v>
+        <v>2.46</v>
+      </c>
+      <c r="E75" s="8" t="n">
+        <v>0.008199999999999999</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2433800</v>
+        <v>2726300</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.28</v>
+        <v>0.24</v>
       </c>
       <c r="H75" t="n">
-        <v>39.92</v>
+        <v>53.17</v>
       </c>
       <c r="I75" s="6" t="inlineStr">
         <is>
@@ -3834,10 +3834,10 @@
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>1.293</v>
+        <v>2.447</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>1.314</v>
+        <v>2.392</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="7" t="inlineStr"/>
@@ -3850,28 +3850,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>5.6</v>
+        <v>0.835</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>-0.0014</v>
+        <v>-0.0118</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2403100</v>
+        <v>2684300</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.31</v>
+        <v>0.89</v>
       </c>
       <c r="H76" t="n">
-        <v>28.93</v>
+        <v>15.99</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>5.875</v>
+        <v>0.908</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>6.164</v>
+        <v>0.97</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3895,28 +3895,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0</v>
+        <v>1.1</v>
+      </c>
+      <c r="E77" s="8" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2298900</v>
+        <v>2628500</v>
       </c>
       <c r="G77" s="5" t="n">
         <v>0.28</v>
       </c>
       <c r="H77" t="n">
-        <v>27.74</v>
+        <v>54.09</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.274</v>
+        <v>1.08</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>0.3</v>
+        <v>1.047</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2185100</v>
+        <v>2574700</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="H78" t="n">
-        <v>52.65</v>
+        <v>36.31</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>1.079</v>
+        <v>0.503</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>1.047</v>
+        <v>0.523</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3985,28 +3985,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E79" s="8" t="n">
-        <v>0.0111</v>
+        <v>1.24</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2136000</v>
+        <v>2564700</v>
       </c>
       <c r="G79" s="5" t="n">
         <v>0.29</v>
       </c>
       <c r="H79" t="n">
-        <v>30.38</v>
+        <v>39.92</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.493</v>
+        <v>1.293</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>0.552</v>
+        <v>1.314</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4030,28 +4030,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.76</v>
+        <v>0.865</v>
       </c>
       <c r="E80" s="3" t="n">
-        <v>-0.013</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2083200</v>
+        <v>2563000</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.25</v>
+        <v>0.84</v>
       </c>
       <c r="H80" t="n">
-        <v>47</v>
+        <v>51.48</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.77</v>
+        <v>0.865</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.771</v>
+        <v>0.86</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4075,39 +4075,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>SKYWLD</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E81" s="8" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.335</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>-0.08220000000000001</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2060400</v>
+        <v>2539000</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="H81" t="n">
-        <v>48.48</v>
-      </c>
-      <c r="I81" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.71</v>
+      </c>
+      <c r="I81" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.379</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.391</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="7" t="inlineStr"/>
@@ -4120,39 +4120,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.62</v>
+        <v>0.765</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>-0.0313</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2054800</v>
+        <v>2361200</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>11.46</v>
+        <v>0.29</v>
       </c>
       <c r="H82" t="n">
-        <v>69.41</v>
-      </c>
-      <c r="I82" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.22</v>
+      </c>
+      <c r="I82" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.771</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.546</v>
+        <v>0.772</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4165,39 +4165,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>0.625</v>
+        <v>0.45</v>
       </c>
       <c r="E83" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2042800</v>
+        <v>2309100</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.61</v>
+        <v>0.31</v>
       </c>
       <c r="H83" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="I83" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.78</v>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.618</v>
+        <v>0.493</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>0.606</v>
+        <v>0.552</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="7" t="inlineStr"/>
@@ -4210,28 +4210,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E84" s="8" t="n">
-        <v>0.0325</v>
+        <v>4.81</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2032800</v>
+        <v>2305600</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.82</v>
+        <v>0.09</v>
       </c>
       <c r="H84" t="n">
-        <v>60.16</v>
+        <v>46.62</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>0.742</v>
+        <v>4.894</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0.706</v>
+        <v>4.736</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4255,28 +4255,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E85" s="3" t="n">
-        <v>-0.0103</v>
+        <v>0.26</v>
+      </c>
+      <c r="E85" s="8" t="n">
+        <v>0.0196</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1995900</v>
+        <v>2299100</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.08</v>
+        <v>0.28</v>
       </c>
       <c r="H85" t="n">
-        <v>46.11</v>
+        <v>33.4</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>4.893</v>
+        <v>0.275</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>4.736</v>
+        <v>0.3</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4300,39 +4300,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>5315</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SKYWLD</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E86" s="3" t="n">
-        <v>-0.06849999999999999</v>
+        <v>1.93</v>
+      </c>
+      <c r="E86" s="8" t="n">
+        <v>0.0158</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>1994900</v>
+        <v>2280000</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>1.71</v>
+        <v>0.39</v>
       </c>
       <c r="H86" t="n">
-        <v>26</v>
-      </c>
-      <c r="I86" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.3</v>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.38</v>
+        <v>1.921</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>0.391</v>
+        <v>1.949</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4345,28 +4345,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="E87" s="3" t="n">
-        <v>-0.05</v>
+        <v>0.79</v>
+      </c>
+      <c r="E87" s="8" t="n">
+        <v>0.026</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>1902300</v>
+        <v>2262700</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.33</v>
+        <v>0.91</v>
       </c>
       <c r="H87" t="n">
-        <v>53.44</v>
+        <v>59.57</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4374,10 +4374,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.57</v>
+        <v>0.741</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.473</v>
+        <v>0.706</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4390,39 +4390,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>2.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>0.0123</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>1891900</v>
+        <v>2253400</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>0.17</v>
+        <v>1.1</v>
       </c>
       <c r="H88" t="n">
-        <v>54.36</v>
-      </c>
-      <c r="I88" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.48</v>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>2.448</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>2.392</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4435,28 +4435,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>0.51</v>
+        <v>4.95</v>
       </c>
       <c r="E89" s="3" t="n">
-        <v>-0.0097</v>
+        <v>-0.008</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>1879700</v>
+        <v>2125900</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.71</v>
+        <v>0.54</v>
       </c>
       <c r="H89" t="n">
-        <v>31.58</v>
+        <v>43.23</v>
       </c>
       <c r="I89" s="6" t="inlineStr">
         <is>
@@ -4464,10 +4464,10 @@
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.54</v>
+        <v>5.048</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0.569</v>
+        <v>5.052</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4480,39 +4480,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="E90" s="8" t="n">
-        <v>0.0211</v>
+        <v>0.515</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>1869800</v>
+        <v>2108700</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.32</v>
+        <v>0.79</v>
       </c>
       <c r="H90" t="n">
-        <v>51.67</v>
-      </c>
-      <c r="I90" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.15</v>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>1.922</v>
+        <v>0.54</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>1.95</v>
+        <v>0.569</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4525,28 +4525,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E91" s="8" t="n">
-        <v>0.0698</v>
+        <v>0.62</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>1825500</v>
+        <v>2054800</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>1.79</v>
+        <v>11.46</v>
       </c>
       <c r="H91" t="n">
-        <v>78.56</v>
+        <v>69.41</v>
       </c>
       <c r="I91" s="9" t="inlineStr">
         <is>
@@ -4554,10 +4554,10 @@
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.21</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.21</v>
+        <v>0.546</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4570,28 +4570,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>0.44</v>
+        <v>9.98</v>
       </c>
       <c r="E92" s="8" t="n">
-        <v>0.0476</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>1772500</v>
+        <v>2040900</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.84</v>
+        <v>0.15</v>
       </c>
       <c r="H92" t="n">
-        <v>61.36</v>
+        <v>46.87</v>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>0.419</v>
+        <v>9.999000000000001</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>0.433</v>
+        <v>10.138</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4624,19 +4624,19 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>-0.0164</v>
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1740200</v>
+        <v>1994700</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="H93" t="n">
-        <v>22.42</v>
+        <v>22.97</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.374</v>
+        <v>1.375</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.55</v>
+        <v>1.551</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4660,39 +4660,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E94" s="8" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>-0.0667</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>1727900</v>
+        <v>1983000</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>0.13</v>
+        <v>0.34</v>
       </c>
       <c r="H94" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="I94" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.01</v>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>9.999000000000001</v>
+        <v>0.569</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>10.138</v>
+        <v>0.473</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4714,19 +4714,19 @@
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>3.92</v>
+        <v>3.89</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>-0.0101</v>
+        <v>-0.0177</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1676600</v>
+        <v>1922100</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="H95" t="n">
-        <v>51.12</v>
+        <v>50.09</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>3.957</v>
+        <v>3.954</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>3.572</v>
+        <v>3.571</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4750,28 +4750,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="E96" s="3" t="n">
-        <v>-0.008</v>
+        <v>2.49</v>
+      </c>
+      <c r="E96" s="8" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1638400</v>
+        <v>1837700</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.41</v>
+        <v>0.61</v>
       </c>
       <c r="H96" t="n">
-        <v>43.23</v>
+        <v>39.94</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>5.048</v>
+        <v>2.549</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>5.052</v>
+        <v>2.676</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>2.48</v>
+        <v>0.44</v>
       </c>
       <c r="E97" s="8" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.0476</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1618300</v>
+        <v>1829900</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.54</v>
+        <v>0.86</v>
       </c>
       <c r="H97" t="n">
-        <v>38.57</v>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.36</v>
+      </c>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2.548</v>
+        <v>0.419</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2.676</v>
+        <v>0.433</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4840,39 +4840,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E98" s="3" t="n">
-        <v>-0.0179</v>
+        <v>0.23</v>
+      </c>
+      <c r="E98" s="8" t="n">
+        <v>0.0698</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1610800</v>
+        <v>1825600</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.28</v>
+        <v>1.79</v>
       </c>
       <c r="H98" t="n">
-        <v>20.38</v>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.56</v>
+      </c>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.327</v>
+        <v>0.21</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.369</v>
+        <v>0.21</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4894,19 +4894,19 @@
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.63</v>
+        <v>0.625</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>-0.0233</v>
+        <v>-0.031</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1605100</v>
+        <v>1791600</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H99" t="n">
-        <v>40</v>
+        <v>39.21</v>
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
@@ -4930,28 +4930,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>0.255</v>
+        <v>2.34</v>
       </c>
       <c r="E100" s="3" t="n">
-        <v>-0.0192</v>
+        <v>-0.064</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1542600</v>
+        <v>1720800</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="H100" t="n">
-        <v>40.54</v>
+        <v>28.06</v>
       </c>
       <c r="I100" s="6" t="inlineStr">
         <is>
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.272</v>
+        <v>2.764</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0.292</v>
+        <v>2.878</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4975,28 +4975,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>2.36</v>
+        <v>0.58</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.05599999999999999</v>
+        <v>-0.0252</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1511300</v>
+        <v>1682400</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="H101" t="n">
-        <v>28.57</v>
+        <v>46.78</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>2.766</v>
+        <v>0.596</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>2.879</v>
+        <v>0.586</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5020,39 +5020,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0</v>
+        <v>2.09</v>
+      </c>
+      <c r="E102" s="8" t="n">
+        <v>0.0048</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1454800</v>
+        <v>1660800</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="H102" t="n">
-        <v>41.34</v>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.56</v>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.434</v>
+        <v>2.105</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0.435</v>
+        <v>2.102</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5065,28 +5065,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>0.8149999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-0.0121</v>
+        <v>-0.0075</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1427700</v>
+        <v>1618000</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.41</v>
+        <v>0.79</v>
       </c>
       <c r="H103" t="n">
-        <v>49.71</v>
+        <v>37.05</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>0.825</v>
+        <v>1.363</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>0.785</v>
+        <v>1.342</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5110,39 +5110,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0261</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>0.365</v>
+        <v>6.48</v>
       </c>
       <c r="E104" s="3" t="n">
-        <v>-0.1205</v>
+        <v>-0.0107</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1408400</v>
+        <v>1597900</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>2.97</v>
+        <v>0.27</v>
       </c>
       <c r="H104" t="n">
-        <v>46.29</v>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.43</v>
+      </c>
+      <c r="I104" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.38</v>
+        <v>6.206</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>0.365</v>
+        <v>5.931</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5155,28 +5155,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1407300</v>
+        <v>1582600</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.74</v>
+        <v>0.23</v>
       </c>
       <c r="H105" t="n">
-        <v>42.1</v>
+        <v>40.54</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.728</v>
+        <v>0.272</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.744</v>
+        <v>0.292</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5200,28 +5200,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>0.235</v>
+        <v>2.84</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.0208</v>
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1405700</v>
+        <v>1559800</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.8</v>
+        <v>0.17</v>
       </c>
       <c r="H106" t="n">
-        <v>36.08</v>
+        <v>54.45</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.252</v>
+        <v>2.801</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>0.273</v>
+        <v>2.672</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5245,39 +5245,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E107" s="8" t="n">
-        <v>0.0152</v>
+        <v>1.37</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>-0.0552</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1397300</v>
+        <v>1519900</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.29</v>
+        <v>2.02</v>
       </c>
       <c r="H107" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="I107" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>26.48</v>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.335</v>
+        <v>1.491</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0.343</v>
+        <v>1.502</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5290,28 +5290,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.215</v>
-      </c>
-      <c r="E108" s="3" t="n">
-        <v>-0.0227</v>
+        <v>0.405</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1383900</v>
+        <v>1501600</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>1.84</v>
+        <v>0.16</v>
       </c>
       <c r="H108" t="n">
-        <v>42.03</v>
+        <v>41.34</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.223</v>
+        <v>0.434</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.232</v>
+        <v>0.435</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5335,39 +5335,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E109" s="8" t="n">
-        <v>0.0048</v>
+        <v>0.725</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>-0.0268</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1377100</v>
+        <v>1471500</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="H109" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I109" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.44</v>
+      </c>
+      <c r="I109" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>2.105</v>
+        <v>0.741</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>2.102</v>
+        <v>0.679</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5395,10 +5395,10 @@
         <v>-0.018</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1362600</v>
+        <v>1470800</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H110" t="n">
         <v>41.92</v>
@@ -5425,39 +5425,39 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E111" s="3" t="n">
-        <v>-0.0154</v>
+        <v>0.715</v>
+      </c>
+      <c r="E111" s="8" t="n">
+        <v>0.006999999999999999</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1360900</v>
+        <v>1468200</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.22</v>
+        <v>0.77</v>
       </c>
       <c r="H111" t="n">
-        <v>62.32</v>
-      </c>
-      <c r="I111" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.05</v>
+      </c>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.929</v>
+        <v>0.729</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.88</v>
+        <v>0.744</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5470,28 +5470,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0261</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>2.85</v>
+        <v>0.38</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>-0.0035</v>
+        <v>-0.0843</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1359900</v>
+        <v>1450900</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>0.15</v>
+        <v>3.06</v>
       </c>
       <c r="H112" t="n">
-        <v>55.12</v>
+        <v>51.34</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>2.802</v>
+        <v>0.382</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>2.672</v>
+        <v>0.365</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5515,39 +5515,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>6.5</v>
+        <v>3.78</v>
       </c>
       <c r="E113" s="3" t="n">
-        <v>-0.0076</v>
+        <v>-0.0182</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1355200</v>
+        <v>1450200</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.23</v>
+        <v>0.49</v>
       </c>
       <c r="H113" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="I113" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.34</v>
+      </c>
+      <c r="I113" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>6.208</v>
+        <v>3.844</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>5.931</v>
+        <v>3.699</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5560,28 +5560,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.22</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E114" s="3" t="n">
-        <v>-0.0435</v>
+        <v>-0.0121</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1309200</v>
+        <v>1438700</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="H114" t="n">
-        <v>53.76</v>
+        <v>49.71</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.221</v>
+        <v>0.825</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.185</v>
+        <v>0.785</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5605,28 +5605,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E115" s="3" t="n">
-        <v>-0.008399999999999999</v>
+        <v>1.11</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1308100</v>
+        <v>1437900</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H115" t="n">
-        <v>49.02</v>
+        <v>58.81</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.597</v>
+        <v>1.06</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.586</v>
+        <v>0.923</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5650,39 +5650,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.725</v>
+        <v>0.96</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>-0.0268</v>
+        <v>-0.0154</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1284800</v>
+        <v>1416700</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
       <c r="H116" t="n">
-        <v>49.44</v>
-      </c>
-      <c r="I116" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.32</v>
+      </c>
+      <c r="I116" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.741</v>
+        <v>0.929</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.679</v>
+        <v>0.88</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5695,28 +5695,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1.4</v>
+        <v>0.235</v>
       </c>
       <c r="E117" s="3" t="n">
-        <v>-0.0345</v>
+        <v>-0.0208</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1281200</v>
+        <v>1405700</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="H117" t="n">
-        <v>29.57</v>
+        <v>36.08</v>
       </c>
       <c r="I117" s="6" t="inlineStr">
         <is>
@@ -5724,10 +5724,10 @@
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>1.494</v>
+        <v>0.252</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>1.503</v>
+        <v>0.273</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5740,39 +5740,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>1.26</v>
+        <v>0.58</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0252</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1271800</v>
+        <v>1405600</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
       <c r="H118" t="n">
-        <v>48.87</v>
-      </c>
-      <c r="I118" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.84</v>
+      </c>
+      <c r="I118" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.285</v>
+        <v>0.517</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>1.229</v>
+        <v>0.472</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5785,39 +5785,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E119" s="3" t="n">
-        <v>-0.03759999999999999</v>
+        <v>0.335</v>
+      </c>
+      <c r="E119" s="8" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1258100</v>
+        <v>1405300</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.38</v>
+        <v>0.29</v>
       </c>
       <c r="H119" t="n">
-        <v>32.17</v>
-      </c>
-      <c r="I119" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.93</v>
+      </c>
+      <c r="I119" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.716</v>
+        <v>0.335</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.743</v>
+        <v>0.343</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5830,28 +5830,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E120" s="10" t="n">
-        <v>0</v>
+        <v>0.215</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1252400</v>
+        <v>1383900</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>0.37</v>
+        <v>1.84</v>
       </c>
       <c r="H120" t="n">
-        <v>49.45</v>
+        <v>42.03</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.236</v>
+        <v>0.223</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1.077</v>
+        <v>0.232</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5875,39 +5875,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>0.58</v>
+        <v>1.25</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>-0.0252</v>
+        <v>-0.0157</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1252100</v>
+        <v>1378500</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.3</v>
+        <v>0.44</v>
       </c>
       <c r="H121" t="n">
-        <v>65.84</v>
-      </c>
-      <c r="I121" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.08</v>
+      </c>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.517</v>
+        <v>1.284</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0.472</v>
+        <v>1.229</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5920,28 +5920,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E122" s="8" t="n">
-        <v>0.0075</v>
+        <v>1.2</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1246000</v>
+        <v>1370700</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="H122" t="n">
-        <v>39.24</v>
+        <v>49.45</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.742</v>
+        <v>1.236</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>0.723</v>
+        <v>1.077</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5965,39 +5965,39 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.275</v>
+        <v>0.225</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>-0.0179</v>
+        <v>-0.0217</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1239800</v>
+        <v>1310700</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>1.33</v>
+        <v>0.68</v>
       </c>
       <c r="H123" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="I123" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.71</v>
+      </c>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.276</v>
+        <v>0.221</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.268</v>
+        <v>0.185</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6010,28 +6010,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E124" s="10" t="n">
-        <v>0</v>
+        <v>0.675</v>
+      </c>
+      <c r="E124" s="8" t="n">
+        <v>0.0075</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1218400</v>
+        <v>1272600</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.6</v>
+        <v>0.08</v>
       </c>
       <c r="H124" t="n">
-        <v>40.19</v>
+        <v>39.24</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>1.364</v>
+        <v>0.742</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>1.342</v>
+        <v>0.723</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6070,10 +6070,10 @@
         <v>0.008500000000000001</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1212400</v>
+        <v>1267700</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="H125" t="n">
         <v>53.65</v>
@@ -6100,39 +6100,39 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>-0.0301</v>
+      </c>
+      <c r="F126" s="4" t="n">
+        <v>1258700</v>
+      </c>
+      <c r="G126" s="5" t="n">
         <v>0.38</v>
       </c>
-      <c r="E126" s="3" t="n">
-        <v>-0.0256</v>
-      </c>
-      <c r="F126" s="4" t="n">
-        <v>1172000</v>
-      </c>
-      <c r="G126" s="5" t="n">
-        <v>0.47</v>
-      </c>
       <c r="H126" t="n">
-        <v>46.47</v>
-      </c>
-      <c r="I126" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.82</v>
+      </c>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.387</v>
+        <v>0.717</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.39</v>
+        <v>0.743</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6145,39 +6145,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>3.78</v>
+        <v>0.275</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0179</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1169900</v>
+        <v>1239800</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>0.39</v>
+        <v>1.33</v>
       </c>
       <c r="H127" t="n">
-        <v>48.34</v>
-      </c>
-      <c r="I127" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.1</v>
+      </c>
+      <c r="I127" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>3.844</v>
+        <v>0.276</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>3.699</v>
+        <v>0.268</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6190,28 +6190,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E128" s="10" t="n">
-        <v>0</v>
+        <v>7.1</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>-0.0274</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1131600</v>
+        <v>1239700</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H128" t="n">
-        <v>58.81</v>
+        <v>46.87</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>1.06</v>
+        <v>7.327</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>0.923</v>
+        <v>6.904</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6235,39 +6235,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0</v>
+        <v>0.985</v>
+      </c>
+      <c r="E129" s="3" t="n">
+        <v>-0.0343</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1126700</v>
+        <v>1235100</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>1.08</v>
+        <v>0.31</v>
       </c>
       <c r="H129" t="n">
-        <v>42.78</v>
-      </c>
-      <c r="I129" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.23</v>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.229</v>
+        <v>1.039</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.238</v>
+        <v>0.949</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6280,28 +6280,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>0.985</v>
+        <v>10.42</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>-0.0343</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1084100</v>
+        <v>1202400</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
       <c r="H130" t="n">
-        <v>44.23</v>
+        <v>53.31</v>
       </c>
       <c r="I130" s="6" t="inlineStr">
         <is>
@@ -6309,10 +6309,10 @@
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>1.039</v>
+        <v>10.415</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0.949</v>
+        <v>9.781000000000001</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6325,39 +6325,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E131" s="10" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1031900</v>
+        <v>1200800</v>
       </c>
       <c r="G131" s="5" t="n">
-        <v>0.15</v>
+        <v>0.29</v>
       </c>
       <c r="H131" t="n">
-        <v>27.88</v>
-      </c>
-      <c r="I131" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.75</v>
+      </c>
+      <c r="I131" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.719</v>
+        <v>1.261</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>0.786</v>
+        <v>1.276</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6370,28 +6370,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>1.25</v>
+        <v>0.5</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>-0.0157</v>
+        <v>-0.0196</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1003500</v>
+        <v>1189200</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.46</v>
+        <v>0.28</v>
       </c>
       <c r="H132" t="n">
-        <v>42.62</v>
+        <v>29.84</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>1.317</v>
+        <v>0.574</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>1.288</v>
+        <v>0.597</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6415,39 +6415,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E133" s="10" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E133" s="3" t="n">
+        <v>-0.0256</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>986200</v>
+        <v>1174200</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="H133" t="n">
-        <v>45.14</v>
-      </c>
-      <c r="I133" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.47</v>
+      </c>
+      <c r="I133" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>2.603</v>
+        <v>0.387</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>2.61</v>
+        <v>0.39</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6460,39 +6460,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E134" s="3" t="n">
-        <v>-0.0194</v>
+        <v>0.225</v>
+      </c>
+      <c r="E134" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>972500</v>
+        <v>1129600</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.43</v>
+        <v>1.08</v>
       </c>
       <c r="H134" t="n">
-        <v>62.26</v>
-      </c>
-      <c r="I134" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.78</v>
+      </c>
+      <c r="I134" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.733</v>
+        <v>0.229</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.652</v>
+        <v>0.238</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6505,39 +6505,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="E135" s="3" t="n">
-        <v>-0.0233</v>
+        <v>4.47</v>
+      </c>
+      <c r="E135" s="8" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>964700</v>
+        <v>1129300</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="H135" t="n">
-        <v>47.51</v>
-      </c>
-      <c r="I135" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.49</v>
+      </c>
+      <c r="I135" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>7.33</v>
+        <v>4.367</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>6.905</v>
+        <v>4.431</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6550,28 +6550,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>10.44</v>
+        <v>2.4</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>-0.0038</v>
+        <v>-0.0083</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>950600</v>
+        <v>1125900</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="H136" t="n">
-        <v>53.73</v>
+        <v>35.11</v>
       </c>
       <c r="I136" s="6" t="inlineStr">
         <is>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>10.417</v>
+        <v>2.529</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>9.781000000000001</v>
+        <v>2.7</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6595,28 +6595,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>4.48</v>
+        <v>0.245</v>
       </c>
       <c r="E137" s="8" t="n">
-        <v>0.0182</v>
+        <v>0.0208</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>944000</v>
+        <v>1117700</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>0.18</v>
+        <v>1.14</v>
       </c>
       <c r="H137" t="n">
-        <v>53.85</v>
+        <v>64.06</v>
       </c>
       <c r="I137" s="9" t="inlineStr">
         <is>
@@ -6624,10 +6624,10 @@
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>4.368</v>
+        <v>0.224</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>4.431</v>
+        <v>0.211</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6640,28 +6640,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>0.915</v>
+        <v>2.55</v>
       </c>
       <c r="E138" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>936900</v>
+        <v>1112700</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.53</v>
+        <v>0.19</v>
       </c>
       <c r="H138" t="n">
-        <v>51.22</v>
+        <v>45.14</v>
       </c>
       <c r="I138" s="6" t="inlineStr">
         <is>
@@ -6669,10 +6669,10 @@
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.915</v>
+        <v>2.603</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0.879</v>
+        <v>2.61</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6685,39 +6685,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="E139" s="3" t="n">
-        <v>-0.0227</v>
+        <v>2.33</v>
+      </c>
+      <c r="E139" s="8" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>936200</v>
+        <v>1103300</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.39</v>
+        <v>0.31</v>
       </c>
       <c r="H139" t="n">
-        <v>54.96</v>
-      </c>
-      <c r="I139" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.34</v>
+      </c>
+      <c r="I139" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>1.264</v>
+        <v>2.233</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>1.176</v>
+        <v>2.175</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6730,39 +6730,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E140" s="3" t="n">
-        <v>-0.0071</v>
+        <v>0.675</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>934700</v>
+        <v>1072900</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.26</v>
+        <v>0.15</v>
       </c>
       <c r="H140" t="n">
-        <v>58.65</v>
-      </c>
-      <c r="I140" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.88</v>
+      </c>
+      <c r="I140" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>2.693</v>
+        <v>0.719</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>2.283</v>
+        <v>0.786</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6775,39 +6775,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="E141" s="8" t="n">
-        <v>0.0043</v>
+        <v>6.75</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>912100</v>
+        <v>1029100</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H141" t="n">
-        <v>59.64</v>
-      </c>
-      <c r="I141" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.34</v>
+      </c>
+      <c r="I141" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>2.232</v>
+        <v>6.755</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>2.175</v>
+        <v>6.824</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6820,39 +6820,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>-0.0156</v>
+        <v>-0.0157</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>879900</v>
+        <v>1028500</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.21</v>
+        <v>0.47</v>
       </c>
       <c r="H142" t="n">
-        <v>49.37</v>
-      </c>
-      <c r="I142" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.62</v>
+      </c>
+      <c r="I142" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>1.26</v>
+        <v>1.317</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1.276</v>
+        <v>1.288</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6865,39 +6865,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1.29</v>
+        <v>2.8</v>
       </c>
       <c r="E143" s="3" t="n">
-        <v>-0.0077</v>
+        <v>-0.0071</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>877000</v>
+        <v>1027900</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.43</v>
+        <v>0.29</v>
       </c>
       <c r="H143" t="n">
-        <v>24.64</v>
-      </c>
-      <c r="I143" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.65</v>
+      </c>
+      <c r="I143" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>1.392</v>
+        <v>2.693</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>1.46</v>
+        <v>2.283</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6910,28 +6910,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>3.11</v>
+        <v>5.23</v>
       </c>
       <c r="E144" s="3" t="n">
-        <v>-0.0127</v>
+        <v>-0.0113</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>845400</v>
+        <v>977800</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.55</v>
+        <v>0.77</v>
       </c>
       <c r="H144" t="n">
-        <v>49.79</v>
+        <v>31.94</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>3.167</v>
+        <v>5.464</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>2.894</v>
+        <v>5.8</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6955,39 +6955,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0.63</v>
+        <v>0.76</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0194</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>842400</v>
+        <v>975800</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="H145" t="n">
-        <v>47.44</v>
-      </c>
-      <c r="I145" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>62.26</v>
+      </c>
+      <c r="I145" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.637</v>
+        <v>0.733</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0.624</v>
+        <v>0.652</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -7000,28 +7000,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>2.81</v>
+        <v>1.28</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>-0.0175</v>
+        <v>-0.0303</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>834400</v>
+        <v>958900</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.65</v>
+        <v>0.39</v>
       </c>
       <c r="H146" t="n">
-        <v>29.07</v>
+        <v>53.95</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>2.916</v>
+        <v>1.263</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>3.056</v>
+        <v>1.176</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7045,28 +7045,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>2.99</v>
+        <v>0.625</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>818200</v>
+        <v>946300</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H147" t="n">
-        <v>50.24</v>
+        <v>46.98</v>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>3.024</v>
+        <v>0.637</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>2.858</v>
+        <v>0.616</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7105,10 +7105,10 @@
         <v>0.0245</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>817900</v>
+        <v>940300</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="H148" t="n">
         <v>32.77</v>
@@ -7135,28 +7135,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="E149" s="3" t="n">
-        <v>-0.0113</v>
+        <v>0.915</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>814000</v>
+        <v>936900</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.64</v>
+        <v>0.53</v>
       </c>
       <c r="H149" t="n">
-        <v>31.94</v>
+        <v>51.22</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>5.464</v>
+        <v>0.915</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>5.8</v>
+        <v>0.879</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7180,39 +7180,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E150" s="3" t="n">
-        <v>-0.0076</v>
+        <v>5.37</v>
+      </c>
+      <c r="E150" s="8" t="n">
+        <v>0.017</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>790500</v>
+        <v>923100</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="H150" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="I150" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.97</v>
+      </c>
+      <c r="I150" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.585</v>
+        <v>5.556</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>0.532</v>
+        <v>5.793</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7225,28 +7225,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="E151" s="3" t="n">
-        <v>-0.0165</v>
+        <v>-0.0175</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>770700</v>
+        <v>919800</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.17</v>
+        <v>0.72</v>
       </c>
       <c r="H151" t="n">
-        <v>33.98</v>
+        <v>29.07</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>2.527</v>
+        <v>2.916</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>2.699</v>
+        <v>3.056</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7270,28 +7270,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>0.9</v>
+        <v>3.11</v>
       </c>
       <c r="E152" s="3" t="n">
-        <v>-0.011</v>
+        <v>-0.0127</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>763600</v>
+        <v>908100</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.44</v>
+        <v>0.59</v>
       </c>
       <c r="H152" t="n">
-        <v>31.3</v>
+        <v>49.79</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.167</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>0.999</v>
+        <v>2.894</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7315,28 +7315,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1.68</v>
+        <v>1.27</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>-0.0175</v>
+        <v>-0.0231</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>752800</v>
+        <v>899000</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.13</v>
+        <v>0.44</v>
       </c>
       <c r="H153" t="n">
-        <v>32.26</v>
+        <v>22.86</v>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>1.764</v>
+        <v>1.39</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>1.881</v>
+        <v>1.459</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7360,28 +7360,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="E154" s="8" t="n">
-        <v>0.0114</v>
+        <v>1.68</v>
+      </c>
+      <c r="E154" s="3" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>730400</v>
+        <v>893900</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.38</v>
+        <v>0.15</v>
       </c>
       <c r="H154" t="n">
-        <v>33.84</v>
+        <v>32.26</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>5.554</v>
+        <v>1.764</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>5.793</v>
+        <v>1.881</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7405,39 +7405,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>0.65</v>
+        <v>4.01</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>-0.0152</v>
+        <v>-0.0291</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>725900</v>
+        <v>873500</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.26</v>
+        <v>0.34</v>
       </c>
       <c r="H155" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="I155" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.18</v>
+      </c>
+      <c r="I155" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.646</v>
+        <v>4.259</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>4.314</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7450,39 +7450,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.625</v>
+        <v>0.65</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0076</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>710300</v>
+        <v>853600</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.19</v>
+        <v>0.78</v>
       </c>
       <c r="H156" t="n">
-        <v>46.98</v>
-      </c>
-      <c r="I156" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.56</v>
+      </c>
+      <c r="I156" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.637</v>
+        <v>0.585</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.616</v>
+        <v>0.532</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7495,39 +7495,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>-0.0169</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>700300</v>
+        <v>842400</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H157" t="n">
-        <v>36.97</v>
-      </c>
-      <c r="I157" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.44</v>
+      </c>
+      <c r="I157" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.602</v>
+        <v>0.637</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>0.63</v>
+        <v>0.624</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7540,28 +7540,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>PARADIGM</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>0.8</v>
+        <v>4.47</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>-0.0062</v>
+        <v>-0.0067</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>657100</v>
+        <v>836300</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>1.71</v>
+        <v>0.09</v>
       </c>
       <c r="H158" t="n">
-        <v>25.89</v>
+        <v>37.35</v>
       </c>
       <c r="I158" s="6" t="inlineStr">
         <is>
@@ -7569,10 +7569,10 @@
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.819</v>
+        <v>4.603</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>0.848</v>
+        <v>4.64</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7585,28 +7585,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1.12</v>
+        <v>2.99</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>638100</v>
+        <v>820600</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="H159" t="n">
-        <v>54.69</v>
+        <v>50.24</v>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>1.112</v>
+        <v>3.024</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0.896</v>
+        <v>2.858</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7630,28 +7630,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>4.04</v>
+        <v>0.74</v>
       </c>
       <c r="E160" s="3" t="n">
-        <v>-0.0218</v>
+        <v>-0.0263</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>621500</v>
+        <v>805300</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.24</v>
+        <v>0.35</v>
       </c>
       <c r="H160" t="n">
-        <v>41.01</v>
+        <v>43.46</v>
       </c>
       <c r="I160" s="6" t="inlineStr">
         <is>
@@ -7659,10 +7659,10 @@
         </is>
       </c>
       <c r="J160" s="2" t="n">
-        <v>4.262</v>
+        <v>0.772</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>4.315</v>
+        <v>0.77</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="7" t="inlineStr"/>
@@ -7675,28 +7675,28 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1.02</v>
+        <v>0.9</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>-0.0192</v>
+        <v>-0.011</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>609200</v>
+        <v>789300</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="H161" t="n">
-        <v>32.99</v>
+        <v>31.3</v>
       </c>
       <c r="I161" s="6" t="inlineStr">
         <is>
@@ -7704,10 +7704,10 @@
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>1.13</v>
+        <v>0.999</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7720,28 +7720,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0</v>
+        <v>1.02</v>
+      </c>
+      <c r="E162" s="3" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>595000</v>
+        <v>775200</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H162" t="n">
-        <v>45.03</v>
+        <v>32.99</v>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>0.631</v>
+        <v>1.08</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>0.631</v>
+        <v>1.13</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7765,28 +7765,28 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>0.745</v>
+        <v>1.95</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>-0.0197</v>
+        <v>-0.067</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>562500</v>
+        <v>772700</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.24</v>
+        <v>0.3</v>
       </c>
       <c r="H163" t="n">
-        <v>44.35</v>
+        <v>42.69</v>
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.772</v>
+        <v>2.097</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>0.77</v>
+        <v>1.993</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="7" t="inlineStr"/>
@@ -7810,28 +7810,28 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E164" s="10" t="n">
-        <v>0</v>
+        <v>0.65</v>
+      </c>
+      <c r="E164" s="3" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>541100</v>
+        <v>771200</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="H164" t="n">
-        <v>54.7</v>
+        <v>54.56</v>
       </c>
       <c r="I164" s="9" t="inlineStr">
         <is>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>2.112</v>
+        <v>0.646</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>2.066</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7855,39 +7855,39 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>SUPERLN</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E165" s="8" t="n">
-        <v>0.0167</v>
+        <v>2.39</v>
+      </c>
+      <c r="E165" s="3" t="n">
+        <v>-0.0285</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>540700</v>
+        <v>730000</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>1.47</v>
+        <v>0.42</v>
       </c>
       <c r="H165" t="n">
-        <v>64.01000000000001</v>
-      </c>
-      <c r="I165" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.5</v>
+      </c>
+      <c r="I165" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.862</v>
+        <v>2.505</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>0.841</v>
+        <v>2.256</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7900,39 +7900,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>0.695</v>
+        <v>0.58</v>
       </c>
       <c r="E166" s="3" t="n">
-        <v>-0.0071</v>
+        <v>-0.0169</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>539300</v>
+        <v>724800</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.91</v>
+        <v>0.33</v>
       </c>
       <c r="H166" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="I166" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.97</v>
+      </c>
+      <c r="I166" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.681</v>
+        <v>0.602</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>0.658</v>
+        <v>0.63</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7945,39 +7945,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>2.38</v>
+        <v>7.46</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>-0.0325</v>
+        <v>-0.0027</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>526000</v>
+        <v>694400</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="H167" t="n">
-        <v>46.03</v>
-      </c>
-      <c r="I167" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.29</v>
+      </c>
+      <c r="I167" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>2.504</v>
+        <v>7.565</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>2.256</v>
+        <v>7.754</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7990,28 +7990,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="E168" s="3" t="n">
-        <v>-0.0016</v>
+        <v>3.21</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>523900</v>
+        <v>670500</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="H168" t="n">
-        <v>36.16</v>
+        <v>32.06</v>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>6.371</v>
+        <v>3.351</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>6.731</v>
+        <v>3.593</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8035,28 +8035,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>PARADIGM</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="E169" s="3" t="n">
-        <v>-0.0031</v>
+        <v>-0.0062</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>518000</v>
+        <v>664100</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>0.09</v>
+        <v>1.73</v>
       </c>
       <c r="H169" t="n">
-        <v>31.51</v>
+        <v>25.89</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>3.35</v>
+        <v>0.819</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>3.593</v>
+        <v>0.848</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8080,28 +8080,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>2</v>
+        <v>0.79</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>-0.0431</v>
+        <v>-0.0063</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>517100</v>
+        <v>648600</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="H170" t="n">
-        <v>45.15</v>
+        <v>15.78</v>
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>2.102</v>
+        <v>0.924</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>1.994</v>
+        <v>1.071</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8125,28 +8125,28 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>6.75</v>
+        <v>1.13</v>
       </c>
       <c r="E171" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>506600</v>
+        <v>643100</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
       <c r="H171" t="n">
-        <v>49.34</v>
+        <v>55.71</v>
       </c>
       <c r="I171" s="6" t="inlineStr">
         <is>
@@ -8154,10 +8154,10 @@
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>6.755</v>
+        <v>1.113</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>6.824</v>
+        <v>0.896</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8170,28 +8170,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>MENTIGA</t>
+          <t>SUPERLN</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>1.02</v>
+        <v>0.92</v>
       </c>
       <c r="E172" s="8" t="n">
-        <v>0.0462</v>
+        <v>0.0222</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>505500</v>
+        <v>634200</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>3.71</v>
+        <v>1.73</v>
       </c>
       <c r="H172" t="n">
-        <v>84.15000000000001</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="I172" s="9" t="inlineStr">
         <is>
@@ -8199,10 +8199,10 @@
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.722</v>
+        <v>0.863</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>0.661</v>
+        <v>0.841</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8215,28 +8215,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>5.41</v>
-      </c>
-      <c r="E173" s="3" t="n">
-        <v>-0.0164</v>
+        <v>0.63</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>500600</v>
+        <v>630000</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H173" t="n">
-        <v>48.4</v>
+        <v>45.03</v>
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
@@ -8244,16 +8244,556 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>5.503</v>
+        <v>0.631</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>5.388</v>
+        <v>0.631</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
     </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="E174" s="3" t="n">
+        <v>-0.0218</v>
+      </c>
+      <c r="F174" s="4" t="n">
+        <v>626900</v>
+      </c>
+      <c r="G174" s="5" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H174" t="n">
+        <v>47.67</v>
+      </c>
+      <c r="I174" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K174" s="2" t="n">
+        <v>5.387</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>7195</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>BNASTRA</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E175" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F175" s="4" t="n">
+        <v>612000</v>
+      </c>
+      <c r="G175" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H175" t="n">
+        <v>86.48</v>
+      </c>
+      <c r="I175" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="n">
+        <v>2.621</v>
+      </c>
+      <c r="K175" s="2" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5280</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>KIPREIT</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="n">
+        <v>0.865</v>
+      </c>
+      <c r="E176" s="3" t="n">
+        <v>-0.005699999999999999</v>
+      </c>
+      <c r="F176" s="4" t="n">
+        <v>609400</v>
+      </c>
+      <c r="G176" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H176" t="n">
+        <v>56.24</v>
+      </c>
+      <c r="I176" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="K176" s="2" t="n">
+        <v>0.854</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="7" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="E177" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F177" s="4" t="n">
+        <v>608600</v>
+      </c>
+      <c r="G177" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H177" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="I177" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="n">
+        <v>2.112</v>
+      </c>
+      <c r="K177" s="2" t="n">
+        <v>2.066</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="7" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" s="4" t="n">
+        <v>604000</v>
+      </c>
+      <c r="G178" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H178" t="n">
+        <v>36.53</v>
+      </c>
+      <c r="I178" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="n">
+        <v>6.372</v>
+      </c>
+      <c r="K178" s="2" t="n">
+        <v>6.732</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>0326</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>SORENTO</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E179" s="3" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="F179" s="4" t="n">
+        <v>539300</v>
+      </c>
+      <c r="G179" s="5" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H179" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="I179" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="n">
+        <v>0.681</v>
+      </c>
+      <c r="K179" s="2" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="7" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>4758</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>ANCOMNY</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="n">
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F180" s="4" t="n">
+        <v>536300</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H180" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="I180" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="n">
+        <v>0.841</v>
+      </c>
+      <c r="K180" s="2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="7" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>5223</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>MENTIGA</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="E181" s="8" t="n">
+        <v>0.0564</v>
+      </c>
+      <c r="F181" s="4" t="n">
+        <v>535600</v>
+      </c>
+      <c r="G181" s="5" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="H181" t="n">
+        <v>84.45</v>
+      </c>
+      <c r="I181" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="K181" s="2" t="n">
+        <v>0.661</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="7" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="E182" s="3" t="n">
+        <v>-0.0064</v>
+      </c>
+      <c r="F182" s="4" t="n">
+        <v>531600</v>
+      </c>
+      <c r="G182" s="5" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H182" t="n">
+        <v>41.02</v>
+      </c>
+      <c r="I182" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="n">
+        <v>3.146</v>
+      </c>
+      <c r="K182" s="2" t="n">
+        <v>3.314</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="7" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="E183" s="8" t="n">
+        <v>0.0048</v>
+      </c>
+      <c r="F183" s="4" t="n">
+        <v>525500</v>
+      </c>
+      <c r="G183" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H183" t="n">
+        <v>33.81</v>
+      </c>
+      <c r="I183" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="n">
+        <v>4.387</v>
+      </c>
+      <c r="K183" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="7" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="E184" s="3" t="n">
+        <v>-0.0275</v>
+      </c>
+      <c r="F184" s="4" t="n">
+        <v>517800</v>
+      </c>
+      <c r="G184" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H184" t="n">
+        <v>56.11</v>
+      </c>
+      <c r="I184" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J184" s="2" t="n">
+        <v>2.789</v>
+      </c>
+      <c r="K184" s="2" t="n">
+        <v>2.239</v>
+      </c>
+      <c r="L184" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>5071</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>COASTAL</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E185" s="8" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="F185" s="4" t="n">
+        <v>500500</v>
+      </c>
+      <c r="G185" s="5" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="H185" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="I185" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J185" s="2" t="n">
+        <v>1.583</v>
+      </c>
+      <c r="K185" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L185" t="inlineStr"/>
+      <c r="M185" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M173"/>
+  <autoFilter ref="A1:M185"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
+++ b/docs/downloads/2026-10-20/bursa-report-2026-10-20.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-20" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-20'!$A$1:$M$187</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M185"/>
+  <dimension ref="A1:M187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -552,19 +552,19 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.335</v>
+        <v>0.33</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>-0.0147</v>
+        <v>-0.0294</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>49989000</v>
+        <v>50114700</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>0.62</v>
       </c>
       <c r="H2" t="n">
-        <v>66.04000000000001</v>
+        <v>63.6</v>
       </c>
       <c r="I2" s="6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J2" s="2" t="n">
-        <v>0.308</v>
+        <v>0.307</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>0.259</v>
@@ -603,7 +603,7 @@
         <v>0.0449</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>36601200</v>
+        <v>36611200</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>1.05</v>
@@ -642,19 +642,19 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.905</v>
+        <v>0.91</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>0.0169</v>
+        <v>0.0225</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>35432500</v>
+        <v>36604300</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="H4" t="n">
-        <v>65.92</v>
+        <v>66.47</v>
       </c>
       <c r="I4" s="9" t="inlineStr">
         <is>
@@ -693,10 +693,10 @@
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>32309600</v>
+        <v>33838500</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="H5" t="n">
         <v>22.63</v>
@@ -738,10 +738,10 @@
         <v>-0.0559</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>22575200</v>
+        <v>22673500</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>4.51</v>
+        <v>4.53</v>
       </c>
       <c r="H6" t="n">
         <v>27.02</v>
@@ -783,10 +783,10 @@
         <v>0.1111</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>18537800</v>
+        <v>18781100</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="H7" t="n">
         <v>28.68</v>
@@ -828,10 +828,10 @@
         <v>0.0217</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>18016900</v>
+        <v>18367100</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="H8" t="n">
         <v>80.01000000000001</v>
@@ -918,7 +918,7 @@
         <v>-0.1667</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>17133200</v>
+        <v>17186100</v>
       </c>
       <c r="G10" s="5" t="n">
         <v>0.44</v>
@@ -950,19 +950,19 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.098</v>
+        <v>-0.1078</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>16963500</v>
+        <v>17097500</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="H11" t="n">
-        <v>41.67</v>
+        <v>40.96</v>
       </c>
       <c r="I11" s="6" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>0.514</v>
+        <v>0.513</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0.463</v>
@@ -1040,19 +1040,19 @@
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>0.865</v>
+        <v>0.86</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0115</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>13104000</v>
+        <v>13296400</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>0.66</v>
       </c>
       <c r="H13" t="n">
-        <v>46.09</v>
+        <v>41.72</v>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>-0.0061</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>12737100</v>
+        <v>12737400</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.8</v>
@@ -1175,19 +1175,19 @@
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0</v>
+        <v>0.385</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.0128</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>11303800</v>
+        <v>11308800</v>
       </c>
       <c r="G16" s="5" t="n">
         <v>1.13</v>
       </c>
       <c r="H16" t="n">
-        <v>33.85</v>
+        <v>28.49</v>
       </c>
       <c r="I16" s="6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>0.0132</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10810900</v>
+        <v>10861700</v>
       </c>
       <c r="G17" s="5" t="n">
         <v>0.18</v>
@@ -1264,7 +1264,7 @@
         <v>0.06849999999999999</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10087200</v>
+        <v>10107800</v>
       </c>
       <c r="G18" s="5" t="n">
         <v>1.92</v>
@@ -1352,7 +1352,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>9941900</v>
+        <v>9942900</v>
       </c>
       <c r="G20" s="5" t="n">
         <v>0.42</v>
@@ -1390,10 +1390,10 @@
         <v>-0.04650000000000001</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>9713500</v>
+        <v>9828000</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="H21" t="n">
         <v>28.47</v>
@@ -1420,28 +1420,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E22" s="3" t="n">
-        <v>-0.0146</v>
+        <v>0.775</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>9561000</v>
+        <v>9785400</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.33</v>
+        <v>0.64</v>
       </c>
       <c r="H22" t="n">
-        <v>58.58</v>
+        <v>49.91</v>
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>1.941</v>
+        <v>0.775</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>1.754</v>
+        <v>0.776</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="7" t="inlineStr"/>
@@ -1465,28 +1465,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0</v>
+        <v>2.02</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.0146</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>9403400</v>
+        <v>9725500</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.61</v>
+        <v>0.34</v>
       </c>
       <c r="H23" t="n">
-        <v>49.91</v>
+        <v>58.58</v>
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.775</v>
+        <v>1.941</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>0.776</v>
+        <v>1.754</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="7" t="inlineStr"/>
@@ -1525,7 +1525,7 @@
         <v>-0.0238</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>9395800</v>
+        <v>9572600</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>0.42</v>
@@ -1555,28 +1555,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>0.975</v>
-      </c>
-      <c r="E25" s="3" t="n">
-        <v>-0.0201</v>
+        <v>0.435</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>8830700</v>
+        <v>9048900</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>1.08</v>
+        <v>0.25</v>
       </c>
       <c r="H25" t="n">
-        <v>41.71</v>
+        <v>36.45</v>
       </c>
       <c r="I25" s="6" t="inlineStr">
         <is>
@@ -1584,10 +1584,10 @@
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.042</v>
+        <v>0.473</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0.964</v>
+        <v>0.481</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="7" t="inlineStr"/>
@@ -1600,28 +1600,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E26" s="8" t="n">
-        <v>0.0247</v>
+        <v>0.975</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>-0.0201</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>8579900</v>
+        <v>8844100</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.7</v>
+        <v>1.09</v>
       </c>
       <c r="H26" t="n">
-        <v>57.67</v>
+        <v>41.71</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
@@ -1629,10 +1629,10 @@
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.394</v>
+        <v>1.042</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>0.379</v>
+        <v>0.964</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="7" t="inlineStr"/>
@@ -1645,28 +1645,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0</v>
+        <v>0.415</v>
+      </c>
+      <c r="E27" s="8" t="n">
+        <v>0.0247</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>8518400</v>
+        <v>8620900</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.23</v>
+        <v>0.71</v>
       </c>
       <c r="H27" t="n">
-        <v>36.45</v>
+        <v>57.67</v>
       </c>
       <c r="I27" s="6" t="inlineStr">
         <is>
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.473</v>
+        <v>0.394</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0.481</v>
+        <v>0.379</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="7" t="inlineStr"/>
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>0.435</v>
+        <v>0.44</v>
       </c>
       <c r="E28" s="8" t="n">
-        <v>0.0116</v>
+        <v>0.0233</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>8396500</v>
+        <v>8484500</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>0.41</v>
       </c>
       <c r="H28" t="n">
-        <v>55.91</v>
+        <v>57.01</v>
       </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
@@ -1735,39 +1735,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0</v>
+        <v>0.545</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.0091</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>8288800</v>
+        <v>8310500</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.76</v>
+        <v>0.4</v>
       </c>
       <c r="H29" t="n">
-        <v>59.52</v>
-      </c>
-      <c r="I29" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.15</v>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>0.619</v>
+        <v>0.571</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0.616</v>
+        <v>0.543</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="7" t="inlineStr"/>
@@ -1780,39 +1780,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E30" s="3" t="n">
-        <v>-0.0154</v>
+        <v>0.63</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>8103600</v>
+        <v>8288800</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.45</v>
+        <v>0.76</v>
       </c>
       <c r="H30" t="n">
-        <v>45.65</v>
-      </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.52</v>
+      </c>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>2.635</v>
+        <v>0.619</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>2.556</v>
+        <v>0.616</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="7" t="inlineStr"/>
@@ -1825,28 +1825,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>0.54</v>
+        <v>2.55</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>-0.0182</v>
+        <v>-0.0154</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>7889500</v>
+        <v>8103700</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.38</v>
+        <v>0.45</v>
       </c>
       <c r="H31" t="n">
-        <v>45.28</v>
+        <v>45.65</v>
       </c>
       <c r="I31" s="6" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.57</v>
+        <v>2.635</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>0.543</v>
+        <v>2.556</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="7" t="inlineStr"/>
@@ -1885,10 +1885,10 @@
         <v>0.0286</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>7775400</v>
+        <v>8027600</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H32" t="n">
         <v>44.12</v>
@@ -1975,7 +1975,7 @@
         <v>-0.033</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>7332500</v>
+        <v>7361600</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>0.32</v>
@@ -2020,7 +2020,7 @@
         <v>-0.0345</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>7320700</v>
+        <v>7345800</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>1.16</v>
@@ -2065,7 +2065,7 @@
         <v>0.0588</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>6986200</v>
+        <v>7021200</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>1.35</v>
@@ -2104,19 +2104,19 @@
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E37" s="8" t="n">
-        <v>0.0256</v>
+        <v>0.195</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>6391000</v>
+        <v>6400000</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>16.77</v>
+        <v>16.8</v>
       </c>
       <c r="H37" t="n">
-        <v>82.42</v>
+        <v>80.03</v>
       </c>
       <c r="I37" s="9" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.177</v>
+        <v>0.176</v>
       </c>
       <c r="K37" s="2" t="n">
         <v>0.171</v>
@@ -2149,19 +2149,19 @@
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>0.66</v>
+        <v>0.65</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>-0.0897</v>
+        <v>-0.1034</v>
       </c>
       <c r="F38" s="4" t="n">
-        <v>6133700</v>
+        <v>6201700</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="H38" t="n">
-        <v>37.73</v>
+        <v>36.67</v>
       </c>
       <c r="I38" s="6" t="inlineStr">
         <is>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>0.751</v>
+        <v>0.75</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>0.6860000000000001</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="7" t="inlineStr"/>
@@ -2200,10 +2200,10 @@
         <v>0.0303</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>6093800</v>
+        <v>6105400</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>2.03</v>
+        <v>2.04</v>
       </c>
       <c r="H39" t="n">
         <v>64.43000000000001</v>
@@ -2230,39 +2230,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7225</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>0.175</v>
+        <v>1.16</v>
       </c>
       <c r="E40" s="3" t="n">
-        <v>-0.0541</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>5810900</v>
+        <v>5929600</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>1.42</v>
+        <v>0.75</v>
       </c>
       <c r="H40" t="n">
-        <v>24.82</v>
-      </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.26</v>
+      </c>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.197</v>
+        <v>1.226</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>0.207</v>
+        <v>1.316</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="7" t="inlineStr"/>
@@ -2275,39 +2275,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7225</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E41" s="8" t="n">
-        <v>0.0156</v>
+        <v>0.175</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>-0.0541</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>5614400</v>
+        <v>5860900</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.89</v>
+        <v>1.43</v>
       </c>
       <c r="H41" t="n">
-        <v>64.47</v>
-      </c>
-      <c r="I41" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.82</v>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.208</v>
+        <v>0.197</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>1.193</v>
+        <v>0.207</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="7" t="inlineStr"/>
@@ -2320,28 +2320,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E42" s="3" t="n">
-        <v>-0.0171</v>
+        <v>1.29</v>
+      </c>
+      <c r="E42" s="8" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>5340200</v>
+        <v>5642000</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="H42" t="n">
-        <v>34.18</v>
+        <v>63.52</v>
       </c>
       <c r="I42" s="9" t="inlineStr">
         <is>
@@ -2349,10 +2349,10 @@
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>1.225</v>
+        <v>1.207</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>1.316</v>
+        <v>1.192</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="7" t="inlineStr"/>
@@ -2365,39 +2365,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="E43" s="8" t="n">
-        <v>0.0062</v>
+        <v>0.14</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>5289600</v>
+        <v>5421000</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.72</v>
+        <v>0.08</v>
       </c>
       <c r="H43" t="n">
-        <v>47.87</v>
-      </c>
-      <c r="I43" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>42.14</v>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.623</v>
+        <v>0.157</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>1.689</v>
+        <v>0.141</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="7" t="inlineStr"/>
@@ -2410,39 +2410,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0</v>
+        <v>1.62</v>
+      </c>
+      <c r="E44" s="8" t="n">
+        <v>0.0062</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>5193000</v>
+        <v>5411100</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="H44" t="n">
-        <v>50.51</v>
-      </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.87</v>
+      </c>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.353</v>
+        <v>1.623</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>0.328</v>
+        <v>1.689</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="7" t="inlineStr"/>
@@ -2455,39 +2455,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>0.375</v>
+        <v>0.35</v>
       </c>
       <c r="E45" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>4988200</v>
+        <v>5193000</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.68</v>
+        <v>0.67</v>
       </c>
       <c r="H45" t="n">
-        <v>55.92</v>
-      </c>
-      <c r="I45" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.51</v>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>0.371</v>
+        <v>0.353</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0.369</v>
+        <v>0.328</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="7" t="inlineStr"/>
@@ -2500,39 +2500,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0143</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>KEYASIC</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="E46" s="8" t="n">
-        <v>0.0064</v>
+        <v>0.04</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="4" t="n">
-        <v>4927400</v>
+        <v>5043400</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.24</v>
+        <v>0.78</v>
       </c>
       <c r="H46" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="I46" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.68</v>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>4.729</v>
+        <v>0.052</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4.84</v>
+        <v>0.06</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="7" t="inlineStr"/>
@@ -2545,28 +2545,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>7.3</v>
-      </c>
-      <c r="E47" s="8" t="n">
-        <v>0.0139</v>
+        <v>0.375</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="4" t="n">
-        <v>4847400</v>
+        <v>4988200</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.48</v>
+        <v>0.68</v>
       </c>
       <c r="H47" t="n">
-        <v>37.79</v>
+        <v>55.92</v>
       </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
@@ -2574,10 +2574,10 @@
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>7.439</v>
+        <v>0.371</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>7.92</v>
+        <v>0.369</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="7" t="inlineStr"/>
@@ -2590,39 +2590,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HENGYUAN</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>3.87</v>
+        <v>4.74</v>
       </c>
       <c r="E48" s="8" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.0064</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>4618000</v>
+        <v>4948900</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="H48" t="n">
-        <v>59.48</v>
-      </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.36</v>
+      </c>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>3.673</v>
+        <v>4.729</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>3.056</v>
+        <v>4.84</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="7" t="inlineStr"/>
@@ -2635,39 +2635,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>-0.0147</v>
+        <v>7.28</v>
+      </c>
+      <c r="E49" s="8" t="n">
+        <v>0.0111</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>4604300</v>
+        <v>4877400</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="H49" t="n">
-        <v>47.18</v>
-      </c>
-      <c r="I49" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.55</v>
+      </c>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>0.345</v>
+        <v>7.437</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0.335</v>
+        <v>7.92</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="7" t="inlineStr"/>
@@ -2680,28 +2680,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>HENGYUAN</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E50" s="3" t="n">
-        <v>-0.009899999999999999</v>
+        <v>3.9</v>
+      </c>
+      <c r="E50" s="8" t="n">
+        <v>0.0156</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>4601700</v>
+        <v>4723800</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.38</v>
+        <v>0.54</v>
       </c>
       <c r="H50" t="n">
-        <v>31.74</v>
+        <v>60.17</v>
       </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>2.134</v>
+        <v>3.676</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2.235</v>
+        <v>3.057</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="7" t="inlineStr"/>
@@ -2725,28 +2725,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>0.27</v>
+        <v>2</v>
       </c>
       <c r="E51" s="3" t="n">
-        <v>-0.0357</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>4584600</v>
+        <v>4656700</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.78</v>
+        <v>0.39</v>
       </c>
       <c r="H51" t="n">
-        <v>19.52</v>
+        <v>31.74</v>
       </c>
       <c r="I51" s="6" t="inlineStr">
         <is>
@@ -2754,10 +2754,10 @@
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.327</v>
+        <v>2.134</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.369</v>
+        <v>2.235</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="7" t="inlineStr"/>
@@ -2770,28 +2770,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>5.32</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0.0114</v>
+        <v>0.27</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>4460100</v>
+        <v>4639100</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.33</v>
+        <v>0.79</v>
       </c>
       <c r="H52" t="n">
-        <v>43.13</v>
+        <v>19.52</v>
       </c>
       <c r="I52" s="6" t="inlineStr">
         <is>
@@ -2799,10 +2799,10 @@
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>5.49</v>
+        <v>0.327</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>5.47</v>
+        <v>0.369</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="7" t="inlineStr"/>
@@ -2815,28 +2815,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E53" s="10" t="n">
-        <v>0</v>
+        <v>0.335</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>4331000</v>
+        <v>4627000</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.48</v>
       </c>
       <c r="H53" t="n">
-        <v>42.14</v>
+        <v>47.18</v>
       </c>
       <c r="I53" s="6" t="inlineStr">
         <is>
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>0.157</v>
+        <v>0.345</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0.141</v>
+        <v>0.335</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="7" t="inlineStr"/>
@@ -2860,28 +2860,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E54" s="3" t="n">
-        <v>-0.0357</v>
+        <v>5.32</v>
+      </c>
+      <c r="E54" s="8" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>4319500</v>
+        <v>4469000</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.47</v>
+        <v>0.33</v>
       </c>
       <c r="H54" t="n">
-        <v>32.82</v>
+        <v>43.13</v>
       </c>
       <c r="I54" s="6" t="inlineStr">
         <is>
@@ -2889,10 +2889,10 @@
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.636</v>
+        <v>5.49</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.619</v>
+        <v>5.47</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="7" t="inlineStr"/>
@@ -2905,39 +2905,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0</v>
+        <v>0.54</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>-0.0357</v>
       </c>
       <c r="F55" s="4" t="n">
-        <v>4074000</v>
+        <v>4364900</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.72</v>
+        <v>0.48</v>
       </c>
       <c r="H55" t="n">
-        <v>64.98999999999999</v>
-      </c>
-      <c r="I55" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.82</v>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.795</v>
+        <v>0.636</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.773</v>
+        <v>0.619</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="7" t="inlineStr"/>
@@ -2950,39 +2950,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>0.845</v>
-      </c>
-      <c r="E56" s="3" t="n">
-        <v>-0.0287</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F56" s="4" t="n">
-        <v>4006100</v>
+        <v>4074000</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="H56" t="n">
-        <v>40.43</v>
-      </c>
-      <c r="I56" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.98999999999999</v>
+      </c>
+      <c r="I56" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.92</v>
+        <v>0.795</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.85</v>
+        <v>0.773</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="7" t="inlineStr"/>
@@ -2995,28 +2995,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="E57" s="8" t="n">
-        <v>0.0014</v>
+        <v>0.845</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>-0.0287</v>
       </c>
       <c r="F57" s="4" t="n">
-        <v>3956100</v>
+        <v>4013900</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.24</v>
+        <v>0.54</v>
       </c>
       <c r="H57" t="n">
-        <v>33.47</v>
+        <v>40.43</v>
       </c>
       <c r="I57" s="6" t="inlineStr">
         <is>
@@ -3024,10 +3024,10 @@
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>7.472</v>
+        <v>0.92</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>7.672</v>
+        <v>0.85</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="7" t="inlineStr"/>
@@ -3040,28 +3040,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="E58" s="3" t="n">
-        <v>-0.0833</v>
+        <v>7.17</v>
+      </c>
+      <c r="E58" s="8" t="n">
+        <v>0.0028</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>3926300</v>
+        <v>3989200</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H58" t="n">
-        <v>30.91</v>
+        <v>34.03</v>
       </c>
       <c r="I58" s="6" t="inlineStr">
         <is>
@@ -3069,10 +3069,10 @@
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.14</v>
+        <v>7.473</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0.148</v>
+        <v>7.672</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="7" t="inlineStr"/>
@@ -3085,28 +3085,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>0.43</v>
+        <v>0.115</v>
       </c>
       <c r="E59" s="3" t="n">
-        <v>-0.0115</v>
+        <v>-0.0417</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>3752000</v>
+        <v>3932500</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.54</v>
+        <v>0.19</v>
       </c>
       <c r="H59" t="n">
-        <v>52.29</v>
+        <v>32.68</v>
       </c>
       <c r="I59" s="6" t="inlineStr">
         <is>
@@ -3114,10 +3114,10 @@
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.425</v>
+        <v>0.14</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0.417</v>
+        <v>0.149</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="7" t="inlineStr"/>
@@ -3130,28 +3130,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0186</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PTRANS</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0</v>
+        <v>0.765</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>3543300</v>
+        <v>3823400</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.62</v>
+        <v>3.09</v>
       </c>
       <c r="H60" t="n">
-        <v>34.49</v>
+        <v>61.83</v>
       </c>
       <c r="I60" s="6" t="inlineStr">
         <is>
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.176</v>
+        <v>0.749</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0.196</v>
+        <v>0.721</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="7" t="inlineStr"/>
@@ -3175,28 +3175,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>2.67</v>
+        <v>0.425</v>
       </c>
       <c r="E61" s="3" t="n">
-        <v>-0.0074</v>
+        <v>-0.023</v>
       </c>
       <c r="F61" s="4" t="n">
-        <v>3459800</v>
+        <v>3775000</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.28</v>
+        <v>0.54</v>
       </c>
       <c r="H61" t="n">
-        <v>43.48</v>
+        <v>51</v>
       </c>
       <c r="I61" s="6" t="inlineStr">
         <is>
@@ -3204,10 +3204,10 @@
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>2.754</v>
+        <v>0.425</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2.741</v>
+        <v>0.416</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="7" t="inlineStr"/>
@@ -3235,10 +3235,10 @@
         <v>0.0015</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>3457000</v>
+        <v>3728200</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.33</v>
+        <v>0.36</v>
       </c>
       <c r="H62" t="n">
         <v>29.21</v>
@@ -3265,28 +3265,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0078</t>
+          <t>0186</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GDEX</t>
+          <t>PTRANS</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>0.125</v>
+        <v>0.165</v>
       </c>
       <c r="E63" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>3371000</v>
+        <v>3543300</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>2.4</v>
+        <v>0.62</v>
       </c>
       <c r="H63" t="n">
-        <v>41.4</v>
+        <v>34.49</v>
       </c>
       <c r="I63" s="6" t="inlineStr">
         <is>
@@ -3294,10 +3294,10 @@
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>0.129</v>
+        <v>0.176</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0.13</v>
+        <v>0.196</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="7" t="inlineStr"/>
@@ -3310,28 +3310,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>0.275</v>
+        <v>1.43</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>-0.0179</v>
+        <v>-0.0069</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>3355300</v>
+        <v>3492900</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="H64" t="n">
-        <v>44.46</v>
+        <v>21.73</v>
       </c>
       <c r="I64" s="6" t="inlineStr">
         <is>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.289</v>
+        <v>1.668</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0.283</v>
+        <v>1.931</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="7" t="inlineStr"/>
@@ -3355,28 +3355,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1.43</v>
+        <v>2.67</v>
       </c>
       <c r="E65" s="3" t="n">
-        <v>-0.0069</v>
+        <v>-0.0074</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>3329200</v>
+        <v>3461700</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="H65" t="n">
-        <v>21.73</v>
+        <v>43.48</v>
       </c>
       <c r="I65" s="6" t="inlineStr">
         <is>
@@ -3384,10 +3384,10 @@
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.668</v>
+        <v>2.754</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>1.931</v>
+        <v>2.741</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="7" t="inlineStr"/>
@@ -3400,28 +3400,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0078</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>GDEX</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E66" s="3" t="n">
-        <v>-0.0215</v>
+        <v>0.125</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>3177900</v>
+        <v>3421000</v>
       </c>
       <c r="G66" s="5" t="n">
-        <v>0.78</v>
+        <v>2.43</v>
       </c>
       <c r="H66" t="n">
-        <v>22.95</v>
+        <v>41.4</v>
       </c>
       <c r="I66" s="6" t="inlineStr">
         <is>
@@ -3429,10 +3429,10 @@
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.964</v>
+        <v>0.129</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1.048</v>
+        <v>0.13</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="7" t="inlineStr"/>
@@ -3445,28 +3445,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>0.52</v>
+        <v>0.275</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>-0.0459</v>
+        <v>-0.0179</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>3144100</v>
+        <v>3364300</v>
       </c>
       <c r="G67" s="5" t="n">
-        <v>0.59</v>
+        <v>0.29</v>
       </c>
       <c r="H67" t="n">
-        <v>43.45</v>
+        <v>44.46</v>
       </c>
       <c r="I67" s="6" t="inlineStr">
         <is>
@@ -3474,10 +3474,10 @@
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.556</v>
+        <v>0.289</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0.518</v>
+        <v>0.283</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="7" t="inlineStr"/>
@@ -3490,28 +3490,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E68" s="10" t="n">
-        <v>0</v>
+        <v>0.915</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>-0.0161</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>3080100</v>
+        <v>3251200</v>
       </c>
       <c r="G68" s="5" t="n">
-        <v>0.93</v>
+        <v>0.8</v>
       </c>
       <c r="H68" t="n">
-        <v>46.01</v>
+        <v>23.81</v>
       </c>
       <c r="I68" s="6" t="inlineStr">
         <is>
@@ -3519,10 +3519,10 @@
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>2.043</v>
+        <v>0.965</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>2.069</v>
+        <v>1.049</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="7" t="inlineStr"/>
@@ -3535,28 +3535,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>5.6</v>
+        <v>0.52</v>
       </c>
       <c r="E69" s="3" t="n">
-        <v>-0.0014</v>
+        <v>-0.0459</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>2985000</v>
+        <v>3167800</v>
       </c>
       <c r="G69" s="5" t="n">
-        <v>0.39</v>
+        <v>0.59</v>
       </c>
       <c r="H69" t="n">
-        <v>28.93</v>
+        <v>43.45</v>
       </c>
       <c r="I69" s="6" t="inlineStr">
         <is>
@@ -3564,10 +3564,10 @@
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>5.875</v>
+        <v>0.556</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>6.164</v>
+        <v>0.518</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="7" t="inlineStr"/>
@@ -3580,39 +3580,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0</v>
+        <v>2.02</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>2979000</v>
+        <v>3090400</v>
       </c>
       <c r="G70" s="5" t="n">
-        <v>0.89</v>
+        <v>0.93</v>
       </c>
       <c r="H70" t="n">
-        <v>70.16</v>
-      </c>
-      <c r="I70" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.31</v>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.618</v>
+        <v>2.042</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0.606</v>
+        <v>2.069</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="7" t="inlineStr"/>
@@ -3625,28 +3625,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>0.765</v>
+        <v>5.6</v>
       </c>
       <c r="E71" s="3" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.0014</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>2955800</v>
+        <v>2996600</v>
       </c>
       <c r="G71" s="5" t="n">
-        <v>2.39</v>
+        <v>0.39</v>
       </c>
       <c r="H71" t="n">
-        <v>61.83</v>
+        <v>28.93</v>
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
@@ -3654,10 +3654,10 @@
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.749</v>
+        <v>5.875</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0.721</v>
+        <v>6.164</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="7" t="inlineStr"/>
@@ -3670,28 +3670,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>3.27</v>
-      </c>
-      <c r="E72" s="8" t="n">
-        <v>0.0391</v>
+        <v>0.625</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>2950500</v>
+        <v>2979000</v>
       </c>
       <c r="G72" s="5" t="n">
-        <v>0.93</v>
+        <v>0.89</v>
       </c>
       <c r="H72" t="n">
-        <v>86.5</v>
+        <v>70.16</v>
       </c>
       <c r="I72" s="9" t="inlineStr">
         <is>
@@ -3699,10 +3699,10 @@
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>2.873</v>
+        <v>0.618</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>2.456</v>
+        <v>0.606</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="7" t="inlineStr"/>
@@ -3715,28 +3715,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0278</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>EDELTEQ</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E73" s="3" t="n">
-        <v>-0.0581</v>
+        <v>3.27</v>
+      </c>
+      <c r="E73" s="8" t="n">
+        <v>0.0391</v>
       </c>
       <c r="F73" s="4" t="n">
-        <v>2927800</v>
+        <v>2961200</v>
       </c>
       <c r="G73" s="5" t="n">
-        <v>0.52</v>
+        <v>0.93</v>
       </c>
       <c r="H73" t="n">
-        <v>54.56</v>
+        <v>86.5</v>
       </c>
       <c r="I73" s="9" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.393</v>
+        <v>2.873</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0.362</v>
+        <v>2.456</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="7" t="inlineStr"/>
@@ -3760,39 +3760,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0278</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>EDELTEQ</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>0.915</v>
+        <v>0.405</v>
       </c>
       <c r="E74" s="3" t="n">
-        <v>-0.08039999999999999</v>
+        <v>-0.0581</v>
       </c>
       <c r="F74" s="4" t="n">
-        <v>2764000</v>
+        <v>2947800</v>
       </c>
       <c r="G74" s="5" t="n">
-        <v>0.67</v>
+        <v>0.52</v>
       </c>
       <c r="H74" t="n">
-        <v>58.69</v>
-      </c>
-      <c r="I74" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.56</v>
+      </c>
+      <c r="I74" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.848</v>
+        <v>0.393</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0.586</v>
+        <v>0.362</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="7" t="inlineStr"/>
@@ -3820,10 +3820,10 @@
         <v>0.008199999999999999</v>
       </c>
       <c r="F75" s="4" t="n">
-        <v>2726300</v>
+        <v>2876600</v>
       </c>
       <c r="G75" s="5" t="n">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="H75" t="n">
         <v>53.17</v>
@@ -3850,28 +3850,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>0.835</v>
+        <v>1.23</v>
       </c>
       <c r="E76" s="3" t="n">
-        <v>-0.0118</v>
+        <v>-0.016</v>
       </c>
       <c r="F76" s="4" t="n">
-        <v>2684300</v>
+        <v>2815000</v>
       </c>
       <c r="G76" s="5" t="n">
-        <v>0.89</v>
+        <v>0.32</v>
       </c>
       <c r="H76" t="n">
-        <v>15.99</v>
+        <v>38.68</v>
       </c>
       <c r="I76" s="6" t="inlineStr">
         <is>
@@ -3879,10 +3879,10 @@
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.908</v>
+        <v>1.292</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0.97</v>
+        <v>1.314</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="7" t="inlineStr"/>
@@ -3895,28 +3895,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E77" s="8" t="n">
-        <v>0.0092</v>
+        <v>0.835</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>-0.0118</v>
       </c>
       <c r="F77" s="4" t="n">
-        <v>2628500</v>
+        <v>2802600</v>
       </c>
       <c r="G77" s="5" t="n">
-        <v>0.28</v>
+        <v>0.93</v>
       </c>
       <c r="H77" t="n">
-        <v>54.09</v>
+        <v>15.99</v>
       </c>
       <c r="I77" s="6" t="inlineStr">
         <is>
@@ -3924,10 +3924,10 @@
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.08</v>
+        <v>0.908</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1.047</v>
+        <v>0.97</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="7" t="inlineStr"/>
@@ -3940,28 +3940,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0259</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SNS</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>0.47</v>
+        <v>0.915</v>
       </c>
       <c r="E78" s="3" t="n">
-        <v>-0.0208</v>
+        <v>-0.08039999999999999</v>
       </c>
       <c r="F78" s="4" t="n">
-        <v>2574700</v>
+        <v>2764500</v>
       </c>
       <c r="G78" s="5" t="n">
-        <v>0.3</v>
+        <v>0.67</v>
       </c>
       <c r="H78" t="n">
-        <v>36.31</v>
+        <v>58.69</v>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.503</v>
+        <v>0.848</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0.523</v>
+        <v>0.586</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="7" t="inlineStr"/>
@@ -3985,28 +3985,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1.24</v>
+        <v>0.47</v>
       </c>
       <c r="E79" s="3" t="n">
-        <v>-0.008</v>
+        <v>-0.0208</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>2564700</v>
+        <v>2663700</v>
       </c>
       <c r="G79" s="5" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H79" t="n">
-        <v>39.92</v>
+        <v>36.31</v>
       </c>
       <c r="I79" s="6" t="inlineStr">
         <is>
@@ -4014,10 +4014,10 @@
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.293</v>
+        <v>0.503</v>
       </c>
       <c r="K79" s="2" t="n">
-        <v>1.314</v>
+        <v>0.523</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="7" t="inlineStr"/>
@@ -4030,28 +4030,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.09</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>2563000</v>
+        <v>2632700</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>0.84</v>
+        <v>0.28</v>
       </c>
       <c r="H80" t="n">
-        <v>51.48</v>
+        <v>52.65</v>
       </c>
       <c r="I80" s="6" t="inlineStr">
         <is>
@@ -4059,10 +4059,10 @@
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.865</v>
+        <v>1.079</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0.86</v>
+        <v>1.047</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="7" t="inlineStr"/>
@@ -4090,10 +4090,10 @@
         <v>-0.08220000000000001</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>2539000</v>
+        <v>2591900</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="H81" t="n">
         <v>24.71</v>
@@ -4120,28 +4120,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>0.765</v>
+        <v>0.865</v>
       </c>
       <c r="E82" s="3" t="n">
-        <v>-0.006500000000000001</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>2361200</v>
+        <v>2563000</v>
       </c>
       <c r="G82" s="5" t="n">
-        <v>0.29</v>
+        <v>0.84</v>
       </c>
       <c r="H82" t="n">
-        <v>48.22</v>
+        <v>51.48</v>
       </c>
       <c r="I82" s="6" t="inlineStr">
         <is>
@@ -4149,10 +4149,10 @@
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.771</v>
+        <v>0.865</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>0.772</v>
+        <v>0.86</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="7" t="inlineStr"/>
@@ -4180,10 +4180,10 @@
         <v>0</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>2309100</v>
+        <v>2373100</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="H83" t="n">
         <v>27.78</v>
@@ -4210,28 +4210,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>4.81</v>
+        <v>0.765</v>
       </c>
       <c r="E84" s="3" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.006500000000000001</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>2305600</v>
+        <v>2361200</v>
       </c>
       <c r="G84" s="5" t="n">
-        <v>0.09</v>
+        <v>0.29</v>
       </c>
       <c r="H84" t="n">
-        <v>46.62</v>
+        <v>48.22</v>
       </c>
       <c r="I84" s="6" t="inlineStr">
         <is>
@@ -4239,10 +4239,10 @@
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>4.894</v>
+        <v>0.771</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>4.736</v>
+        <v>0.772</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="7" t="inlineStr"/>
@@ -4255,28 +4255,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E85" s="8" t="n">
-        <v>0.0196</v>
+        <v>4.8</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>2299100</v>
+        <v>2315600</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>0.28</v>
+        <v>0.09</v>
       </c>
       <c r="H85" t="n">
-        <v>33.4</v>
+        <v>46.11</v>
       </c>
       <c r="I85" s="6" t="inlineStr">
         <is>
@@ -4284,10 +4284,10 @@
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.275</v>
+        <v>4.893</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>0.3</v>
+        <v>4.736</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="7" t="inlineStr"/>
@@ -4300,39 +4300,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="E86" s="8" t="n">
-        <v>0.0158</v>
+        <v>0.255</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>2280000</v>
+        <v>2307400</v>
       </c>
       <c r="G86" s="5" t="n">
-        <v>0.39</v>
+        <v>0.28</v>
       </c>
       <c r="H86" t="n">
-        <v>50.3</v>
-      </c>
-      <c r="I86" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.74</v>
+      </c>
+      <c r="I86" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>1.921</v>
+        <v>0.274</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>1.949</v>
+        <v>0.3</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="7" t="inlineStr"/>
@@ -4354,19 +4354,19 @@
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
       <c r="E87" s="8" t="n">
-        <v>0.026</v>
+        <v>0.013</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>2262700</v>
+        <v>2294800</v>
       </c>
       <c r="G87" s="5" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="H87" t="n">
-        <v>59.57</v>
+        <v>58.33</v>
       </c>
       <c r="I87" s="6" t="inlineStr">
         <is>
@@ -4374,10 +4374,10 @@
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.741</v>
+        <v>0.74</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0.706</v>
+        <v>0.705</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="7" t="inlineStr"/>
@@ -4390,28 +4390,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.94</v>
       </c>
       <c r="E88" s="8" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.0211</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>2253400</v>
+        <v>2284300</v>
       </c>
       <c r="G88" s="5" t="n">
-        <v>1.1</v>
+        <v>0.39</v>
       </c>
       <c r="H88" t="n">
-        <v>48.48</v>
+        <v>51.67</v>
       </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
@@ -4419,10 +4419,10 @@
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.922</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.95</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="7" t="inlineStr"/>
@@ -4435,39 +4435,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="E89" s="3" t="n">
-        <v>-0.008</v>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E89" s="8" t="n">
+        <v>0.0071</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>2125900</v>
+        <v>2270100</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>0.54</v>
+        <v>0.17</v>
       </c>
       <c r="H89" t="n">
-        <v>43.23</v>
-      </c>
-      <c r="I89" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.25</v>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>5.048</v>
+        <v>9.997999999999999</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>5.052</v>
+        <v>10.137</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="7" t="inlineStr"/>
@@ -4480,39 +4480,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E90" s="8" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F90" s="4" t="n">
-        <v>2108700</v>
+        <v>2253400</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>0.79</v>
+        <v>1.1</v>
       </c>
       <c r="H90" t="n">
-        <v>33.15</v>
-      </c>
-      <c r="I90" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.48</v>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.54</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0.569</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="7" t="inlineStr"/>
@@ -4525,39 +4525,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5843</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>KPS</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E91" s="3" t="n">
-        <v>-0.0313</v>
+        <v>0.515</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F91" s="4" t="n">
-        <v>2054800</v>
+        <v>2144700</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>11.46</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H91" t="n">
-        <v>69.41</v>
-      </c>
-      <c r="I91" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.15</v>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0.546</v>
+        <v>0.569</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="7" t="inlineStr"/>
@@ -4570,39 +4570,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E92" s="8" t="n">
-        <v>0.008100000000000001</v>
+        <v>4.95</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>2040900</v>
+        <v>2139400</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>0.15</v>
+        <v>0.54</v>
       </c>
       <c r="H92" t="n">
-        <v>46.87</v>
-      </c>
-      <c r="I92" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.23</v>
+      </c>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>9.999000000000001</v>
+        <v>5.048</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>10.138</v>
+        <v>5.052</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="7" t="inlineStr"/>
@@ -4624,19 +4624,19 @@
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="E93" s="3" t="n">
-        <v>-0.008199999999999999</v>
+        <v>-0.0164</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>1994700</v>
+        <v>2112800</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="H93" t="n">
-        <v>22.97</v>
+        <v>22.42</v>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
@@ -4644,10 +4644,10 @@
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.375</v>
+        <v>1.374</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>1.551</v>
+        <v>1.55</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="7" t="inlineStr"/>
@@ -4660,39 +4660,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5843</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>KPS</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>-0.0313</v>
+      </c>
+      <c r="F94" s="4" t="n">
+        <v>2054800</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>11.46</v>
+      </c>
+      <c r="H94" t="n">
+        <v>69.41</v>
+      </c>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="E94" s="3" t="n">
-        <v>-0.0667</v>
-      </c>
-      <c r="F94" s="4" t="n">
-        <v>1983000</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H94" t="n">
-        <v>52.01</v>
-      </c>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="n">
-        <v>0.569</v>
-      </c>
       <c r="K94" s="2" t="n">
-        <v>0.473</v>
+        <v>0.546</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="7" t="inlineStr"/>
@@ -4705,28 +4705,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>3.89</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E95" s="3" t="n">
-        <v>-0.0177</v>
+        <v>-0.0667</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>1922100</v>
+        <v>1983100</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="H95" t="n">
-        <v>50.09</v>
+        <v>52.01</v>
       </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
@@ -4734,10 +4734,10 @@
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>3.954</v>
+        <v>0.569</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>3.571</v>
+        <v>0.473</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="7" t="inlineStr"/>
@@ -4750,28 +4750,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E96" s="8" t="n">
-        <v>0.0122</v>
+        <v>3.9</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>1837700</v>
+        <v>1939800</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>0.61</v>
+        <v>0.2</v>
       </c>
       <c r="H96" t="n">
-        <v>39.94</v>
+        <v>50.43</v>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
@@ -4779,10 +4779,10 @@
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>2.549</v>
+        <v>3.955</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>2.676</v>
+        <v>3.572</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="7" t="inlineStr"/>
@@ -4795,39 +4795,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E97" s="8" t="n">
-        <v>0.0476</v>
+        <v>0.625</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>-0.031</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1829900</v>
+        <v>1896200</v>
       </c>
       <c r="G97" s="5" t="n">
-        <v>0.86</v>
+        <v>0.21</v>
       </c>
       <c r="H97" t="n">
-        <v>61.36</v>
-      </c>
-      <c r="I97" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.21</v>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.419</v>
+        <v>0.674</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>0.433</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="7" t="inlineStr"/>
@@ -4840,39 +4840,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>0397</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>5ER</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>0.23</v>
+        <v>2.48</v>
       </c>
       <c r="E98" s="8" t="n">
-        <v>0.0698</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>1825600</v>
+        <v>1845000</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>1.79</v>
+        <v>0.61</v>
       </c>
       <c r="H98" t="n">
-        <v>78.56</v>
-      </c>
-      <c r="I98" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.57</v>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.21</v>
+        <v>2.548</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0.21</v>
+        <v>2.676</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="7" t="inlineStr"/>
@@ -4885,39 +4885,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0397</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>5ER</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E99" s="3" t="n">
-        <v>-0.031</v>
+        <v>0.23</v>
+      </c>
+      <c r="E99" s="8" t="n">
+        <v>0.0698</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>1791600</v>
+        <v>1839800</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>0.2</v>
+        <v>1.81</v>
       </c>
       <c r="H99" t="n">
-        <v>39.21</v>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.56</v>
+      </c>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.674</v>
+        <v>0.21</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.21</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="7" t="inlineStr"/>
@@ -4930,39 +4930,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E100" s="3" t="n">
-        <v>-0.064</v>
+        <v>0.44</v>
+      </c>
+      <c r="E100" s="8" t="n">
+        <v>0.0476</v>
       </c>
       <c r="F100" s="4" t="n">
-        <v>1720800</v>
+        <v>1829900</v>
       </c>
       <c r="G100" s="5" t="n">
-        <v>0.33</v>
+        <v>0.86</v>
       </c>
       <c r="H100" t="n">
-        <v>28.06</v>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.36</v>
+      </c>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>2.764</v>
+        <v>0.419</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>2.878</v>
+        <v>0.433</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="7" t="inlineStr"/>
@@ -4975,28 +4975,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0196</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>QES</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>0.58</v>
+        <v>2.34</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>-0.0252</v>
+        <v>-0.064</v>
       </c>
       <c r="F101" s="4" t="n">
-        <v>1682400</v>
+        <v>1725100</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.38</v>
+        <v>0.34</v>
       </c>
       <c r="H101" t="n">
-        <v>46.78</v>
+        <v>28.06</v>
       </c>
       <c r="I101" s="6" t="inlineStr">
         <is>
@@ -5004,10 +5004,10 @@
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.596</v>
+        <v>2.764</v>
       </c>
       <c r="K101" s="2" t="n">
-        <v>0.586</v>
+        <v>2.878</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="7" t="inlineStr"/>
@@ -5020,39 +5020,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0345</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>SUNLOGY</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="E102" s="8" t="n">
-        <v>0.0048</v>
+        <v>0.4</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>1660800</v>
+        <v>1692200</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="H102" t="n">
-        <v>47.56</v>
-      </c>
-      <c r="I102" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.25</v>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>2.105</v>
+        <v>0.434</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>2.102</v>
+        <v>0.435</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="7" t="inlineStr"/>
@@ -5065,28 +5065,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1.33</v>
+        <v>2.83</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>-0.0075</v>
+        <v>-0.0105</v>
       </c>
       <c r="F103" s="4" t="n">
-        <v>1618000</v>
+        <v>1687100</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>0.79</v>
+        <v>0.18</v>
       </c>
       <c r="H103" t="n">
-        <v>37.05</v>
+        <v>53.79</v>
       </c>
       <c r="I103" s="6" t="inlineStr">
         <is>
@@ -5094,10 +5094,10 @@
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.363</v>
+        <v>2.801</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>1.342</v>
+        <v>2.672</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="7" t="inlineStr"/>
@@ -5110,28 +5110,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>6.48</v>
-      </c>
-      <c r="E104" s="3" t="n">
-        <v>-0.0107</v>
+        <v>2.08</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="4" t="n">
-        <v>1597900</v>
+        <v>1686400</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>0.27</v>
+        <v>0.1</v>
       </c>
       <c r="H104" t="n">
-        <v>56.43</v>
+        <v>45.7</v>
       </c>
       <c r="I104" s="9" t="inlineStr">
         <is>
@@ -5139,10 +5139,10 @@
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>6.206</v>
+        <v>2.104</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>5.931</v>
+        <v>2.102</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="7" t="inlineStr"/>
@@ -5155,28 +5155,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0196</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>QES</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>0.255</v>
+        <v>0.58</v>
       </c>
       <c r="E105" s="3" t="n">
-        <v>-0.0192</v>
+        <v>-0.0252</v>
       </c>
       <c r="F105" s="4" t="n">
-        <v>1582600</v>
+        <v>1683300</v>
       </c>
       <c r="G105" s="5" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H105" t="n">
-        <v>40.54</v>
+        <v>46.78</v>
       </c>
       <c r="I105" s="6" t="inlineStr">
         <is>
@@ -5184,10 +5184,10 @@
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>0.272</v>
+        <v>0.596</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0.292</v>
+        <v>0.586</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="7" t="inlineStr"/>
@@ -5200,28 +5200,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>2.84</v>
+        <v>1.33</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>-0.006999999999999999</v>
+        <v>-0.0075</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>1559800</v>
+        <v>1618000</v>
       </c>
       <c r="G106" s="5" t="n">
-        <v>0.17</v>
+        <v>0.79</v>
       </c>
       <c r="H106" t="n">
-        <v>54.45</v>
+        <v>37.05</v>
       </c>
       <c r="I106" s="6" t="inlineStr">
         <is>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>2.801</v>
+        <v>1.363</v>
       </c>
       <c r="K106" s="2" t="n">
-        <v>2.672</v>
+        <v>1.342</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="7" t="inlineStr"/>
@@ -5245,39 +5245,39 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>LAGENDA</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1.37</v>
+        <v>6.48</v>
       </c>
       <c r="E107" s="3" t="n">
-        <v>-0.0552</v>
+        <v>-0.0107</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>1519900</v>
+        <v>1610500</v>
       </c>
       <c r="G107" s="5" t="n">
-        <v>2.02</v>
+        <v>0.27</v>
       </c>
       <c r="H107" t="n">
-        <v>26.48</v>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.43</v>
+      </c>
+      <c r="I107" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.491</v>
+        <v>6.206</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>1.502</v>
+        <v>5.931</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="7" t="inlineStr"/>
@@ -5290,28 +5290,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0345</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SUNLOGY</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>-0.0192</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>1501600</v>
+        <v>1582600</v>
       </c>
       <c r="G108" s="5" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H108" t="n">
-        <v>41.34</v>
+        <v>40.54</v>
       </c>
       <c r="I108" s="6" t="inlineStr">
         <is>
@@ -5319,10 +5319,10 @@
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.434</v>
+        <v>0.272</v>
       </c>
       <c r="K108" s="2" t="n">
-        <v>0.435</v>
+        <v>0.292</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="7" t="inlineStr"/>
@@ -5335,28 +5335,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>0.725</v>
+        <v>3.78</v>
       </c>
       <c r="E109" s="3" t="n">
-        <v>-0.0268</v>
+        <v>-0.0182</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>1471500</v>
+        <v>1571400</v>
       </c>
       <c r="G109" s="5" t="n">
-        <v>0.24</v>
+        <v>0.53</v>
       </c>
       <c r="H109" t="n">
-        <v>49.44</v>
+        <v>48.34</v>
       </c>
       <c r="I109" s="6" t="inlineStr">
         <is>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.741</v>
+        <v>3.844</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>0.679</v>
+        <v>3.699</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="7" t="inlineStr"/>
@@ -5389,19 +5389,19 @@
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>-0.018</v>
+        <v>-0.027</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>1470800</v>
+        <v>1555900</v>
       </c>
       <c r="G110" s="5" t="n">
-        <v>0.36</v>
+        <v>0.38</v>
       </c>
       <c r="H110" t="n">
-        <v>41.92</v>
+        <v>40.67</v>
       </c>
       <c r="I110" s="6" t="inlineStr">
         <is>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>1.149</v>
+        <v>1.148</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>1.103</v>
+        <v>1.102</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="7" t="inlineStr"/>
@@ -5425,28 +5425,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>LHI</t>
+          <t>LAGENDA</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E111" s="8" t="n">
-        <v>0.006999999999999999</v>
+        <v>1.35</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>-0.06900000000000001</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1468200</v>
+        <v>1550900</v>
       </c>
       <c r="G111" s="5" t="n">
-        <v>0.77</v>
+        <v>2.06</v>
       </c>
       <c r="H111" t="n">
-        <v>44.05</v>
+        <v>24.75</v>
       </c>
       <c r="I111" s="6" t="inlineStr">
         <is>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.729</v>
+        <v>1.489</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0.744</v>
+        <v>1.502</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="7" t="inlineStr"/>
@@ -5470,28 +5470,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0261</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>COSMOS</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>0.38</v>
+        <v>0.725</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>-0.0843</v>
+        <v>-0.0268</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>1450900</v>
+        <v>1497500</v>
       </c>
       <c r="G112" s="5" t="n">
-        <v>3.06</v>
+        <v>0.24</v>
       </c>
       <c r="H112" t="n">
-        <v>51.34</v>
+        <v>49.44</v>
       </c>
       <c r="I112" s="6" t="inlineStr">
         <is>
@@ -5499,10 +5499,10 @@
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.382</v>
+        <v>0.741</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0.365</v>
+        <v>0.679</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="7" t="inlineStr"/>
@@ -5515,28 +5515,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="E113" s="3" t="n">
-        <v>-0.0182</v>
+        <v>1.11</v>
+      </c>
+      <c r="E113" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>1450200</v>
+        <v>1480100</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>0.49</v>
+        <v>0.33</v>
       </c>
       <c r="H113" t="n">
-        <v>48.34</v>
+        <v>58.81</v>
       </c>
       <c r="I113" s="6" t="inlineStr">
         <is>
@@ -5544,10 +5544,10 @@
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>3.844</v>
+        <v>1.06</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>3.699</v>
+        <v>0.923</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="7" t="inlineStr"/>
@@ -5560,28 +5560,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>LHI</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E114" s="3" t="n">
-        <v>-0.0121</v>
+        <v>0.71</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="4" t="n">
-        <v>1438700</v>
+        <v>1469200</v>
       </c>
       <c r="G114" s="5" t="n">
-        <v>0.41</v>
+        <v>0.77</v>
       </c>
       <c r="H114" t="n">
-        <v>49.71</v>
+        <v>42.1</v>
       </c>
       <c r="I114" s="6" t="inlineStr">
         <is>
@@ -5589,10 +5589,10 @@
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.825</v>
+        <v>0.728</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0.785</v>
+        <v>0.744</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="7" t="inlineStr"/>
@@ -5605,28 +5605,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0261</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>COSMOS</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>0</v>
+        <v>0.38</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>-0.0843</v>
       </c>
       <c r="F115" s="4" t="n">
-        <v>1437900</v>
+        <v>1455800</v>
       </c>
       <c r="G115" s="5" t="n">
-        <v>0.32</v>
+        <v>3.07</v>
       </c>
       <c r="H115" t="n">
-        <v>58.81</v>
+        <v>51.34</v>
       </c>
       <c r="I115" s="6" t="inlineStr">
         <is>
@@ -5634,10 +5634,10 @@
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.06</v>
+        <v>0.382</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0.923</v>
+        <v>0.365</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="7" t="inlineStr"/>
@@ -5650,39 +5650,39 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>0.96</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="E116" s="3" t="n">
-        <v>-0.0154</v>
+        <v>-0.0121</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1416700</v>
+        <v>1449500</v>
       </c>
       <c r="G116" s="5" t="n">
-        <v>0.23</v>
+        <v>0.41</v>
       </c>
       <c r="H116" t="n">
-        <v>62.32</v>
-      </c>
-      <c r="I116" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.71</v>
+      </c>
+      <c r="I116" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.929</v>
+        <v>0.825</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0.88</v>
+        <v>0.785</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="7" t="inlineStr"/>
@@ -5695,39 +5695,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0298</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>WENTEL</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E117" s="3" t="n">
-        <v>-0.0208</v>
+        <v>0.335</v>
+      </c>
+      <c r="E117" s="8" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F117" s="4" t="n">
-        <v>1405700</v>
+        <v>1422400</v>
       </c>
       <c r="G117" s="5" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="H117" t="n">
-        <v>36.08</v>
-      </c>
-      <c r="I117" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.93</v>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.252</v>
+        <v>0.335</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0.273</v>
+        <v>0.343</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="7" t="inlineStr"/>
@@ -5740,28 +5740,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>0.58</v>
+        <v>0.965</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-0.0252</v>
+        <v>-0.0103</v>
       </c>
       <c r="F118" s="4" t="n">
-        <v>1405600</v>
+        <v>1421700</v>
       </c>
       <c r="G118" s="5" t="n">
-        <v>0.34</v>
+        <v>0.23</v>
       </c>
       <c r="H118" t="n">
-        <v>65.84</v>
+        <v>64.12</v>
       </c>
       <c r="I118" s="9" t="inlineStr">
         <is>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>0.517</v>
+        <v>0.929</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0.472</v>
+        <v>0.88</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="7" t="inlineStr"/>
@@ -5785,39 +5785,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E119" s="8" t="n">
-        <v>0.0152</v>
+        <v>1.25</v>
+      </c>
+      <c r="E119" s="3" t="n">
+        <v>-0.0157</v>
       </c>
       <c r="F119" s="4" t="n">
-        <v>1405300</v>
+        <v>1419000</v>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.29</v>
+        <v>0.45</v>
       </c>
       <c r="H119" t="n">
-        <v>47.93</v>
-      </c>
-      <c r="I119" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.08</v>
+      </c>
+      <c r="I119" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.335</v>
+        <v>1.284</v>
       </c>
       <c r="K119" s="2" t="n">
-        <v>0.343</v>
+        <v>1.229</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="7" t="inlineStr"/>
@@ -5830,28 +5830,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5932</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>BPURI</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>0.215</v>
+        <v>1.19</v>
       </c>
       <c r="E120" s="3" t="n">
-        <v>-0.0227</v>
+        <v>-0.0083</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>1383900</v>
+        <v>1417800</v>
       </c>
       <c r="G120" s="5" t="n">
-        <v>1.84</v>
+        <v>0.42</v>
       </c>
       <c r="H120" t="n">
-        <v>42.03</v>
+        <v>48.39</v>
       </c>
       <c r="I120" s="6" t="inlineStr">
         <is>
@@ -5859,10 +5859,10 @@
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.223</v>
+        <v>1.235</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>0.232</v>
+        <v>1.076</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="7" t="inlineStr"/>
@@ -5875,39 +5875,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>1.25</v>
+        <v>0.58</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>-0.0157</v>
+        <v>-0.0252</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>1378500</v>
+        <v>1411600</v>
       </c>
       <c r="G121" s="5" t="n">
-        <v>0.44</v>
+        <v>0.34</v>
       </c>
       <c r="H121" t="n">
-        <v>48.08</v>
-      </c>
-      <c r="I121" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>65.84</v>
+      </c>
+      <c r="I121" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.284</v>
+        <v>0.517</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>1.229</v>
+        <v>0.472</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="7" t="inlineStr"/>
@@ -5920,28 +5920,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0298</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>WENTEL</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="E122" s="10" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1370700</v>
+        <v>1405700</v>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="H122" t="n">
-        <v>49.45</v>
+        <v>36.08</v>
       </c>
       <c r="I122" s="6" t="inlineStr">
         <is>
@@ -5949,10 +5949,10 @@
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>1.236</v>
+        <v>0.252</v>
       </c>
       <c r="K122" s="2" t="n">
-        <v>1.077</v>
+        <v>0.273</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="7" t="inlineStr"/>
@@ -5965,28 +5965,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0268</t>
+          <t>5932</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>L&amp;PBHD</t>
+          <t>BPURI</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>0.225</v>
+        <v>0.215</v>
       </c>
       <c r="E123" s="3" t="n">
-        <v>-0.0217</v>
+        <v>-0.0227</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1310700</v>
+        <v>1383900</v>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.68</v>
+        <v>1.84</v>
       </c>
       <c r="H123" t="n">
-        <v>56.71</v>
+        <v>42.03</v>
       </c>
       <c r="I123" s="6" t="inlineStr">
         <is>
@@ -5994,10 +5994,10 @@
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.221</v>
+        <v>0.223</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0.185</v>
+        <v>0.232</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="7" t="inlineStr"/>
@@ -6010,28 +6010,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E124" s="8" t="n">
-        <v>0.0075</v>
+        <v>0.64</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>-0.03759999999999999</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>1272600</v>
+        <v>1377800</v>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.08</v>
+        <v>0.42</v>
       </c>
       <c r="H124" t="n">
-        <v>39.24</v>
+        <v>32.17</v>
       </c>
       <c r="I124" s="6" t="inlineStr">
         <is>
@@ -6039,10 +6039,10 @@
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.742</v>
+        <v>0.716</v>
       </c>
       <c r="K124" s="2" t="n">
-        <v>0.723</v>
+        <v>0.743</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="7" t="inlineStr"/>
@@ -6055,28 +6055,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E125" s="8" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.62</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>-0.0159</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>1267700</v>
+        <v>1357800</v>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.18</v>
+        <v>0.37</v>
       </c>
       <c r="H125" t="n">
-        <v>53.65</v>
+        <v>45.29</v>
       </c>
       <c r="I125" s="6" t="inlineStr">
         <is>
@@ -6084,10 +6084,10 @@
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.172</v>
+        <v>0.636</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1.14</v>
+        <v>0.616</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="7" t="inlineStr"/>
@@ -6100,28 +6100,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0167</t>
+          <t>0268</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MCLEAN</t>
+          <t>L&amp;PBHD</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>0.645</v>
+        <v>0.22</v>
       </c>
       <c r="E126" s="3" t="n">
-        <v>-0.0301</v>
+        <v>-0.0435</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>1258700</v>
+        <v>1318700</v>
       </c>
       <c r="G126" s="5" t="n">
-        <v>0.38</v>
+        <v>0.68</v>
       </c>
       <c r="H126" t="n">
-        <v>32.82</v>
+        <v>53.76</v>
       </c>
       <c r="I126" s="6" t="inlineStr">
         <is>
@@ -6129,10 +6129,10 @@
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.717</v>
+        <v>0.221</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0.743</v>
+        <v>0.185</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="7" t="inlineStr"/>
@@ -6145,39 +6145,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>0.275</v>
+        <v>7.09</v>
       </c>
       <c r="E127" s="3" t="n">
-        <v>-0.0179</v>
+        <v>-0.0288</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>1239800</v>
+        <v>1282600</v>
       </c>
       <c r="G127" s="5" t="n">
-        <v>1.33</v>
+        <v>0.29</v>
       </c>
       <c r="H127" t="n">
-        <v>51.1</v>
-      </c>
-      <c r="I127" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.67</v>
+      </c>
+      <c r="I127" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.276</v>
+        <v>7.326</v>
       </c>
       <c r="K127" s="2" t="n">
-        <v>0.268</v>
+        <v>6.904</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="7" t="inlineStr"/>
@@ -6190,28 +6190,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>7.1</v>
-      </c>
-      <c r="E128" s="3" t="n">
-        <v>-0.0274</v>
+        <v>0.68</v>
+      </c>
+      <c r="E128" s="8" t="n">
+        <v>0.0149</v>
       </c>
       <c r="F128" s="4" t="n">
-        <v>1239700</v>
+        <v>1274500</v>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.29</v>
+        <v>0.08</v>
       </c>
       <c r="H128" t="n">
-        <v>46.87</v>
+        <v>40.17</v>
       </c>
       <c r="I128" s="6" t="inlineStr">
         <is>
@@ -6219,10 +6219,10 @@
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>7.327</v>
+        <v>0.742</v>
       </c>
       <c r="K128" s="2" t="n">
-        <v>6.904</v>
+        <v>0.723</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="7" t="inlineStr"/>
@@ -6235,28 +6235,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>0.985</v>
-      </c>
-      <c r="E129" s="3" t="n">
-        <v>-0.0343</v>
+        <v>1.19</v>
+      </c>
+      <c r="E129" s="8" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F129" s="4" t="n">
-        <v>1235100</v>
+        <v>1273100</v>
       </c>
       <c r="G129" s="5" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="H129" t="n">
-        <v>44.23</v>
+        <v>53.65</v>
       </c>
       <c r="I129" s="6" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>1.039</v>
+        <v>1.172</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>0.949</v>
+        <v>1.14</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="7" t="inlineStr"/>
@@ -6280,39 +6280,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>10.42</v>
+        <v>0.275</v>
       </c>
       <c r="E130" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0179</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>1202400</v>
+        <v>1240000</v>
       </c>
       <c r="G130" s="5" t="n">
-        <v>0.34</v>
+        <v>1.33</v>
       </c>
       <c r="H130" t="n">
-        <v>53.31</v>
-      </c>
-      <c r="I130" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.1</v>
+      </c>
+      <c r="I130" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>10.415</v>
+        <v>0.276</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>9.781000000000001</v>
+        <v>0.268</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="7" t="inlineStr"/>
@@ -6325,39 +6325,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>1.27</v>
+        <v>0.5</v>
       </c>
       <c r="E131" s="3" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0196</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>1200800</v>
+        <v>1239200</v>
       </c>
       <c r="G131" s="5" t="n">
         <v>0.29</v>
       </c>
       <c r="H131" t="n">
-        <v>51.75</v>
-      </c>
-      <c r="I131" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.84</v>
+      </c>
+      <c r="I131" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>1.261</v>
+        <v>0.574</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>1.276</v>
+        <v>0.597</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="7" t="inlineStr"/>
@@ -6370,28 +6370,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>0.5</v>
+        <v>0.985</v>
       </c>
       <c r="E132" s="3" t="n">
-        <v>-0.0196</v>
+        <v>-0.0343</v>
       </c>
       <c r="F132" s="4" t="n">
-        <v>1189200</v>
+        <v>1237300</v>
       </c>
       <c r="G132" s="5" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="H132" t="n">
-        <v>29.84</v>
+        <v>44.23</v>
       </c>
       <c r="I132" s="6" t="inlineStr">
         <is>
@@ -6399,10 +6399,10 @@
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.574</v>
+        <v>1.039</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>0.597</v>
+        <v>0.949</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="7" t="inlineStr"/>
@@ -6415,28 +6415,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>7173</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>TOYOVEN</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E133" s="3" t="n">
-        <v>-0.0256</v>
+        <v>0.245</v>
+      </c>
+      <c r="E133" s="8" t="n">
+        <v>0.0208</v>
       </c>
       <c r="F133" s="4" t="n">
-        <v>1174200</v>
+        <v>1217700</v>
       </c>
       <c r="G133" s="5" t="n">
-        <v>0.47</v>
+        <v>1.24</v>
       </c>
       <c r="H133" t="n">
-        <v>46.47</v>
+        <v>64.06</v>
       </c>
       <c r="I133" s="9" t="inlineStr">
         <is>
@@ -6444,10 +6444,10 @@
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>0.387</v>
+        <v>0.224</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0.39</v>
+        <v>0.211</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="7" t="inlineStr"/>
@@ -6460,39 +6460,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E134" s="10" t="n">
-        <v>0</v>
+        <v>10.4</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>1129600</v>
+        <v>1211000</v>
       </c>
       <c r="G134" s="5" t="n">
-        <v>1.08</v>
+        <v>0.34</v>
       </c>
       <c r="H134" t="n">
-        <v>42.78</v>
-      </c>
-      <c r="I134" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.9</v>
+      </c>
+      <c r="I134" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.229</v>
+        <v>10.413</v>
       </c>
       <c r="K134" s="2" t="n">
-        <v>0.238</v>
+        <v>9.781000000000001</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="7" t="inlineStr"/>
@@ -6505,28 +6505,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E135" s="8" t="n">
-        <v>0.0159</v>
+        <v>1.27</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>1129300</v>
+        <v>1206300</v>
       </c>
       <c r="G135" s="5" t="n">
-        <v>0.21</v>
+        <v>0.29</v>
       </c>
       <c r="H135" t="n">
-        <v>53.49</v>
+        <v>51.75</v>
       </c>
       <c r="I135" s="9" t="inlineStr">
         <is>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>4.367</v>
+        <v>1.261</v>
       </c>
       <c r="K135" s="2" t="n">
-        <v>4.431</v>
+        <v>1.276</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="7" t="inlineStr"/>
@@ -6550,39 +6550,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>2.4</v>
+        <v>0.38</v>
       </c>
       <c r="E136" s="3" t="n">
-        <v>-0.0083</v>
+        <v>-0.0256</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>1125900</v>
+        <v>1174200</v>
       </c>
       <c r="G136" s="5" t="n">
-        <v>0.24</v>
+        <v>0.47</v>
       </c>
       <c r="H136" t="n">
-        <v>35.11</v>
-      </c>
-      <c r="I136" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.47</v>
+      </c>
+      <c r="I136" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>2.529</v>
+        <v>0.387</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>2.7</v>
+        <v>0.39</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="7" t="inlineStr"/>
@@ -6595,39 +6595,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>7173</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TOYOVEN</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>0.245</v>
-      </c>
-      <c r="E137" s="8" t="n">
-        <v>0.0208</v>
+        <v>2.55</v>
+      </c>
+      <c r="E137" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>1117700</v>
+        <v>1154100</v>
       </c>
       <c r="G137" s="5" t="n">
-        <v>1.14</v>
+        <v>0.19</v>
       </c>
       <c r="H137" t="n">
-        <v>64.06</v>
-      </c>
-      <c r="I137" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.14</v>
+      </c>
+      <c r="I137" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.224</v>
+        <v>2.603</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>0.211</v>
+        <v>2.61</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="7" t="inlineStr"/>
@@ -6640,39 +6640,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>2.55</v>
+        <v>0.225</v>
       </c>
       <c r="E138" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1112700</v>
+        <v>1145600</v>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.19</v>
+        <v>1.1</v>
       </c>
       <c r="H138" t="n">
-        <v>45.14</v>
-      </c>
-      <c r="I138" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.78</v>
+      </c>
+      <c r="I138" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>2.603</v>
+        <v>0.229</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>2.61</v>
+        <v>0.238</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="7" t="inlineStr"/>
@@ -6685,28 +6685,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>2.33</v>
+        <v>4.47</v>
       </c>
       <c r="E139" s="8" t="n">
-        <v>0.008699999999999999</v>
+        <v>0.0159</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>1103300</v>
+        <v>1143500</v>
       </c>
       <c r="G139" s="5" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="H139" t="n">
-        <v>60.34</v>
+        <v>53.49</v>
       </c>
       <c r="I139" s="9" t="inlineStr">
         <is>
@@ -6714,10 +6714,10 @@
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>2.233</v>
+        <v>4.367</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>2.175</v>
+        <v>4.431</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="7" t="inlineStr"/>
@@ -6730,28 +6730,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>0</v>
+        <v>2.38</v>
+      </c>
+      <c r="E140" s="3" t="n">
+        <v>-0.0165</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>1072900</v>
+        <v>1137900</v>
       </c>
       <c r="G140" s="5" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="H140" t="n">
-        <v>27.88</v>
+        <v>33.98</v>
       </c>
       <c r="I140" s="6" t="inlineStr">
         <is>
@@ -6759,10 +6759,10 @@
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.719</v>
+        <v>2.527</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0.786</v>
+        <v>2.699</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="7" t="inlineStr"/>
@@ -6775,39 +6775,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0</v>
+        <v>2.33</v>
+      </c>
+      <c r="E141" s="8" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>1029100</v>
+        <v>1104300</v>
       </c>
       <c r="G141" s="5" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="H141" t="n">
-        <v>49.34</v>
-      </c>
-      <c r="I141" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.34</v>
+      </c>
+      <c r="I141" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>6.755</v>
+        <v>2.233</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>6.824</v>
+        <v>2.175</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="7" t="inlineStr"/>
@@ -6820,28 +6820,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0391</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>AMBEST</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="E142" s="3" t="n">
-        <v>-0.0157</v>
+        <v>-0.0379</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1028500</v>
+        <v>1095000</v>
       </c>
       <c r="G142" s="5" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="H142" t="n">
-        <v>42.62</v>
+        <v>52.97</v>
       </c>
       <c r="I142" s="6" t="inlineStr">
         <is>
@@ -6849,10 +6849,10 @@
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>1.317</v>
+        <v>1.262</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1.288</v>
+        <v>1.176</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="7" t="inlineStr"/>
@@ -6865,39 +6865,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0233</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>PEKAT</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="E143" s="3" t="n">
-        <v>-0.0071</v>
+        <v>0.675</v>
+      </c>
+      <c r="E143" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>1027900</v>
+        <v>1082900</v>
       </c>
       <c r="G143" s="5" t="n">
-        <v>0.29</v>
+        <v>0.15</v>
       </c>
       <c r="H143" t="n">
-        <v>58.65</v>
-      </c>
-      <c r="I143" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>27.88</v>
+      </c>
+      <c r="I143" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>2.693</v>
+        <v>0.719</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>2.283</v>
+        <v>0.786</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="7" t="inlineStr"/>
@@ -6910,28 +6910,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>3794</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>MCEMENT</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="E144" s="3" t="n">
-        <v>-0.0113</v>
+        <v>6.75</v>
+      </c>
+      <c r="E144" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>977800</v>
+        <v>1070600</v>
       </c>
       <c r="G144" s="5" t="n">
-        <v>0.77</v>
+        <v>0.26</v>
       </c>
       <c r="H144" t="n">
-        <v>31.94</v>
+        <v>49.34</v>
       </c>
       <c r="I144" s="6" t="inlineStr">
         <is>
@@ -6939,10 +6939,10 @@
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>5.464</v>
+        <v>6.755</v>
       </c>
       <c r="K144" s="2" t="n">
-        <v>5.8</v>
+        <v>6.824</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="7" t="inlineStr"/>
@@ -6955,39 +6955,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>0359</t>
+          <t>0233</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>HKB</t>
+          <t>PEKAT</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>0.76</v>
+        <v>2.8</v>
       </c>
       <c r="E145" s="3" t="n">
-        <v>-0.0194</v>
+        <v>-0.0071</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>975800</v>
+        <v>1047900</v>
       </c>
       <c r="G145" s="5" t="n">
-        <v>0.43</v>
+        <v>0.3</v>
       </c>
       <c r="H145" t="n">
-        <v>62.26</v>
-      </c>
-      <c r="I145" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.65</v>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.733</v>
+        <v>2.693</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>0.652</v>
+        <v>2.283</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="7" t="inlineStr"/>
@@ -7000,28 +7000,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0391</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>AMBEST</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="E146" s="3" t="n">
-        <v>-0.0303</v>
+        <v>-0.0236</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>958900</v>
+        <v>1034700</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.39</v>
+        <v>0.47</v>
       </c>
       <c r="H146" t="n">
-        <v>53.95</v>
+        <v>41.7</v>
       </c>
       <c r="I146" s="6" t="inlineStr">
         <is>
@@ -7029,10 +7029,10 @@
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>1.263</v>
+        <v>1.316</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>1.176</v>
+        <v>1.288</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="7" t="inlineStr"/>
@@ -7045,28 +7045,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0353</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>WESTRVR</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>0.625</v>
+        <v>0.415</v>
       </c>
       <c r="E147" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>946300</v>
+        <v>1010200</v>
       </c>
       <c r="G147" s="5" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H147" t="n">
-        <v>46.98</v>
+        <v>51.62</v>
       </c>
       <c r="I147" s="6" t="inlineStr">
         <is>
@@ -7074,10 +7074,10 @@
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>0.637</v>
+        <v>0.416</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>0.616</v>
+        <v>0.385</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="7" t="inlineStr"/>
@@ -7090,28 +7090,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E148" s="8" t="n">
-        <v>0.0245</v>
+        <v>3.98</v>
+      </c>
+      <c r="E148" s="3" t="n">
+        <v>-0.0363</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>940300</v>
+        <v>992100</v>
       </c>
       <c r="G148" s="5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="H148" t="n">
-        <v>32.77</v>
+        <v>39.39</v>
       </c>
       <c r="I148" s="6" t="inlineStr">
         <is>
@@ -7119,10 +7119,10 @@
         </is>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.889</v>
+        <v>4.256</v>
       </c>
       <c r="K148" s="2" t="n">
-        <v>0.949</v>
+        <v>4.313</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="7" t="inlineStr"/>
@@ -7135,28 +7135,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>3794</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>MCEMENT</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>0.915</v>
-      </c>
-      <c r="E149" s="10" t="n">
-        <v>0</v>
+        <v>5.23</v>
+      </c>
+      <c r="E149" s="3" t="n">
+        <v>-0.0113</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>936900</v>
+        <v>984900</v>
       </c>
       <c r="G149" s="5" t="n">
-        <v>0.53</v>
+        <v>0.77</v>
       </c>
       <c r="H149" t="n">
-        <v>51.22</v>
+        <v>31.94</v>
       </c>
       <c r="I149" s="6" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         </is>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.915</v>
+        <v>5.464</v>
       </c>
       <c r="K149" s="2" t="n">
-        <v>0.879</v>
+        <v>5.8</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="7" t="inlineStr"/>
@@ -7180,28 +7180,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>0359</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>HKB</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>5.37</v>
-      </c>
-      <c r="E150" s="8" t="n">
-        <v>0.017</v>
+        <v>0.76</v>
+      </c>
+      <c r="E150" s="3" t="n">
+        <v>-0.0194</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>923100</v>
+        <v>975800</v>
       </c>
       <c r="G150" s="5" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
       <c r="H150" t="n">
-        <v>35.97</v>
+        <v>62.26</v>
       </c>
       <c r="I150" s="6" t="inlineStr">
         <is>
@@ -7209,10 +7209,10 @@
         </is>
       </c>
       <c r="J150" s="2" t="n">
-        <v>5.556</v>
+        <v>0.733</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>5.793</v>
+        <v>0.652</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="7" t="inlineStr"/>
@@ -7225,28 +7225,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TAKAFUL</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="E151" s="3" t="n">
-        <v>-0.0175</v>
+        <v>5.37</v>
+      </c>
+      <c r="E151" s="8" t="n">
+        <v>0.017</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>919800</v>
+        <v>967100</v>
       </c>
       <c r="G151" s="5" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
       <c r="H151" t="n">
-        <v>29.07</v>
+        <v>35.97</v>
       </c>
       <c r="I151" s="6" t="inlineStr">
         <is>
@@ -7254,10 +7254,10 @@
         </is>
       </c>
       <c r="J151" s="2" t="n">
-        <v>2.916</v>
+        <v>5.556</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>3.056</v>
+        <v>5.793</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="7" t="inlineStr"/>
@@ -7270,28 +7270,28 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="E152" s="3" t="n">
-        <v>-0.0127</v>
+        <v>0.83</v>
+      </c>
+      <c r="E152" s="8" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>908100</v>
+        <v>945600</v>
       </c>
       <c r="G152" s="5" t="n">
-        <v>0.59</v>
+        <v>0.29</v>
       </c>
       <c r="H152" t="n">
-        <v>49.79</v>
+        <v>31.05</v>
       </c>
       <c r="I152" s="6" t="inlineStr">
         <is>
@@ -7299,10 +7299,10 @@
         </is>
       </c>
       <c r="J152" s="2" t="n">
-        <v>3.167</v>
+        <v>0.889</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>2.894</v>
+        <v>0.949</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="7" t="inlineStr"/>
@@ -7315,28 +7315,28 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>1.27</v>
+        <v>0.895</v>
       </c>
       <c r="E153" s="3" t="n">
-        <v>-0.0231</v>
+        <v>-0.0219</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>899000</v>
+        <v>939400</v>
       </c>
       <c r="G153" s="5" t="n">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
       <c r="H153" t="n">
-        <v>22.86</v>
+        <v>48.11</v>
       </c>
       <c r="I153" s="6" t="inlineStr">
         <is>
@@ -7344,10 +7344,10 @@
         </is>
       </c>
       <c r="J153" s="2" t="n">
-        <v>1.39</v>
+        <v>0.914</v>
       </c>
       <c r="K153" s="2" t="n">
-        <v>1.459</v>
+        <v>0.878</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="7" t="inlineStr"/>
@@ -7360,28 +7360,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>TAKAFUL</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>1.68</v>
+        <v>2.81</v>
       </c>
       <c r="E154" s="3" t="n">
         <v>-0.0175</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>893900</v>
+        <v>926400</v>
       </c>
       <c r="G154" s="5" t="n">
-        <v>0.15</v>
+        <v>0.72</v>
       </c>
       <c r="H154" t="n">
-        <v>32.26</v>
+        <v>29.07</v>
       </c>
       <c r="I154" s="6" t="inlineStr">
         <is>
@@ -7389,10 +7389,10 @@
         </is>
       </c>
       <c r="J154" s="2" t="n">
-        <v>1.764</v>
+        <v>2.916</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>1.881</v>
+        <v>3.056</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="7" t="inlineStr"/>
@@ -7405,28 +7405,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>4.01</v>
+        <v>1.28</v>
       </c>
       <c r="E155" s="3" t="n">
-        <v>-0.0291</v>
+        <v>-0.0154</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>873500</v>
+        <v>911100</v>
       </c>
       <c r="G155" s="5" t="n">
-        <v>0.34</v>
+        <v>0.45</v>
       </c>
       <c r="H155" t="n">
-        <v>40.18</v>
+        <v>23.72</v>
       </c>
       <c r="I155" s="6" t="inlineStr">
         <is>
@@ -7434,10 +7434,10 @@
         </is>
       </c>
       <c r="J155" s="2" t="n">
-        <v>4.259</v>
+        <v>1.391</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>4.314</v>
+        <v>1.459</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="7" t="inlineStr"/>
@@ -7450,39 +7450,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>PGLOBAL</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>0.65</v>
+        <v>3.11</v>
       </c>
       <c r="E156" s="3" t="n">
-        <v>-0.0076</v>
+        <v>-0.0127</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>853600</v>
+        <v>908100</v>
       </c>
       <c r="G156" s="5" t="n">
-        <v>0.78</v>
+        <v>0.59</v>
       </c>
       <c r="H156" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="I156" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.79</v>
+      </c>
+      <c r="I156" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.585</v>
+        <v>3.167</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>0.532</v>
+        <v>2.894</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="7" t="inlineStr"/>
@@ -7495,39 +7495,39 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>0112</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MIKROMB</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>0.63</v>
+        <v>1.69</v>
       </c>
       <c r="E157" s="3" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0117</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>842400</v>
+        <v>907100</v>
       </c>
       <c r="G157" s="5" t="n">
-        <v>0.38</v>
+        <v>0.15</v>
       </c>
       <c r="H157" t="n">
-        <v>47.44</v>
-      </c>
-      <c r="I157" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.28</v>
+      </c>
+      <c r="I157" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.637</v>
+        <v>1.765</v>
       </c>
       <c r="K157" s="2" t="n">
-        <v>0.624</v>
+        <v>1.881</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="7" t="inlineStr"/>
@@ -7540,39 +7540,39 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5331</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>PGLOBAL</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>4.47</v>
+        <v>0.65</v>
       </c>
       <c r="E158" s="3" t="n">
-        <v>-0.0067</v>
+        <v>-0.0076</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>836300</v>
+        <v>871100</v>
       </c>
       <c r="G158" s="5" t="n">
-        <v>0.09</v>
+        <v>0.79</v>
       </c>
       <c r="H158" t="n">
-        <v>37.35</v>
-      </c>
-      <c r="I158" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.56</v>
+      </c>
+      <c r="I158" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J158" s="2" t="n">
-        <v>4.603</v>
+        <v>0.585</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>4.64</v>
+        <v>0.532</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="7" t="inlineStr"/>
@@ -7585,28 +7585,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>2.99</v>
+        <v>4.45</v>
       </c>
       <c r="E159" s="3" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.0111</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>820600</v>
+        <v>846900</v>
       </c>
       <c r="G159" s="5" t="n">
-        <v>0.27</v>
+        <v>0.09</v>
       </c>
       <c r="H159" t="n">
-        <v>50.24</v>
+        <v>36.17</v>
       </c>
       <c r="I159" s="6" t="inlineStr">
         <is>
@@ -7614,10 +7614,10 @@
         </is>
       </c>
       <c r="J159" s="2" t="n">
-        <v>3.024</v>
+        <v>4.601</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>2.858</v>
+        <v>4.64</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="7" t="inlineStr"/>
@@ -7645,10 +7645,10 @@
         <v>-0.0263</v>
       </c>
       <c r="F160" s="4" t="n">
-        <v>805300</v>
+        <v>845700</v>
       </c>
       <c r="G160" s="5" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="H160" t="n">
         <v>43.46</v>
@@ -7675,39 +7675,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>0112</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>JTIASA</t>
+          <t>MIKROMB</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>0.9</v>
+        <v>0.63</v>
       </c>
       <c r="E161" s="3" t="n">
-        <v>-0.011</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F161" s="4" t="n">
-        <v>789300</v>
+        <v>842400</v>
       </c>
       <c r="G161" s="5" t="n">
-        <v>0.46</v>
+        <v>0.38</v>
       </c>
       <c r="H161" t="n">
-        <v>31.3</v>
-      </c>
-      <c r="I161" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.44</v>
+      </c>
+      <c r="I161" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J161" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.637</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>0.999</v>
+        <v>0.624</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="7" t="inlineStr"/>
@@ -7720,28 +7720,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>5236</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>MATRIX</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>1.02</v>
+        <v>2.98</v>
       </c>
       <c r="E162" s="3" t="n">
-        <v>-0.0192</v>
+        <v>-0.0132</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>775200</v>
+        <v>841000</v>
       </c>
       <c r="G162" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.28</v>
       </c>
       <c r="H162" t="n">
-        <v>32.99</v>
+        <v>49.78</v>
       </c>
       <c r="I162" s="6" t="inlineStr">
         <is>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="J162" s="2" t="n">
-        <v>1.08</v>
+        <v>3.023</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>1.13</v>
+        <v>2.858</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="7" t="inlineStr"/>
@@ -7774,19 +7774,19 @@
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="E163" s="3" t="n">
-        <v>-0.067</v>
+        <v>-0.0622</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>772700</v>
+        <v>822700</v>
       </c>
       <c r="G163" s="5" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H163" t="n">
-        <v>42.69</v>
+        <v>43.16</v>
       </c>
       <c r="I163" s="6" t="inlineStr">
         <is>
@@ -7794,7 +7794,7 @@
         </is>
       </c>
       <c r="J163" s="2" t="n">
-        <v>2.097</v>
+        <v>2.098</v>
       </c>
       <c r="K163" s="2" t="n">
         <v>1.993</v>
@@ -7810,39 +7810,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5236</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>MATRIX</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>0.65</v>
+        <v>1.02</v>
       </c>
       <c r="E164" s="3" t="n">
-        <v>-0.0152</v>
+        <v>-0.0192</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>771200</v>
+        <v>804900</v>
       </c>
       <c r="G164" s="5" t="n">
-        <v>0.28</v>
+        <v>0.59</v>
       </c>
       <c r="H164" t="n">
-        <v>54.56</v>
-      </c>
-      <c r="I164" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.99</v>
+      </c>
+      <c r="I164" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.646</v>
+        <v>1.08</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.13</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="7" t="inlineStr"/>
@@ -7855,28 +7855,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0291</t>
+          <t>4383</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>CHB</t>
+          <t>JTIASA</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>2.39</v>
+        <v>0.9</v>
       </c>
       <c r="E165" s="3" t="n">
-        <v>-0.0285</v>
+        <v>-0.011</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>730000</v>
+        <v>789600</v>
       </c>
       <c r="G165" s="5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="H165" t="n">
-        <v>46.5</v>
+        <v>31.3</v>
       </c>
       <c r="I165" s="6" t="inlineStr">
         <is>
@@ -7884,10 +7884,10 @@
         </is>
       </c>
       <c r="J165" s="2" t="n">
-        <v>2.505</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>2.256</v>
+        <v>0.999</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="7" t="inlineStr"/>
@@ -7900,39 +7900,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>3662</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>MFLOUR</t>
+          <t>AWC</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E166" s="3" t="n">
-        <v>-0.0169</v>
+        <v>0.66</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>724800</v>
+        <v>771800</v>
       </c>
       <c r="G166" s="5" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="H166" t="n">
-        <v>36.97</v>
-      </c>
-      <c r="I166" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.04</v>
+      </c>
+      <c r="I166" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="2" t="n">
-        <v>0.602</v>
+        <v>0.647</v>
       </c>
       <c r="K166" s="2" t="n">
-        <v>0.63</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="7" t="inlineStr"/>
@@ -7945,39 +7945,39 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>7.46</v>
+        <v>3.19</v>
       </c>
       <c r="E167" s="3" t="n">
-        <v>-0.0027</v>
+        <v>-0.0062</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>694400</v>
+        <v>760900</v>
       </c>
       <c r="G167" s="5" t="n">
-        <v>0.27</v>
+        <v>0.13</v>
       </c>
       <c r="H167" t="n">
-        <v>44.29</v>
-      </c>
-      <c r="I167" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.97</v>
+      </c>
+      <c r="I167" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J167" s="2" t="n">
-        <v>7.565</v>
+        <v>3.349</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>7.754</v>
+        <v>3.593</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="7" t="inlineStr"/>
@@ -7990,28 +7990,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>0291</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>CHB</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="E168" s="10" t="n">
-        <v>0</v>
+        <v>2.39</v>
+      </c>
+      <c r="E168" s="3" t="n">
+        <v>-0.0285</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>670500</v>
+        <v>752400</v>
       </c>
       <c r="G168" s="5" t="n">
-        <v>0.11</v>
+        <v>0.43</v>
       </c>
       <c r="H168" t="n">
-        <v>32.06</v>
+        <v>46.5</v>
       </c>
       <c r="I168" s="6" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         </is>
       </c>
       <c r="J168" s="2" t="n">
-        <v>3.351</v>
+        <v>2.505</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>3.593</v>
+        <v>2.256</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="7" t="inlineStr"/>
@@ -8035,28 +8035,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>5338</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>PARADIGM</t>
+          <t>99SMART</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E169" s="3" t="n">
-        <v>-0.0062</v>
+        <v>3.11</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>664100</v>
+        <v>732000</v>
       </c>
       <c r="G169" s="5" t="n">
-        <v>1.73</v>
+        <v>0.21</v>
       </c>
       <c r="H169" t="n">
-        <v>25.89</v>
+        <v>42.63</v>
       </c>
       <c r="I169" s="6" t="inlineStr">
         <is>
@@ -8064,10 +8064,10 @@
         </is>
       </c>
       <c r="J169" s="2" t="n">
-        <v>0.819</v>
+        <v>3.148</v>
       </c>
       <c r="K169" s="2" t="n">
-        <v>0.848</v>
+        <v>3.314</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="7" t="inlineStr"/>
@@ -8080,28 +8080,28 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>3662</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>MFLOUR</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>0.79</v>
+        <v>0.585</v>
       </c>
       <c r="E170" s="3" t="n">
-        <v>-0.0063</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>648600</v>
+        <v>724900</v>
       </c>
       <c r="G170" s="5" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="H170" t="n">
-        <v>15.78</v>
+        <v>38.72</v>
       </c>
       <c r="I170" s="6" t="inlineStr">
         <is>
@@ -8109,10 +8109,10 @@
         </is>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.924</v>
+        <v>0.602</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>1.071</v>
+        <v>0.63</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="7" t="inlineStr"/>
@@ -8125,39 +8125,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>0340</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>NORTHERN</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E171" s="10" t="n">
-        <v>0</v>
+        <v>7.46</v>
+      </c>
+      <c r="E171" s="3" t="n">
+        <v>-0.0027</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>643100</v>
+        <v>702600</v>
       </c>
       <c r="G171" s="5" t="n">
-        <v>0.08</v>
+        <v>0.28</v>
       </c>
       <c r="H171" t="n">
-        <v>55.71</v>
-      </c>
-      <c r="I171" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>44.29</v>
+      </c>
+      <c r="I171" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J171" s="2" t="n">
-        <v>1.113</v>
+        <v>7.565</v>
       </c>
       <c r="K171" s="2" t="n">
-        <v>0.896</v>
+        <v>7.754</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="7" t="inlineStr"/>
@@ -8170,39 +8170,39 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>SUPERLN</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E172" s="8" t="n">
-        <v>0.0222</v>
+        <v>0.785</v>
+      </c>
+      <c r="E172" s="3" t="n">
+        <v>-0.0126</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>634200</v>
+        <v>698600</v>
       </c>
       <c r="G172" s="5" t="n">
-        <v>1.73</v>
+        <v>0.3</v>
       </c>
       <c r="H172" t="n">
-        <v>64.79000000000001</v>
-      </c>
-      <c r="I172" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>15.49</v>
+      </c>
+      <c r="I172" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.863</v>
+        <v>0.924</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>0.841</v>
+        <v>1.07</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="7" t="inlineStr"/>
@@ -8215,28 +8215,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>PARADIGM</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E173" s="10" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E173" s="3" t="n">
+        <v>-0.0124</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>630000</v>
+        <v>664600</v>
       </c>
       <c r="G173" s="5" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.73</v>
       </c>
       <c r="H173" t="n">
-        <v>45.03</v>
+        <v>23.74</v>
       </c>
       <c r="I173" s="6" t="inlineStr">
         <is>
@@ -8244,10 +8244,10 @@
         </is>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.631</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>0.631</v>
+        <v>0.848</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="7" t="inlineStr"/>
@@ -8269,19 +8269,19 @@
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>5.38</v>
+        <v>5.37</v>
       </c>
       <c r="E174" s="3" t="n">
-        <v>-0.0218</v>
+        <v>-0.0236</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>626900</v>
+        <v>655200</v>
       </c>
       <c r="G174" s="5" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="H174" t="n">
-        <v>47.67</v>
+        <v>47.43</v>
       </c>
       <c r="I174" s="6" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="J174" s="2" t="n">
-        <v>5.5</v>
+        <v>5.499</v>
       </c>
       <c r="K174" s="2" t="n">
         <v>5.387</v>
@@ -8305,28 +8305,28 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>7195</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>BNASTRA</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>2.83</v>
+        <v>2.13</v>
       </c>
       <c r="E175" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F175" s="4" t="n">
-        <v>612000</v>
+        <v>645600</v>
       </c>
       <c r="G175" s="5" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="H175" t="n">
-        <v>86.48</v>
+        <v>54.7</v>
       </c>
       <c r="I175" s="9" t="inlineStr">
         <is>
@@ -8334,10 +8334,10 @@
         </is>
       </c>
       <c r="J175" s="2" t="n">
-        <v>2.621</v>
+        <v>2.112</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>2.44</v>
+        <v>2.066</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="7" t="inlineStr"/>
@@ -8350,39 +8350,39 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5280</t>
+          <t>0340</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>KIPREIT</t>
+          <t>NORTHERN</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E176" s="3" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.13</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F176" s="4" t="n">
-        <v>609400</v>
+        <v>643100</v>
       </c>
       <c r="G176" s="5" t="n">
-        <v>0.91</v>
+        <v>0.08</v>
       </c>
       <c r="H176" t="n">
-        <v>56.24</v>
-      </c>
-      <c r="I176" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.71</v>
+      </c>
+      <c r="I176" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.862</v>
+        <v>1.113</v>
       </c>
       <c r="K176" s="2" t="n">
-        <v>0.854</v>
+        <v>0.896</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="7" t="inlineStr"/>
@@ -8395,28 +8395,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7235</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>SUPERLN</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E177" s="10" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E177" s="8" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F177" s="4" t="n">
-        <v>608600</v>
+        <v>634200</v>
       </c>
       <c r="G177" s="5" t="n">
-        <v>0.29</v>
+        <v>1.73</v>
       </c>
       <c r="H177" t="n">
-        <v>54.7</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="I177" s="9" t="inlineStr">
         <is>
@@ -8424,10 +8424,10 @@
         </is>
       </c>
       <c r="J177" s="2" t="n">
-        <v>2.112</v>
+        <v>0.863</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>2.066</v>
+        <v>0.841</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="7" t="inlineStr"/>
@@ -8440,28 +8440,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>6.19</v>
+        <v>0.63</v>
       </c>
       <c r="E178" s="10" t="n">
         <v>0</v>
       </c>
       <c r="F178" s="4" t="n">
-        <v>604000</v>
+        <v>630000</v>
       </c>
       <c r="G178" s="5" t="n">
-        <v>0.09</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H178" t="n">
-        <v>36.53</v>
+        <v>45.03</v>
       </c>
       <c r="I178" s="6" t="inlineStr">
         <is>
@@ -8469,10 +8469,10 @@
         </is>
       </c>
       <c r="J178" s="2" t="n">
-        <v>6.372</v>
+        <v>0.631</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>6.732</v>
+        <v>0.631</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="7" t="inlineStr"/>
@@ -8485,39 +8485,39 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>0326</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>SORENTO</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0.695</v>
+        <v>6.18</v>
       </c>
       <c r="E179" s="3" t="n">
-        <v>-0.0071</v>
+        <v>-0.0016</v>
       </c>
       <c r="F179" s="4" t="n">
-        <v>539300</v>
+        <v>626900</v>
       </c>
       <c r="G179" s="5" t="n">
-        <v>0.91</v>
+        <v>0.1</v>
       </c>
       <c r="H179" t="n">
-        <v>61.46</v>
-      </c>
-      <c r="I179" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.16</v>
+      </c>
+      <c r="I179" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.681</v>
+        <v>6.371</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>0.658</v>
+        <v>6.731</v>
       </c>
       <c r="L179" t="inlineStr"/>
       <c r="M179" s="7" t="inlineStr"/>
@@ -8530,39 +8530,39 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>7195</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>ANCOMNY</t>
+          <t>BNASTRA</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>0.8149999999999999</v>
-      </c>
-      <c r="E180" s="10" t="n">
-        <v>0</v>
+        <v>2.79</v>
+      </c>
+      <c r="E180" s="3" t="n">
+        <v>-0.0141</v>
       </c>
       <c r="F180" s="4" t="n">
-        <v>536300</v>
+        <v>622500</v>
       </c>
       <c r="G180" s="5" t="n">
-        <v>0.3</v>
+        <v>0.46</v>
       </c>
       <c r="H180" t="n">
-        <v>33.01</v>
-      </c>
-      <c r="I180" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.16</v>
+      </c>
+      <c r="I180" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J180" s="2" t="n">
-        <v>0.841</v>
+        <v>2.617</v>
       </c>
       <c r="K180" s="2" t="n">
-        <v>0.86</v>
+        <v>2.439</v>
       </c>
       <c r="L180" t="inlineStr"/>
       <c r="M180" s="7" t="inlineStr"/>
@@ -8575,28 +8575,28 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5280</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>MENTIGA</t>
+          <t>KIPREIT</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="E181" s="8" t="n">
-        <v>0.0564</v>
+        <v>0.865</v>
+      </c>
+      <c r="E181" s="3" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F181" s="4" t="n">
-        <v>535600</v>
+        <v>613900</v>
       </c>
       <c r="G181" s="5" t="n">
-        <v>3.93</v>
+        <v>0.92</v>
       </c>
       <c r="H181" t="n">
-        <v>84.45</v>
+        <v>56.24</v>
       </c>
       <c r="I181" s="9" t="inlineStr">
         <is>
@@ -8604,10 +8604,10 @@
         </is>
       </c>
       <c r="J181" s="2" t="n">
-        <v>0.723</v>
+        <v>0.862</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>0.661</v>
+        <v>0.854</v>
       </c>
       <c r="L181" t="inlineStr"/>
       <c r="M181" s="7" t="inlineStr"/>
@@ -8620,39 +8620,39 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>0326</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>99SMART</t>
+          <t>SORENTO</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>3.09</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E182" s="3" t="n">
-        <v>-0.0064</v>
+        <v>-0.0143</v>
       </c>
       <c r="F182" s="4" t="n">
-        <v>531600</v>
+        <v>569300</v>
       </c>
       <c r="G182" s="5" t="n">
-        <v>0.15</v>
+        <v>0.96</v>
       </c>
       <c r="H182" t="n">
-        <v>41.02</v>
-      </c>
-      <c r="I182" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.27</v>
+      </c>
+      <c r="I182" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J182" s="2" t="n">
-        <v>3.146</v>
+        <v>0.68</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>3.314</v>
+        <v>0.658</v>
       </c>
       <c r="L182" t="inlineStr"/>
       <c r="M182" s="7" t="inlineStr"/>
@@ -8665,28 +8665,28 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>4758</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>ANCOMNY</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="E183" s="8" t="n">
-        <v>0.0048</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>0</v>
       </c>
       <c r="F183" s="4" t="n">
-        <v>525500</v>
+        <v>536300</v>
       </c>
       <c r="G183" s="5" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H183" t="n">
-        <v>33.81</v>
+        <v>33.01</v>
       </c>
       <c r="I183" s="6" t="inlineStr">
         <is>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="J183" s="2" t="n">
-        <v>4.387</v>
+        <v>0.841</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>4.7</v>
+        <v>0.86</v>
       </c>
       <c r="L183" t="inlineStr"/>
       <c r="M183" s="7" t="inlineStr"/>
@@ -8710,39 +8710,39 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>0223</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>SAMAIDEN</t>
+          <t>MENTIGA</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="E184" s="3" t="n">
-        <v>-0.0275</v>
+        <v>1.02</v>
+      </c>
+      <c r="E184" s="8" t="n">
+        <v>0.0462</v>
       </c>
       <c r="F184" s="4" t="n">
-        <v>517800</v>
+        <v>535800</v>
       </c>
       <c r="G184" s="5" t="n">
-        <v>0.11</v>
+        <v>3.93</v>
       </c>
       <c r="H184" t="n">
-        <v>56.11</v>
-      </c>
-      <c r="I184" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.15000000000001</v>
+      </c>
+      <c r="I184" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J184" s="2" t="n">
-        <v>2.789</v>
+        <v>0.722</v>
       </c>
       <c r="K184" s="2" t="n">
-        <v>2.239</v>
+        <v>0.661</v>
       </c>
       <c r="L184" t="inlineStr"/>
       <c r="M184" s="7" t="inlineStr"/>
@@ -8755,45 +8755,135 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>5071</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>COASTAL</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>1.69</v>
+        <v>4.19</v>
       </c>
       <c r="E185" s="8" t="n">
-        <v>0.0562</v>
+        <v>0.0024</v>
       </c>
       <c r="F185" s="4" t="n">
-        <v>500500</v>
+        <v>530100</v>
       </c>
       <c r="G185" s="5" t="n">
-        <v>5.38</v>
+        <v>0.12</v>
       </c>
       <c r="H185" t="n">
-        <v>65.59999999999999</v>
-      </c>
-      <c r="I185" s="9" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33</v>
+      </c>
+      <c r="I185" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J185" s="2" t="n">
-        <v>1.583</v>
+        <v>4.387</v>
       </c>
       <c r="K185" s="2" t="n">
-        <v>1.57</v>
+        <v>4.7</v>
       </c>
       <c r="L185" t="inlineStr"/>
       <c r="M185" s="7" t="inlineStr"/>
     </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D186" s="2" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="E186" s="3" t="n">
+        <v>-0.0137</v>
+      </c>
+      <c r="F186" s="4" t="n">
+        <v>518000</v>
+      </c>
+      <c r="G186" s="5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H186" t="n">
+        <v>57.91</v>
+      </c>
+      <c r="I186" s="6" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="n">
+        <v>2.793</v>
+      </c>
+      <c r="K186" s="2" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="L186" t="inlineStr"/>
+      <c r="M186" s="7" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5071</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>COASTAL</t>
+        </is>
+      </c>
+      <c r="D187" s="2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="E187" s="8" t="n">
+        <v>0.0562</v>
+      </c>
+      <c r="F187" s="4" t="n">
+        <v>510500</v>
+      </c>
+      <c r="G187" s="5" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="H187" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="I187" s="9" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J187" s="2" t="n">
+        <v>1.583</v>
+      </c>
+      <c r="K187" s="2" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="L187" t="inlineStr"/>
+      <c r="M187" s="7" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M185"/>
+  <autoFilter ref="A1:M187"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>